--- a/GBDS MARCH FILES 2026/Guillermo DOS 2 - Neilven.xlsx
+++ b/GBDS MARCH FILES 2026/Guillermo DOS 2 - Neilven.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C0A890-A601-456B-88FC-6D3DDEA9208F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE2BFF14-BE44-4065-9D50-64CBA4449AEB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2065,6 +2065,199 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="51" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2074,48 +2267,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2182,225 +2333,74 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="51" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2951,28 +2951,28 @@
       <c r="C2" s="93"/>
       <c r="D2" s="93"/>
       <c r="E2" s="93"/>
-      <c r="F2" s="196" t="s">
+      <c r="F2" s="284" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="196"/>
-      <c r="H2" s="196"/>
-      <c r="I2" s="196"/>
-      <c r="J2" s="196"/>
-      <c r="K2" s="196"/>
-      <c r="L2" s="196"/>
-      <c r="M2" s="196"/>
-      <c r="N2" s="196"/>
-      <c r="O2" s="196"/>
-      <c r="P2" s="196"/>
-      <c r="Q2" s="196"/>
-      <c r="R2" s="196"/>
-      <c r="S2" s="196"/>
+      <c r="G2" s="284"/>
+      <c r="H2" s="284"/>
+      <c r="I2" s="284"/>
+      <c r="J2" s="284"/>
+      <c r="K2" s="284"/>
+      <c r="L2" s="284"/>
+      <c r="M2" s="284"/>
+      <c r="N2" s="284"/>
+      <c r="O2" s="284"/>
+      <c r="P2" s="284"/>
+      <c r="Q2" s="284"/>
+      <c r="R2" s="284"/>
+      <c r="S2" s="284"/>
       <c r="T2" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="U2" s="291"/>
-      <c r="V2" s="291"/>
-      <c r="X2" s="197" t="s">
+      <c r="U2" s="193"/>
+      <c r="V2" s="193"/>
+      <c r="X2" s="237" t="s">
         <v>2</v>
       </c>
       <c r="AB2" s="92">
@@ -2993,7 +2993,7 @@
       <c r="C3" s="93"/>
       <c r="D3" s="93"/>
       <c r="E3" s="93"/>
-      <c r="X3" s="198"/>
+      <c r="X3" s="238"/>
       <c r="AB3" s="92">
         <v>5.76</v>
       </c>
@@ -3014,21 +3014,21 @@
       <c r="C4" s="93"/>
       <c r="D4" s="93"/>
       <c r="E4" s="93"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="200"/>
-      <c r="H4" s="200"/>
-      <c r="I4" s="200"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="200"/>
-      <c r="L4" s="200"/>
-      <c r="M4" s="200"/>
+      <c r="F4" s="285"/>
+      <c r="G4" s="285"/>
+      <c r="H4" s="285"/>
+      <c r="I4" s="285"/>
+      <c r="J4" s="285"/>
+      <c r="K4" s="285"/>
+      <c r="L4" s="285"/>
+      <c r="M4" s="285"/>
       <c r="S4" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T4" s="201"/>
-      <c r="U4" s="201"/>
+      <c r="T4" s="286"/>
+      <c r="U4" s="286"/>
       <c r="V4" s="183"/>
-      <c r="X4" s="199"/>
+      <c r="X4" s="239"/>
       <c r="AB4" s="92">
         <v>5.07</v>
       </c>
@@ -3070,25 +3070,25 @@
       <c r="B6" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="202"/>
-      <c r="G6" s="202"/>
-      <c r="H6" s="202"/>
-      <c r="I6" s="202"/>
-      <c r="J6" s="202"/>
-      <c r="K6" s="202"/>
-      <c r="L6" s="202"/>
-      <c r="M6" s="202"/>
+      <c r="F6" s="287"/>
+      <c r="G6" s="287"/>
+      <c r="H6" s="287"/>
+      <c r="I6" s="287"/>
+      <c r="J6" s="287"/>
+      <c r="K6" s="287"/>
+      <c r="L6" s="287"/>
+      <c r="M6" s="287"/>
       <c r="S6" s="97" t="s">
         <v>6</v>
       </c>
       <c r="T6" s="163" t="s">
         <v>7</v>
       </c>
-      <c r="U6" s="288" t="s">
+      <c r="U6" s="279" t="s">
         <v>8</v>
       </c>
-      <c r="V6" s="288"/>
-      <c r="X6" s="197" t="s">
+      <c r="V6" s="279"/>
+      <c r="X6" s="237" t="s">
         <v>9</v>
       </c>
       <c r="AB6" s="92">
@@ -3111,14 +3111,14 @@
       <c r="C7" s="98"/>
       <c r="D7" s="98"/>
       <c r="E7" s="98"/>
-      <c r="F7" s="202"/>
-      <c r="G7" s="202"/>
-      <c r="H7" s="202"/>
-      <c r="I7" s="202"/>
-      <c r="J7" s="202"/>
-      <c r="K7" s="202"/>
-      <c r="L7" s="202"/>
-      <c r="M7" s="202"/>
+      <c r="F7" s="287"/>
+      <c r="G7" s="287"/>
+      <c r="H7" s="287"/>
+      <c r="I7" s="287"/>
+      <c r="J7" s="287"/>
+      <c r="K7" s="287"/>
+      <c r="L7" s="287"/>
+      <c r="M7" s="287"/>
       <c r="N7" s="99"/>
       <c r="O7" s="99"/>
       <c r="P7" s="99"/>
@@ -3127,9 +3127,9 @@
       <c r="T7" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="U7" s="289"/>
-      <c r="V7" s="290"/>
-      <c r="X7" s="199"/>
+      <c r="U7" s="280"/>
+      <c r="V7" s="281"/>
+      <c r="X7" s="239"/>
       <c r="AB7" s="92">
         <v>5.25</v>
       </c>
@@ -3163,127 +3163,127 @@
       <c r="V8" s="95"/>
     </row>
     <row r="9" spans="2:35" s="100" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="203" t="s">
+      <c r="B9" s="247" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="206" t="s">
+      <c r="C9" s="250" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="206" t="s">
+      <c r="D9" s="250" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="206" t="s">
+      <c r="E9" s="250" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="193" t="s">
+      <c r="F9" s="253" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="194"/>
-      <c r="H9" s="194"/>
-      <c r="I9" s="194"/>
-      <c r="J9" s="194"/>
-      <c r="K9" s="194"/>
-      <c r="L9" s="194"/>
-      <c r="M9" s="194"/>
-      <c r="N9" s="194"/>
-      <c r="O9" s="194"/>
-      <c r="P9" s="194"/>
-      <c r="Q9" s="195"/>
-      <c r="S9" s="292" t="s">
+      <c r="G9" s="254"/>
+      <c r="H9" s="254"/>
+      <c r="I9" s="254"/>
+      <c r="J9" s="254"/>
+      <c r="K9" s="254"/>
+      <c r="L9" s="254"/>
+      <c r="M9" s="254"/>
+      <c r="N9" s="254"/>
+      <c r="O9" s="254"/>
+      <c r="P9" s="254"/>
+      <c r="Q9" s="255"/>
+      <c r="S9" s="288" t="s">
         <v>17</v>
       </c>
-      <c r="T9" s="292"/>
-      <c r="U9" s="292"/>
-      <c r="V9" s="292"/>
-      <c r="Y9" s="219" t="s">
+      <c r="T9" s="288"/>
+      <c r="U9" s="288"/>
+      <c r="V9" s="288"/>
+      <c r="Y9" s="266" t="s">
         <v>18</v>
       </c>
-      <c r="Z9" s="222" t="s">
+      <c r="Z9" s="269" t="s">
         <v>19</v>
       </c>
       <c r="AA9" s="101"/>
-      <c r="AB9" s="209" t="s">
+      <c r="AB9" s="256" t="s">
         <v>20</v>
       </c>
-      <c r="AC9" s="225" t="s">
+      <c r="AC9" s="272" t="s">
         <v>21</v>
       </c>
-      <c r="AD9" s="228" t="s">
+      <c r="AD9" s="275" t="s">
         <v>84</v>
       </c>
-      <c r="AE9" s="209" t="s">
+      <c r="AE9" s="256" t="s">
         <v>22</v>
       </c>
-      <c r="AG9" s="209" t="s">
+      <c r="AG9" s="256" t="s">
         <v>23</v>
       </c>
       <c r="AH9" s="101"/>
-      <c r="AI9" s="209" t="s">
+      <c r="AI9" s="256" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="2:35" s="100" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="204"/>
-      <c r="C10" s="207"/>
-      <c r="D10" s="207"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="213" t="s">
+      <c r="B10" s="248"/>
+      <c r="C10" s="251"/>
+      <c r="D10" s="251"/>
+      <c r="E10" s="251"/>
+      <c r="F10" s="260" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="213" t="s">
+      <c r="G10" s="260" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="213" t="s">
+      <c r="H10" s="260" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="214" t="s">
+      <c r="I10" s="261" t="s">
         <v>28</v>
       </c>
-      <c r="J10" s="214" t="s">
+      <c r="J10" s="261" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="214" t="s">
+      <c r="K10" s="261" t="s">
         <v>30</v>
       </c>
-      <c r="L10" s="214" t="s">
+      <c r="L10" s="261" t="s">
         <v>31</v>
       </c>
-      <c r="M10" s="216" t="s">
+      <c r="M10" s="263" t="s">
         <v>32</v>
       </c>
-      <c r="N10" s="217"/>
-      <c r="O10" s="217"/>
-      <c r="P10" s="217"/>
-      <c r="Q10" s="218"/>
-      <c r="S10" s="292" t="s">
+      <c r="N10" s="264"/>
+      <c r="O10" s="264"/>
+      <c r="P10" s="264"/>
+      <c r="Q10" s="265"/>
+      <c r="S10" s="288" t="s">
         <v>33</v>
       </c>
-      <c r="T10" s="292"/>
-      <c r="U10" s="292"/>
-      <c r="V10" s="292"/>
-      <c r="Y10" s="220"/>
-      <c r="Z10" s="223"/>
+      <c r="T10" s="288"/>
+      <c r="U10" s="288"/>
+      <c r="V10" s="288"/>
+      <c r="Y10" s="267"/>
+      <c r="Z10" s="270"/>
       <c r="AA10" s="101"/>
-      <c r="AB10" s="210"/>
-      <c r="AC10" s="226"/>
-      <c r="AD10" s="229"/>
-      <c r="AE10" s="210"/>
-      <c r="AG10" s="210"/>
+      <c r="AB10" s="257"/>
+      <c r="AC10" s="273"/>
+      <c r="AD10" s="276"/>
+      <c r="AE10" s="257"/>
+      <c r="AG10" s="257"/>
       <c r="AH10" s="101"/>
-      <c r="AI10" s="210"/>
+      <c r="AI10" s="257"/>
     </row>
     <row r="11" spans="2:35" s="102" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="205"/>
-      <c r="C11" s="208"/>
-      <c r="D11" s="208"/>
-      <c r="E11" s="208"/>
-      <c r="F11" s="208"/>
-      <c r="G11" s="208"/>
-      <c r="H11" s="208"/>
-      <c r="I11" s="215"/>
-      <c r="J11" s="215"/>
-      <c r="K11" s="215"/>
-      <c r="L11" s="215"/>
+      <c r="B11" s="249"/>
+      <c r="C11" s="252"/>
+      <c r="D11" s="252"/>
+      <c r="E11" s="252"/>
+      <c r="F11" s="252"/>
+      <c r="G11" s="252"/>
+      <c r="H11" s="252"/>
+      <c r="I11" s="262"/>
+      <c r="J11" s="262"/>
+      <c r="K11" s="262"/>
+      <c r="L11" s="262"/>
       <c r="M11" s="4" t="s">
         <v>34</v>
       </c>
@@ -3305,20 +3305,20 @@
       <c r="T11" s="188" t="s">
         <v>35</v>
       </c>
-      <c r="U11" s="287" t="s">
+      <c r="U11" s="278" t="s">
         <v>36</v>
       </c>
-      <c r="V11" s="287"/>
-      <c r="Y11" s="221"/>
-      <c r="Z11" s="224"/>
+      <c r="V11" s="278"/>
+      <c r="Y11" s="268"/>
+      <c r="Z11" s="271"/>
       <c r="AA11" s="101"/>
-      <c r="AB11" s="212"/>
-      <c r="AC11" s="227"/>
-      <c r="AD11" s="230"/>
-      <c r="AE11" s="212"/>
-      <c r="AG11" s="211"/>
+      <c r="AB11" s="259"/>
+      <c r="AC11" s="274"/>
+      <c r="AD11" s="277"/>
+      <c r="AE11" s="259"/>
+      <c r="AG11" s="258"/>
       <c r="AH11" s="101"/>
-      <c r="AI11" s="212"/>
+      <c r="AI11" s="259"/>
     </row>
     <row r="12" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="103" t="s">
@@ -3348,8 +3348,8 @@
       <c r="Q12" s="13"/>
       <c r="S12" s="14"/>
       <c r="T12" s="189"/>
-      <c r="U12" s="284"/>
-      <c r="V12" s="284"/>
+      <c r="U12" s="282"/>
+      <c r="V12" s="282"/>
       <c r="Y12" s="105">
         <f>F12*C12</f>
         <v>0</v>
@@ -3412,8 +3412,8 @@
       <c r="Q13" s="22"/>
       <c r="S13" s="23"/>
       <c r="T13" s="23"/>
-      <c r="U13" s="279"/>
-      <c r="V13" s="279"/>
+      <c r="U13" s="283"/>
+      <c r="V13" s="283"/>
       <c r="Y13" s="115">
         <f t="shared" ref="Y13:Y70" si="3">F13*C13</f>
         <v>0</v>
@@ -3476,8 +3476,8 @@
       <c r="Q14" s="22"/>
       <c r="S14" s="23"/>
       <c r="T14" s="23"/>
-      <c r="U14" s="279"/>
-      <c r="V14" s="279"/>
+      <c r="U14" s="283"/>
+      <c r="V14" s="283"/>
       <c r="Y14" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3540,8 +3540,8 @@
       <c r="Q15" s="22"/>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
-      <c r="U15" s="280"/>
-      <c r="V15" s="280"/>
+      <c r="U15" s="289"/>
+      <c r="V15" s="289"/>
       <c r="Y15" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3604,8 +3604,8 @@
       <c r="Q16" s="22"/>
       <c r="S16" s="23"/>
       <c r="T16" s="26"/>
-      <c r="U16" s="282"/>
-      <c r="V16" s="282"/>
+      <c r="U16" s="291"/>
+      <c r="V16" s="291"/>
       <c r="Y16" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3668,8 +3668,8 @@
       <c r="Q17" s="22"/>
       <c r="S17" s="23"/>
       <c r="T17" s="26"/>
-      <c r="U17" s="282"/>
-      <c r="V17" s="282"/>
+      <c r="U17" s="291"/>
+      <c r="V17" s="291"/>
       <c r="Y17" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3732,8 +3732,8 @@
       <c r="Q18" s="33"/>
       <c r="S18" s="34"/>
       <c r="T18" s="35"/>
-      <c r="U18" s="286"/>
-      <c r="V18" s="286"/>
+      <c r="U18" s="290"/>
+      <c r="V18" s="290"/>
       <c r="Y18" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3796,8 +3796,8 @@
       <c r="Q19" s="22"/>
       <c r="S19" s="23"/>
       <c r="T19" s="26"/>
-      <c r="U19" s="280"/>
-      <c r="V19" s="280"/>
+      <c r="U19" s="289"/>
+      <c r="V19" s="289"/>
       <c r="Y19" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3860,8 +3860,8 @@
       <c r="Q20" s="33"/>
       <c r="S20" s="34"/>
       <c r="T20" s="35"/>
-      <c r="U20" s="286"/>
-      <c r="V20" s="286"/>
+      <c r="U20" s="290"/>
+      <c r="V20" s="290"/>
       <c r="Y20" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3924,8 +3924,8 @@
       <c r="Q21" s="42"/>
       <c r="S21" s="43"/>
       <c r="T21" s="44"/>
-      <c r="U21" s="280"/>
-      <c r="V21" s="280"/>
+      <c r="U21" s="289"/>
+      <c r="V21" s="289"/>
       <c r="Y21" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3988,8 +3988,8 @@
       <c r="Q22" s="22"/>
       <c r="S22" s="23"/>
       <c r="T22" s="26"/>
-      <c r="U22" s="282"/>
-      <c r="V22" s="282"/>
+      <c r="U22" s="291"/>
+      <c r="V22" s="291"/>
       <c r="Y22" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4052,8 +4052,8 @@
       <c r="Q23" s="22"/>
       <c r="S23" s="23"/>
       <c r="T23" s="26"/>
-      <c r="U23" s="279"/>
-      <c r="V23" s="279"/>
+      <c r="U23" s="283"/>
+      <c r="V23" s="283"/>
       <c r="Y23" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4116,8 +4116,8 @@
       <c r="Q24" s="33"/>
       <c r="S24" s="34"/>
       <c r="T24" s="35"/>
-      <c r="U24" s="282"/>
-      <c r="V24" s="282"/>
+      <c r="U24" s="291"/>
+      <c r="V24" s="291"/>
       <c r="Y24" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4180,8 +4180,8 @@
       <c r="Q25" s="42"/>
       <c r="S25" s="43"/>
       <c r="T25" s="44"/>
-      <c r="U25" s="285"/>
-      <c r="V25" s="285"/>
+      <c r="U25" s="292"/>
+      <c r="V25" s="292"/>
       <c r="Y25" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4244,8 +4244,8 @@
       <c r="Q26" s="33"/>
       <c r="S26" s="34"/>
       <c r="T26" s="35"/>
-      <c r="U26" s="280"/>
-      <c r="V26" s="280"/>
+      <c r="U26" s="289"/>
+      <c r="V26" s="289"/>
       <c r="Y26" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4308,8 +4308,8 @@
       <c r="Q27" s="42"/>
       <c r="S27" s="43"/>
       <c r="T27" s="44"/>
-      <c r="U27" s="285"/>
-      <c r="V27" s="285"/>
+      <c r="U27" s="292"/>
+      <c r="V27" s="292"/>
       <c r="Y27" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4372,8 +4372,8 @@
       <c r="Q28" s="22"/>
       <c r="S28" s="23"/>
       <c r="T28" s="26"/>
-      <c r="U28" s="280"/>
-      <c r="V28" s="280"/>
+      <c r="U28" s="289"/>
+      <c r="V28" s="289"/>
       <c r="Y28" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4434,8 +4434,8 @@
       <c r="Q29" s="22"/>
       <c r="S29" s="23"/>
       <c r="T29" s="26"/>
-      <c r="U29" s="279"/>
-      <c r="V29" s="279"/>
+      <c r="U29" s="283"/>
+      <c r="V29" s="283"/>
       <c r="Y29" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4496,8 +4496,8 @@
       <c r="Q30" s="22"/>
       <c r="S30" s="26"/>
       <c r="T30" s="26"/>
-      <c r="U30" s="282"/>
-      <c r="V30" s="282"/>
+      <c r="U30" s="291"/>
+      <c r="V30" s="291"/>
       <c r="Y30" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4558,8 +4558,8 @@
       <c r="Q31" s="22"/>
       <c r="S31" s="26"/>
       <c r="T31" s="26"/>
-      <c r="U31" s="279"/>
-      <c r="V31" s="279"/>
+      <c r="U31" s="283"/>
+      <c r="V31" s="283"/>
       <c r="Y31" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4615,8 +4615,8 @@
       <c r="Q32" s="22"/>
       <c r="S32" s="26"/>
       <c r="T32" s="26"/>
-      <c r="U32" s="279"/>
-      <c r="V32" s="279"/>
+      <c r="U32" s="283"/>
+      <c r="V32" s="283"/>
       <c r="Y32" s="115"/>
       <c r="Z32" s="116"/>
       <c r="AA32" s="107"/>
@@ -4655,8 +4655,8 @@
       <c r="Q33" s="22"/>
       <c r="S33" s="26"/>
       <c r="T33" s="26"/>
-      <c r="U33" s="279"/>
-      <c r="V33" s="279"/>
+      <c r="U33" s="283"/>
+      <c r="V33" s="283"/>
       <c r="Y33" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4717,8 +4717,8 @@
       <c r="Q34" s="22"/>
       <c r="S34" s="26"/>
       <c r="T34" s="26"/>
-      <c r="U34" s="279"/>
-      <c r="V34" s="279"/>
+      <c r="U34" s="283"/>
+      <c r="V34" s="283"/>
       <c r="Y34" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4779,8 +4779,8 @@
       <c r="Q35" s="33"/>
       <c r="S35" s="35"/>
       <c r="T35" s="35"/>
-      <c r="U35" s="280"/>
-      <c r="V35" s="280"/>
+      <c r="U35" s="289"/>
+      <c r="V35" s="289"/>
       <c r="Y35" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4841,8 +4841,8 @@
       <c r="Q36" s="42"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
-      <c r="U36" s="285"/>
-      <c r="V36" s="285"/>
+      <c r="U36" s="292"/>
+      <c r="V36" s="292"/>
       <c r="Y36" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4903,8 +4903,8 @@
       <c r="Q37" s="22"/>
       <c r="S37" s="26"/>
       <c r="T37" s="26"/>
-      <c r="U37" s="280"/>
-      <c r="V37" s="280"/>
+      <c r="U37" s="289"/>
+      <c r="V37" s="289"/>
       <c r="Y37" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4965,8 +4965,8 @@
       <c r="Q38" s="33"/>
       <c r="S38" s="35"/>
       <c r="T38" s="35"/>
-      <c r="U38" s="286"/>
-      <c r="V38" s="286"/>
+      <c r="U38" s="290"/>
+      <c r="V38" s="290"/>
       <c r="Y38" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5027,8 +5027,8 @@
       <c r="Q39" s="42"/>
       <c r="S39" s="44"/>
       <c r="T39" s="44"/>
-      <c r="U39" s="280"/>
-      <c r="V39" s="280"/>
+      <c r="U39" s="289"/>
+      <c r="V39" s="289"/>
       <c r="Y39" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5089,8 +5089,8 @@
       <c r="Q40" s="22"/>
       <c r="S40" s="26"/>
       <c r="T40" s="26"/>
-      <c r="U40" s="282"/>
-      <c r="V40" s="282"/>
+      <c r="U40" s="291"/>
+      <c r="V40" s="291"/>
       <c r="Y40" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5151,8 +5151,8 @@
       <c r="Q41" s="22"/>
       <c r="S41" s="26"/>
       <c r="T41" s="26"/>
-      <c r="U41" s="282"/>
-      <c r="V41" s="282"/>
+      <c r="U41" s="291"/>
+      <c r="V41" s="291"/>
       <c r="Y41" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5208,8 +5208,8 @@
       <c r="Q42" s="33"/>
       <c r="S42" s="35"/>
       <c r="T42" s="35"/>
-      <c r="U42" s="286"/>
-      <c r="V42" s="286"/>
+      <c r="U42" s="290"/>
+      <c r="V42" s="290"/>
       <c r="Y42" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5263,8 +5263,8 @@
       <c r="Q43" s="22"/>
       <c r="S43" s="23"/>
       <c r="T43" s="26"/>
-      <c r="U43" s="283"/>
-      <c r="V43" s="283"/>
+      <c r="U43" s="293"/>
+      <c r="V43" s="293"/>
       <c r="Y43" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5315,8 +5315,8 @@
       <c r="Q44" s="22"/>
       <c r="S44" s="23"/>
       <c r="T44" s="26"/>
-      <c r="U44" s="277"/>
-      <c r="V44" s="277"/>
+      <c r="U44" s="294"/>
+      <c r="V44" s="294"/>
       <c r="Y44" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5367,8 +5367,8 @@
       <c r="Q45" s="33"/>
       <c r="S45" s="34"/>
       <c r="T45" s="35"/>
-      <c r="U45" s="284"/>
-      <c r="V45" s="284"/>
+      <c r="U45" s="282"/>
+      <c r="V45" s="282"/>
       <c r="Y45" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5416,8 +5416,8 @@
       <c r="Q46" s="174"/>
       <c r="S46" s="171"/>
       <c r="T46" s="172"/>
-      <c r="U46" s="285"/>
-      <c r="V46" s="285"/>
+      <c r="U46" s="292"/>
+      <c r="V46" s="292"/>
       <c r="Y46" s="115"/>
       <c r="Z46" s="116"/>
       <c r="AA46" s="107"/>
@@ -5458,8 +5458,8 @@
       <c r="Q47" s="22"/>
       <c r="S47" s="23"/>
       <c r="T47" s="26"/>
-      <c r="U47" s="279"/>
-      <c r="V47" s="279"/>
+      <c r="U47" s="283"/>
+      <c r="V47" s="283"/>
       <c r="Y47" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5520,8 +5520,8 @@
       <c r="Q48" s="22"/>
       <c r="S48" s="26"/>
       <c r="T48" s="26"/>
-      <c r="U48" s="279"/>
-      <c r="V48" s="279"/>
+      <c r="U48" s="283"/>
+      <c r="V48" s="283"/>
       <c r="Y48" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5584,8 +5584,8 @@
       <c r="Q49" s="22"/>
       <c r="S49" s="23"/>
       <c r="T49" s="26"/>
-      <c r="U49" s="279"/>
-      <c r="V49" s="279"/>
+      <c r="U49" s="283"/>
+      <c r="V49" s="283"/>
       <c r="Y49" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5648,8 +5648,8 @@
       <c r="Q50" s="57"/>
       <c r="S50" s="58"/>
       <c r="T50" s="58"/>
-      <c r="U50" s="283"/>
-      <c r="V50" s="283"/>
+      <c r="U50" s="293"/>
+      <c r="V50" s="293"/>
       <c r="Y50" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5708,8 +5708,8 @@
       <c r="Q51" s="42"/>
       <c r="S51" s="44"/>
       <c r="T51" s="44"/>
-      <c r="U51" s="277"/>
-      <c r="V51" s="277"/>
+      <c r="U51" s="294"/>
+      <c r="V51" s="294"/>
       <c r="Y51" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5768,8 +5768,8 @@
       <c r="Q52" s="22"/>
       <c r="S52" s="23"/>
       <c r="T52" s="23"/>
-      <c r="U52" s="284"/>
-      <c r="V52" s="284"/>
+      <c r="U52" s="282"/>
+      <c r="V52" s="282"/>
       <c r="Y52" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5822,8 +5822,8 @@
       <c r="Q53" s="22"/>
       <c r="S53" s="23"/>
       <c r="T53" s="23"/>
-      <c r="U53" s="282"/>
-      <c r="V53" s="282"/>
+      <c r="U53" s="291"/>
+      <c r="V53" s="291"/>
       <c r="Y53" s="115"/>
       <c r="Z53" s="116"/>
       <c r="AA53" s="107"/>
@@ -5857,8 +5857,8 @@
       <c r="Q54" s="22"/>
       <c r="S54" s="23"/>
       <c r="T54" s="23"/>
-      <c r="U54" s="282"/>
-      <c r="V54" s="282"/>
+      <c r="U54" s="291"/>
+      <c r="V54" s="291"/>
       <c r="Y54" s="115"/>
       <c r="Z54" s="116"/>
       <c r="AA54" s="107"/>
@@ -5892,8 +5892,8 @@
       <c r="Q55" s="22"/>
       <c r="S55" s="23"/>
       <c r="T55" s="23"/>
-      <c r="U55" s="279"/>
-      <c r="V55" s="279"/>
+      <c r="U55" s="283"/>
+      <c r="V55" s="283"/>
       <c r="Y55" s="115"/>
       <c r="Z55" s="116"/>
       <c r="AA55" s="107"/>
@@ -5934,8 +5934,8 @@
       <c r="Q56" s="22"/>
       <c r="S56" s="23"/>
       <c r="T56" s="26"/>
-      <c r="U56" s="280"/>
-      <c r="V56" s="280"/>
+      <c r="U56" s="289"/>
+      <c r="V56" s="289"/>
       <c r="Y56" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5988,8 +5988,8 @@
       <c r="Q57" s="22"/>
       <c r="S57" s="23"/>
       <c r="T57" s="26"/>
-      <c r="U57" s="282"/>
-      <c r="V57" s="282"/>
+      <c r="U57" s="291"/>
+      <c r="V57" s="291"/>
       <c r="Y57" s="115"/>
       <c r="Z57" s="116"/>
       <c r="AA57" s="107"/>
@@ -6023,8 +6023,8 @@
       <c r="Q58" s="22"/>
       <c r="S58" s="23"/>
       <c r="T58" s="26"/>
-      <c r="U58" s="282"/>
-      <c r="V58" s="282"/>
+      <c r="U58" s="291"/>
+      <c r="V58" s="291"/>
       <c r="Y58" s="115"/>
       <c r="Z58" s="116"/>
       <c r="AA58" s="107"/>
@@ -6058,8 +6058,8 @@
       <c r="Q59" s="22"/>
       <c r="S59" s="23"/>
       <c r="T59" s="26"/>
-      <c r="U59" s="279"/>
-      <c r="V59" s="279"/>
+      <c r="U59" s="283"/>
+      <c r="V59" s="283"/>
       <c r="Y59" s="115"/>
       <c r="Z59" s="116"/>
       <c r="AA59" s="107"/>
@@ -6091,8 +6091,8 @@
       <c r="Q60" s="22"/>
       <c r="S60" s="23"/>
       <c r="T60" s="26"/>
-      <c r="U60" s="280"/>
-      <c r="V60" s="280"/>
+      <c r="U60" s="289"/>
+      <c r="V60" s="289"/>
       <c r="Y60" s="115"/>
       <c r="Z60" s="116"/>
       <c r="AA60" s="107"/>
@@ -6131,8 +6131,8 @@
       <c r="Q61" s="22"/>
       <c r="S61" s="180"/>
       <c r="T61" s="59"/>
-      <c r="U61" s="281"/>
-      <c r="V61" s="281"/>
+      <c r="U61" s="295"/>
+      <c r="V61" s="295"/>
       <c r="Y61" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6192,8 +6192,8 @@
       <c r="Q62" s="22"/>
       <c r="S62" s="43"/>
       <c r="T62" s="44"/>
-      <c r="U62" s="277"/>
-      <c r="V62" s="277"/>
+      <c r="U62" s="294"/>
+      <c r="V62" s="294"/>
       <c r="Y62" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6252,8 +6252,8 @@
       <c r="Q63" s="33"/>
       <c r="S63" s="34"/>
       <c r="T63" s="35"/>
-      <c r="U63" s="277"/>
-      <c r="V63" s="277"/>
+      <c r="U63" s="294"/>
+      <c r="V63" s="294"/>
       <c r="Y63" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6311,8 +6311,8 @@
       <c r="Q64" s="42"/>
       <c r="S64" s="44"/>
       <c r="T64" s="44"/>
-      <c r="U64" s="277"/>
-      <c r="V64" s="277"/>
+      <c r="U64" s="294"/>
+      <c r="V64" s="294"/>
       <c r="Y64" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6373,8 +6373,8 @@
       <c r="Q65" s="22"/>
       <c r="S65" s="26"/>
       <c r="T65" s="26"/>
-      <c r="U65" s="277"/>
-      <c r="V65" s="277"/>
+      <c r="U65" s="294"/>
+      <c r="V65" s="294"/>
       <c r="Y65" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6435,8 +6435,8 @@
       <c r="Q66" s="22"/>
       <c r="S66" s="26"/>
       <c r="T66" s="26"/>
-      <c r="U66" s="277"/>
-      <c r="V66" s="277"/>
+      <c r="U66" s="294"/>
+      <c r="V66" s="294"/>
       <c r="Y66" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6497,8 +6497,8 @@
       <c r="Q67" s="22"/>
       <c r="S67" s="26"/>
       <c r="T67" s="26"/>
-      <c r="U67" s="277"/>
-      <c r="V67" s="277"/>
+      <c r="U67" s="294"/>
+      <c r="V67" s="294"/>
       <c r="Y67" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6559,8 +6559,8 @@
       <c r="Q68" s="22"/>
       <c r="S68" s="26"/>
       <c r="T68" s="26"/>
-      <c r="U68" s="277"/>
-      <c r="V68" s="277"/>
+      <c r="U68" s="294"/>
+      <c r="V68" s="294"/>
       <c r="Y68" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6621,8 +6621,8 @@
       <c r="Q69" s="22"/>
       <c r="S69" s="26"/>
       <c r="T69" s="26"/>
-      <c r="U69" s="277"/>
-      <c r="V69" s="277"/>
+      <c r="U69" s="294"/>
+      <c r="V69" s="294"/>
       <c r="Y69" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6683,8 +6683,8 @@
       <c r="Q70" s="57"/>
       <c r="S70" s="58"/>
       <c r="T70" s="58"/>
-      <c r="U70" s="277"/>
-      <c r="V70" s="277"/>
+      <c r="U70" s="294"/>
+      <c r="V70" s="294"/>
       <c r="Y70" s="131">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6761,8 +6761,8 @@
       </c>
       <c r="S71" s="64"/>
       <c r="T71" s="64"/>
-      <c r="U71" s="277"/>
-      <c r="V71" s="277"/>
+      <c r="U71" s="294"/>
+      <c r="V71" s="294"/>
       <c r="AB71" s="102">
         <v>0.61</v>
       </c>
@@ -6809,21 +6809,21 @@
       </c>
       <c r="S72" s="70"/>
       <c r="T72" s="70"/>
-      <c r="U72" s="277"/>
-      <c r="V72" s="277"/>
+      <c r="U72" s="294"/>
+      <c r="V72" s="294"/>
       <c r="AB72" s="102">
         <v>0.61</v>
       </c>
     </row>
     <row r="73" spans="2:35" s="102" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B73" s="231" t="s">
+      <c r="B73" s="232" t="s">
         <v>55</v>
       </c>
-      <c r="C73" s="231"/>
-      <c r="D73" s="231"/>
-      <c r="E73" s="231"/>
-      <c r="F73" s="231"/>
-      <c r="G73" s="231"/>
+      <c r="C73" s="232"/>
+      <c r="D73" s="232"/>
+      <c r="E73" s="232"/>
+      <c r="F73" s="232"/>
+      <c r="G73" s="232"/>
       <c r="H73" s="72" t="str">
         <f>ROUND(((F12+F27+F51+F52+F56+F61+F62+F63)/72+(F13+F16+F17)/108+(F14+SUM(F18:F26)+F28+F29+F47+F49+F41)/63+F15/96+SUM(F30:F40)/100+SUM(F43:F45)/24+SUM(F64:F70)/100+(F50+F42+F48)/100),1)&amp;" pallets"</f>
         <v>0 pallets</v>
@@ -6899,27 +6899,27 @@
       <c r="C75" s="142"/>
       <c r="D75" s="142"/>
       <c r="E75" s="142"/>
-      <c r="F75" s="232"/>
-      <c r="G75" s="232"/>
-      <c r="H75" s="232"/>
-      <c r="I75" s="233"/>
+      <c r="F75" s="233"/>
+      <c r="G75" s="233"/>
+      <c r="H75" s="233"/>
+      <c r="I75" s="234"/>
       <c r="J75" s="77"/>
       <c r="K75" s="77"/>
       <c r="L75" s="77"/>
-      <c r="M75" s="234" t="s">
+      <c r="M75" s="235" t="s">
         <v>57</v>
       </c>
-      <c r="N75" s="235"/>
-      <c r="O75" s="232"/>
-      <c r="P75" s="232"/>
-      <c r="Q75" s="233"/>
+      <c r="N75" s="236"/>
+      <c r="O75" s="233"/>
+      <c r="P75" s="233"/>
+      <c r="Q75" s="234"/>
       <c r="R75" s="139"/>
-      <c r="S75" s="278" t="s">
+      <c r="S75" s="244" t="s">
         <v>58</v>
       </c>
-      <c r="T75" s="278"/>
-      <c r="U75" s="278"/>
-      <c r="V75" s="278"/>
+      <c r="T75" s="244"/>
+      <c r="U75" s="244"/>
+      <c r="V75" s="244"/>
       <c r="W75" s="78"/>
       <c r="X75" s="78"/>
       <c r="Y75" s="78"/>
@@ -6974,31 +6974,31 @@
       <c r="C77" s="142"/>
       <c r="D77" s="142"/>
       <c r="E77" s="142"/>
-      <c r="F77" s="232"/>
-      <c r="G77" s="232"/>
-      <c r="H77" s="232"/>
-      <c r="I77" s="233"/>
+      <c r="F77" s="233"/>
+      <c r="G77" s="233"/>
+      <c r="H77" s="233"/>
+      <c r="I77" s="234"/>
       <c r="J77" s="80"/>
       <c r="K77" s="80"/>
       <c r="L77" s="80"/>
-      <c r="M77" s="239" t="s">
+      <c r="M77" s="243" t="s">
         <v>60</v>
       </c>
-      <c r="N77" s="239"/>
+      <c r="N77" s="243"/>
       <c r="O77" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="P77" s="238"/>
-      <c r="Q77" s="233"/>
+      <c r="P77" s="242"/>
+      <c r="Q77" s="234"/>
       <c r="R77" s="139"/>
-      <c r="S77" s="278" t="s">
+      <c r="S77" s="244" t="s">
         <v>62</v>
       </c>
-      <c r="T77" s="278"/>
-      <c r="U77" s="278"/>
-      <c r="V77" s="278"/>
+      <c r="T77" s="244"/>
+      <c r="U77" s="244"/>
+      <c r="V77" s="244"/>
       <c r="W77" s="78"/>
-      <c r="X77" s="197" t="s">
+      <c r="X77" s="237" t="s">
         <v>63</v>
       </c>
       <c r="Y77" s="78"/>
@@ -7033,7 +7033,7 @@
       <c r="U78" s="81"/>
       <c r="V78" s="81"/>
       <c r="W78" s="78"/>
-      <c r="X78" s="198"/>
+      <c r="X78" s="238"/>
       <c r="Y78" s="78"/>
       <c r="Z78" s="78"/>
       <c r="AA78" s="78"/>
@@ -7053,35 +7053,35 @@
       <c r="C79" s="142"/>
       <c r="D79" s="142"/>
       <c r="E79" s="142"/>
-      <c r="F79" s="232" t="str">
+      <c r="F79" s="233" t="str">
         <f>IF(U6&gt;0,"",F75-T79)</f>
         <v/>
       </c>
-      <c r="G79" s="232"/>
-      <c r="H79" s="232"/>
-      <c r="I79" s="233"/>
+      <c r="G79" s="233"/>
+      <c r="H79" s="233"/>
+      <c r="I79" s="234"/>
       <c r="J79" s="80"/>
       <c r="K79" s="80"/>
       <c r="L79" s="80"/>
-      <c r="M79" s="236" t="str">
+      <c r="M79" s="240" t="str">
         <f>IF(U6&gt;0,"",T4+30)</f>
         <v/>
       </c>
-      <c r="N79" s="237"/>
+      <c r="N79" s="241"/>
       <c r="O79" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="P79" s="238"/>
-      <c r="Q79" s="233"/>
+      <c r="P79" s="242"/>
+      <c r="Q79" s="234"/>
       <c r="R79" s="139"/>
-      <c r="S79" s="293" t="s">
+      <c r="S79" s="245" t="s">
         <v>66</v>
       </c>
-      <c r="T79" s="294"/>
-      <c r="U79" s="294"/>
-      <c r="V79" s="294"/>
+      <c r="T79" s="246"/>
+      <c r="U79" s="246"/>
+      <c r="V79" s="246"/>
       <c r="W79" s="78"/>
-      <c r="X79" s="199"/>
+      <c r="X79" s="239"/>
       <c r="Y79" s="78"/>
       <c r="Z79" s="78"/>
       <c r="AA79" s="78"/>
@@ -7131,83 +7131,83 @@
       <c r="AI80" s="78"/>
     </row>
     <row r="81" spans="2:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="252" t="s">
+      <c r="B81" s="212" t="s">
         <v>67</v>
       </c>
-      <c r="C81" s="253"/>
-      <c r="D81" s="253"/>
-      <c r="E81" s="253"/>
-      <c r="F81" s="253"/>
-      <c r="G81" s="253"/>
-      <c r="H81" s="254"/>
-      <c r="I81" s="261" t="s">
+      <c r="C81" s="213"/>
+      <c r="D81" s="213"/>
+      <c r="E81" s="213"/>
+      <c r="F81" s="213"/>
+      <c r="G81" s="213"/>
+      <c r="H81" s="214"/>
+      <c r="I81" s="221" t="s">
         <v>68</v>
       </c>
       <c r="J81" s="148"/>
       <c r="K81" s="148"/>
       <c r="L81" s="148"/>
-      <c r="M81" s="264"/>
-      <c r="N81" s="267" t="s">
+      <c r="M81" s="223"/>
+      <c r="N81" s="226" t="s">
         <v>69</v>
       </c>
-      <c r="O81" s="270"/>
-      <c r="P81" s="264"/>
-      <c r="Q81" s="240" t="s">
+      <c r="O81" s="229"/>
+      <c r="P81" s="223"/>
+      <c r="Q81" s="203" t="s">
         <v>70</v>
       </c>
-      <c r="R81" s="241"/>
-      <c r="S81" s="246"/>
-      <c r="T81" s="240" t="s">
+      <c r="R81" s="204"/>
+      <c r="S81" s="209"/>
+      <c r="T81" s="203" t="s">
         <v>71</v>
       </c>
-      <c r="U81" s="291"/>
-      <c r="V81" s="291"/>
+      <c r="U81" s="193"/>
+      <c r="V81" s="193"/>
     </row>
     <row r="82" spans="2:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="255"/>
-      <c r="C82" s="256"/>
-      <c r="D82" s="256"/>
-      <c r="E82" s="256"/>
-      <c r="F82" s="256"/>
-      <c r="G82" s="256"/>
-      <c r="H82" s="257"/>
-      <c r="I82" s="262"/>
+      <c r="B82" s="215"/>
+      <c r="C82" s="216"/>
+      <c r="D82" s="216"/>
+      <c r="E82" s="216"/>
+      <c r="F82" s="216"/>
+      <c r="G82" s="216"/>
+      <c r="H82" s="217"/>
+      <c r="I82" s="197"/>
       <c r="J82" s="91"/>
       <c r="K82" s="91"/>
       <c r="L82" s="91"/>
-      <c r="M82" s="265"/>
-      <c r="N82" s="268"/>
-      <c r="O82" s="271"/>
-      <c r="P82" s="265"/>
-      <c r="Q82" s="242"/>
-      <c r="R82" s="243"/>
-      <c r="S82" s="247"/>
-      <c r="T82" s="242"/>
-      <c r="U82" s="291"/>
-      <c r="V82" s="291"/>
+      <c r="M82" s="224"/>
+      <c r="N82" s="227"/>
+      <c r="O82" s="230"/>
+      <c r="P82" s="224"/>
+      <c r="Q82" s="205"/>
+      <c r="R82" s="206"/>
+      <c r="S82" s="210"/>
+      <c r="T82" s="205"/>
+      <c r="U82" s="193"/>
+      <c r="V82" s="193"/>
     </row>
     <row r="83" spans="2:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="258"/>
-      <c r="C83" s="259"/>
-      <c r="D83" s="259"/>
-      <c r="E83" s="259"/>
-      <c r="F83" s="259"/>
-      <c r="G83" s="259"/>
-      <c r="H83" s="260"/>
-      <c r="I83" s="263"/>
+      <c r="B83" s="218"/>
+      <c r="C83" s="219"/>
+      <c r="D83" s="219"/>
+      <c r="E83" s="219"/>
+      <c r="F83" s="219"/>
+      <c r="G83" s="219"/>
+      <c r="H83" s="220"/>
+      <c r="I83" s="222"/>
       <c r="J83" s="149"/>
       <c r="K83" s="149"/>
       <c r="L83" s="149"/>
-      <c r="M83" s="266"/>
-      <c r="N83" s="269"/>
-      <c r="O83" s="272"/>
-      <c r="P83" s="266"/>
-      <c r="Q83" s="244"/>
-      <c r="R83" s="245"/>
-      <c r="S83" s="248"/>
-      <c r="T83" s="244"/>
-      <c r="U83" s="291"/>
-      <c r="V83" s="291"/>
+      <c r="M83" s="225"/>
+      <c r="N83" s="228"/>
+      <c r="O83" s="231"/>
+      <c r="P83" s="225"/>
+      <c r="Q83" s="207"/>
+      <c r="R83" s="208"/>
+      <c r="S83" s="211"/>
+      <c r="T83" s="207"/>
+      <c r="U83" s="193"/>
+      <c r="V83" s="193"/>
     </row>
     <row r="84" spans="2:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="V84" s="190"/>
@@ -7269,22 +7269,22 @@
       <c r="V87" s="157"/>
     </row>
     <row r="88" spans="2:23" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B88" s="249"/>
-      <c r="C88" s="250"/>
-      <c r="D88" s="250"/>
-      <c r="E88" s="250"/>
-      <c r="F88" s="250"/>
-      <c r="G88" s="250"/>
-      <c r="H88" s="250"/>
-      <c r="I88" s="251"/>
+      <c r="B88" s="200"/>
+      <c r="C88" s="201"/>
+      <c r="D88" s="201"/>
+      <c r="E88" s="201"/>
+      <c r="F88" s="201"/>
+      <c r="G88" s="201"/>
+      <c r="H88" s="201"/>
+      <c r="I88" s="202"/>
       <c r="J88" s="88"/>
       <c r="K88" s="88"/>
       <c r="L88" s="88"/>
-      <c r="M88" s="249"/>
-      <c r="N88" s="250"/>
-      <c r="O88" s="250"/>
-      <c r="P88" s="250"/>
-      <c r="Q88" s="251"/>
+      <c r="M88" s="200"/>
+      <c r="N88" s="201"/>
+      <c r="O88" s="201"/>
+      <c r="P88" s="201"/>
+      <c r="Q88" s="202"/>
       <c r="R88" s="158"/>
       <c r="S88" s="159"/>
       <c r="T88" s="159"/>
@@ -7293,29 +7293,29 @@
       <c r="W88" s="155"/>
     </row>
     <row r="89" spans="2:23" ht="18" x14ac:dyDescent="0.25">
-      <c r="B89" s="273" t="s">
+      <c r="B89" s="194" t="s">
         <v>76</v>
       </c>
-      <c r="C89" s="274"/>
-      <c r="D89" s="274"/>
-      <c r="E89" s="274"/>
-      <c r="F89" s="274"/>
-      <c r="G89" s="274"/>
-      <c r="H89" s="274"/>
-      <c r="I89" s="275"/>
-      <c r="M89" s="273" t="s">
+      <c r="C89" s="195"/>
+      <c r="D89" s="195"/>
+      <c r="E89" s="195"/>
+      <c r="F89" s="195"/>
+      <c r="G89" s="195"/>
+      <c r="H89" s="195"/>
+      <c r="I89" s="196"/>
+      <c r="M89" s="194" t="s">
         <v>76</v>
       </c>
-      <c r="N89" s="274"/>
-      <c r="O89" s="274"/>
-      <c r="P89" s="274"/>
-      <c r="Q89" s="275"/>
-      <c r="R89" s="262" t="s">
+      <c r="N89" s="195"/>
+      <c r="O89" s="195"/>
+      <c r="P89" s="195"/>
+      <c r="Q89" s="196"/>
+      <c r="R89" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="S89" s="276"/>
-      <c r="T89" s="276"/>
-      <c r="U89" s="295"/>
+      <c r="S89" s="198"/>
+      <c r="T89" s="198"/>
+      <c r="U89" s="199"/>
       <c r="V89" s="192"/>
       <c r="W89" s="153"/>
     </row>
@@ -7356,16 +7356,16 @@
       <c r="V92" s="154"/>
     </row>
     <row r="93" spans="2:23" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B93" s="249" t="s">
+      <c r="B93" s="200" t="s">
         <v>87</v>
       </c>
-      <c r="C93" s="250"/>
-      <c r="D93" s="250"/>
-      <c r="E93" s="250"/>
-      <c r="F93" s="250"/>
-      <c r="G93" s="250"/>
-      <c r="H93" s="250"/>
-      <c r="I93" s="251"/>
+      <c r="C93" s="201"/>
+      <c r="D93" s="201"/>
+      <c r="E93" s="201"/>
+      <c r="F93" s="201"/>
+      <c r="G93" s="201"/>
+      <c r="H93" s="201"/>
+      <c r="I93" s="202"/>
       <c r="J93" s="88"/>
       <c r="K93" s="88"/>
       <c r="L93" s="88"/>
@@ -7384,24 +7384,24 @@
       <c r="W93" s="155"/>
     </row>
     <row r="94" spans="2:23" ht="18" x14ac:dyDescent="0.25">
-      <c r="B94" s="273" t="s">
+      <c r="B94" s="194" t="s">
         <v>80</v>
       </c>
-      <c r="C94" s="274"/>
-      <c r="D94" s="274"/>
-      <c r="E94" s="274"/>
-      <c r="F94" s="274"/>
-      <c r="G94" s="274"/>
-      <c r="H94" s="274"/>
-      <c r="I94" s="275"/>
+      <c r="C94" s="195"/>
+      <c r="D94" s="195"/>
+      <c r="E94" s="195"/>
+      <c r="F94" s="195"/>
+      <c r="G94" s="195"/>
+      <c r="H94" s="195"/>
+      <c r="I94" s="196"/>
       <c r="M94" s="153"/>
       <c r="Q94" s="86"/>
-      <c r="R94" s="262" t="s">
+      <c r="R94" s="197" t="s">
         <v>81</v>
       </c>
-      <c r="S94" s="276"/>
-      <c r="T94" s="276"/>
-      <c r="U94" s="295"/>
+      <c r="S94" s="198"/>
+      <c r="T94" s="198"/>
+      <c r="U94" s="199"/>
       <c r="V94" s="164"/>
     </row>
     <row r="95" spans="2:23" ht="12.75" x14ac:dyDescent="0.25">
@@ -7443,36 +7443,80 @@
     <row r="102" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="126">
-    <mergeCell ref="U81:V83"/>
-    <mergeCell ref="B89:I89"/>
-    <mergeCell ref="M89:Q89"/>
-    <mergeCell ref="R89:U89"/>
-    <mergeCell ref="B93:I93"/>
-    <mergeCell ref="B94:I94"/>
-    <mergeCell ref="R94:U94"/>
-    <mergeCell ref="Q81:R83"/>
-    <mergeCell ref="S81:S83"/>
-    <mergeCell ref="T81:T83"/>
-    <mergeCell ref="B88:I88"/>
-    <mergeCell ref="M88:Q88"/>
-    <mergeCell ref="B81:H83"/>
-    <mergeCell ref="I81:I83"/>
-    <mergeCell ref="M81:M83"/>
-    <mergeCell ref="N81:N83"/>
-    <mergeCell ref="O81:P83"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="F75:I75"/>
-    <mergeCell ref="M75:N75"/>
-    <mergeCell ref="O75:Q75"/>
-    <mergeCell ref="X77:X79"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="M79:N79"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="F77:I77"/>
-    <mergeCell ref="M77:N77"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="S77:V77"/>
-    <mergeCell ref="S79:V79"/>
+    <mergeCell ref="U69:V69"/>
+    <mergeCell ref="U70:V70"/>
+    <mergeCell ref="U71:V71"/>
+    <mergeCell ref="U72:V72"/>
+    <mergeCell ref="S75:V75"/>
+    <mergeCell ref="U64:V64"/>
+    <mergeCell ref="U65:V65"/>
+    <mergeCell ref="U66:V66"/>
+    <mergeCell ref="U67:V67"/>
+    <mergeCell ref="U68:V68"/>
+    <mergeCell ref="U59:V59"/>
+    <mergeCell ref="U60:V60"/>
+    <mergeCell ref="U61:V61"/>
+    <mergeCell ref="U62:V62"/>
+    <mergeCell ref="U63:V63"/>
+    <mergeCell ref="U54:V54"/>
+    <mergeCell ref="U55:V55"/>
+    <mergeCell ref="U56:V56"/>
+    <mergeCell ref="U57:V57"/>
+    <mergeCell ref="U58:V58"/>
+    <mergeCell ref="U49:V49"/>
+    <mergeCell ref="U50:V50"/>
+    <mergeCell ref="U51:V51"/>
+    <mergeCell ref="U52:V52"/>
+    <mergeCell ref="U53:V53"/>
+    <mergeCell ref="U44:V44"/>
+    <mergeCell ref="U45:V45"/>
+    <mergeCell ref="U46:V46"/>
+    <mergeCell ref="U47:V47"/>
+    <mergeCell ref="U48:V48"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="U41:V41"/>
+    <mergeCell ref="U42:V42"/>
+    <mergeCell ref="U43:V43"/>
+    <mergeCell ref="U34:V34"/>
+    <mergeCell ref="U35:V35"/>
+    <mergeCell ref="U36:V36"/>
+    <mergeCell ref="U37:V37"/>
+    <mergeCell ref="U38:V38"/>
+    <mergeCell ref="U29:V29"/>
+    <mergeCell ref="U30:V30"/>
+    <mergeCell ref="U31:V31"/>
+    <mergeCell ref="U32:V32"/>
+    <mergeCell ref="U33:V33"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="U21:V21"/>
+    <mergeCell ref="U22:V22"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="F2:S2"/>
+    <mergeCell ref="X2:X4"/>
+    <mergeCell ref="F4:M4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="F6:M6"/>
+    <mergeCell ref="X6:X7"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="S9:V9"/>
+    <mergeCell ref="S10:V10"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="D9:D11"/>
@@ -7495,83 +7539,39 @@
     <mergeCell ref="AD9:AD11"/>
     <mergeCell ref="AE9:AE11"/>
     <mergeCell ref="U11:V11"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="F2:S2"/>
-    <mergeCell ref="X2:X4"/>
-    <mergeCell ref="F4:M4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="F6:M6"/>
-    <mergeCell ref="X6:X7"/>
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="S9:V9"/>
-    <mergeCell ref="S10:V10"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="U21:V21"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="U29:V29"/>
-    <mergeCell ref="U30:V30"/>
-    <mergeCell ref="U31:V31"/>
-    <mergeCell ref="U32:V32"/>
-    <mergeCell ref="U33:V33"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="U39:V39"/>
-    <mergeCell ref="U40:V40"/>
-    <mergeCell ref="U41:V41"/>
-    <mergeCell ref="U42:V42"/>
-    <mergeCell ref="U43:V43"/>
-    <mergeCell ref="U34:V34"/>
-    <mergeCell ref="U35:V35"/>
-    <mergeCell ref="U36:V36"/>
-    <mergeCell ref="U37:V37"/>
-    <mergeCell ref="U38:V38"/>
-    <mergeCell ref="U49:V49"/>
-    <mergeCell ref="U50:V50"/>
-    <mergeCell ref="U51:V51"/>
-    <mergeCell ref="U52:V52"/>
-    <mergeCell ref="U53:V53"/>
-    <mergeCell ref="U44:V44"/>
-    <mergeCell ref="U45:V45"/>
-    <mergeCell ref="U46:V46"/>
-    <mergeCell ref="U47:V47"/>
-    <mergeCell ref="U48:V48"/>
-    <mergeCell ref="U59:V59"/>
-    <mergeCell ref="U60:V60"/>
-    <mergeCell ref="U61:V61"/>
-    <mergeCell ref="U62:V62"/>
-    <mergeCell ref="U63:V63"/>
-    <mergeCell ref="U54:V54"/>
-    <mergeCell ref="U55:V55"/>
-    <mergeCell ref="U56:V56"/>
-    <mergeCell ref="U57:V57"/>
-    <mergeCell ref="U58:V58"/>
-    <mergeCell ref="U69:V69"/>
-    <mergeCell ref="U70:V70"/>
-    <mergeCell ref="U71:V71"/>
-    <mergeCell ref="U72:V72"/>
-    <mergeCell ref="S75:V75"/>
-    <mergeCell ref="U64:V64"/>
-    <mergeCell ref="U65:V65"/>
-    <mergeCell ref="U66:V66"/>
-    <mergeCell ref="U67:V67"/>
-    <mergeCell ref="U68:V68"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="F75:I75"/>
+    <mergeCell ref="M75:N75"/>
+    <mergeCell ref="O75:Q75"/>
+    <mergeCell ref="X77:X79"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="M79:N79"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="F77:I77"/>
+    <mergeCell ref="M77:N77"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="S77:V77"/>
+    <mergeCell ref="S79:V79"/>
+    <mergeCell ref="U81:V83"/>
+    <mergeCell ref="B89:I89"/>
+    <mergeCell ref="M89:Q89"/>
+    <mergeCell ref="R89:U89"/>
+    <mergeCell ref="B93:I93"/>
+    <mergeCell ref="B94:I94"/>
+    <mergeCell ref="R94:U94"/>
+    <mergeCell ref="Q81:R83"/>
+    <mergeCell ref="S81:S83"/>
+    <mergeCell ref="T81:T83"/>
+    <mergeCell ref="B88:I88"/>
+    <mergeCell ref="M88:Q88"/>
+    <mergeCell ref="B81:H83"/>
+    <mergeCell ref="I81:I83"/>
+    <mergeCell ref="M81:M83"/>
+    <mergeCell ref="N81:N83"/>
+    <mergeCell ref="O81:P83"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.19685039370078741" right="0" top="0" bottom="0" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageMargins left="0.19685039370078741" right="0" top="0" bottom="0" header="0" footer="0.19685039370078741"/>
   <pageSetup scale="38" orientation="portrait" blackAndWhite="1" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/GBDS MARCH FILES 2026/Guillermo DOS 2 - Neilven.xlsx
+++ b/GBDS MARCH FILES 2026/Guillermo DOS 2 - Neilven.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE2BFF14-BE44-4065-9D50-64CBA4449AEB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A141150-A9BA-43D0-A05C-FBE4AD438B38}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="gbds NEW" sheetId="14" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'gbds NEW'!$A$1:$W$97</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'gbds NEW'!$A$1:$W$98</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="132">
   <si>
     <t>DEALER NAME:</t>
   </si>
@@ -446,6 +446,9 @@
   </si>
   <si>
     <t>SML500C</t>
+  </si>
+  <si>
+    <t>RETURN NO.</t>
   </si>
 </sst>
 </file>
@@ -643,7 +646,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="65">
+  <borders count="66">
     <border>
       <left/>
       <right/>
@@ -1463,6 +1466,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1470,7 +1484,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="296">
+  <cellXfs count="298">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -2065,9 +2079,219 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="51" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2195,210 +2419,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="51" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2428,13 +2449,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304801</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>5186</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>62853</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2478,13 +2499,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>223158</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>67532</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>898071</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>54933</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2528,13 +2549,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>984250</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>74105</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>206375</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>110552</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2890,7 +2911,7 @@
     <tabColor rgb="FF00B050"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:XFC102"/>
+  <dimension ref="A1:XFC103"/>
   <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="91" customWidth="1"/>
@@ -2951,28 +2972,28 @@
       <c r="C2" s="93"/>
       <c r="D2" s="93"/>
       <c r="E2" s="93"/>
-      <c r="F2" s="284" t="s">
+      <c r="F2" s="207" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="284"/>
-      <c r="H2" s="284"/>
-      <c r="I2" s="284"/>
-      <c r="J2" s="284"/>
-      <c r="K2" s="284"/>
-      <c r="L2" s="284"/>
-      <c r="M2" s="284"/>
-      <c r="N2" s="284"/>
-      <c r="O2" s="284"/>
-      <c r="P2" s="284"/>
-      <c r="Q2" s="284"/>
-      <c r="R2" s="284"/>
-      <c r="S2" s="284"/>
+      <c r="G2" s="207"/>
+      <c r="H2" s="207"/>
+      <c r="I2" s="207"/>
+      <c r="J2" s="207"/>
+      <c r="K2" s="207"/>
+      <c r="L2" s="207"/>
+      <c r="M2" s="207"/>
+      <c r="N2" s="207"/>
+      <c r="O2" s="207"/>
+      <c r="P2" s="207"/>
+      <c r="Q2" s="207"/>
+      <c r="R2" s="207"/>
+      <c r="S2" s="207"/>
       <c r="T2" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="U2" s="193"/>
-      <c r="V2" s="193"/>
-      <c r="X2" s="237" t="s">
+      <c r="U2" s="214"/>
+      <c r="V2" s="214"/>
+      <c r="X2" s="208" t="s">
         <v>2</v>
       </c>
       <c r="AB2" s="92">
@@ -2988,483 +3009,447 @@
         <v>330</v>
       </c>
     </row>
-    <row r="3" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="93"/>
       <c r="C3" s="93"/>
       <c r="D3" s="93"/>
       <c r="E3" s="93"/>
-      <c r="X3" s="238"/>
-      <c r="AB3" s="92">
-        <v>5.76</v>
-      </c>
-      <c r="AC3" s="91">
-        <v>1.4500000000000002</v>
-      </c>
-      <c r="AD3" s="91">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="92">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="4" spans="2:35" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="93" t="s">
-        <v>3</v>
-      </c>
+      <c r="F3" s="193"/>
+      <c r="G3" s="193"/>
+      <c r="H3" s="193"/>
+      <c r="I3" s="193"/>
+      <c r="J3" s="193"/>
+      <c r="K3" s="193"/>
+      <c r="L3" s="193"/>
+      <c r="M3" s="193"/>
+      <c r="N3" s="193"/>
+      <c r="O3" s="193"/>
+      <c r="P3" s="193"/>
+      <c r="Q3" s="193"/>
+      <c r="R3" s="193"/>
+      <c r="S3" s="193"/>
+      <c r="T3" s="94" t="s">
+        <v>131</v>
+      </c>
+      <c r="U3" s="297"/>
+      <c r="V3" s="297"/>
+      <c r="X3" s="209"/>
+      <c r="AB3" s="92"/>
+      <c r="AE3" s="92"/>
+    </row>
+    <row r="4" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="93"/>
       <c r="C4" s="93"/>
       <c r="D4" s="93"/>
       <c r="E4" s="93"/>
-      <c r="F4" s="285"/>
-      <c r="G4" s="285"/>
-      <c r="H4" s="285"/>
-      <c r="I4" s="285"/>
-      <c r="J4" s="285"/>
-      <c r="K4" s="285"/>
-      <c r="L4" s="285"/>
-      <c r="M4" s="285"/>
-      <c r="S4" s="91" t="s">
+      <c r="X4" s="209"/>
+      <c r="AB4" s="92">
+        <v>5.76</v>
+      </c>
+      <c r="AC4" s="91">
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="AD4" s="91">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="92">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="2:35" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="93" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
+      <c r="M5" s="211"/>
+      <c r="S5" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T4" s="286"/>
-      <c r="U4" s="286"/>
-      <c r="V4" s="183"/>
-      <c r="X4" s="239"/>
-      <c r="AB4" s="92">
+      <c r="T5" s="212"/>
+      <c r="U5" s="212"/>
+      <c r="V5" s="183"/>
+      <c r="X5" s="210"/>
+      <c r="AB5" s="92">
         <v>5.07</v>
       </c>
-      <c r="AC4" s="91">
+      <c r="AC5" s="91">
         <v>1.2699999999999996</v>
       </c>
-      <c r="AD4" s="91">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="92">
+      <c r="AD5" s="91">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="92">
         <v>1000</v>
       </c>
     </row>
-    <row r="5" spans="2:35" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="95"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="95"/>
-      <c r="H5" s="95"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="95"/>
-      <c r="N5" s="95"/>
-      <c r="O5" s="95"/>
-      <c r="P5" s="95"/>
-      <c r="Q5" s="2"/>
-      <c r="S5" s="95"/>
-      <c r="T5" s="95"/>
-      <c r="U5" s="95"/>
-      <c r="V5" s="95"/>
-      <c r="X5" s="96"/>
-      <c r="AB5" s="92"/>
-    </row>
-    <row r="6" spans="2:35" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="91" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="287"/>
-      <c r="G6" s="287"/>
-      <c r="H6" s="287"/>
-      <c r="I6" s="287"/>
-      <c r="J6" s="287"/>
-      <c r="K6" s="287"/>
-      <c r="L6" s="287"/>
-      <c r="M6" s="287"/>
-      <c r="S6" s="97" t="s">
-        <v>6</v>
-      </c>
-      <c r="T6" s="163" t="s">
-        <v>7</v>
-      </c>
-      <c r="U6" s="279" t="s">
-        <v>8</v>
-      </c>
-      <c r="V6" s="279"/>
-      <c r="X6" s="237" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB6" s="92">
-        <v>2.81</v>
-      </c>
-      <c r="AC6" s="91">
-        <v>0.71</v>
-      </c>
-      <c r="AD6" s="91">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="97" t="s">
-        <v>82</v>
-      </c>
+    <row r="6" spans="2:35" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="95"/>
+      <c r="N6" s="95"/>
+      <c r="O6" s="95"/>
+      <c r="P6" s="95"/>
+      <c r="Q6" s="2"/>
+      <c r="S6" s="95"/>
+      <c r="T6" s="95"/>
+      <c r="U6" s="95"/>
+      <c r="V6" s="95"/>
+      <c r="X6" s="96"/>
+      <c r="AB6" s="92"/>
     </row>
     <row r="7" spans="2:35" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="91" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="213"/>
+      <c r="G7" s="213"/>
+      <c r="H7" s="213"/>
+      <c r="I7" s="213"/>
+      <c r="J7" s="213"/>
+      <c r="K7" s="213"/>
+      <c r="L7" s="213"/>
+      <c r="M7" s="213"/>
+      <c r="S7" s="97" t="s">
+        <v>6</v>
+      </c>
+      <c r="T7" s="163" t="s">
+        <v>7</v>
+      </c>
+      <c r="U7" s="204" t="s">
+        <v>8</v>
+      </c>
+      <c r="V7" s="204"/>
+      <c r="X7" s="208" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB7" s="92">
+        <v>2.81</v>
+      </c>
+      <c r="AC7" s="91">
+        <v>0.71</v>
+      </c>
+      <c r="AD7" s="91">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="97" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="2:35" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="91" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="287"/>
-      <c r="G7" s="287"/>
-      <c r="H7" s="287"/>
-      <c r="I7" s="287"/>
-      <c r="J7" s="287"/>
-      <c r="K7" s="287"/>
-      <c r="L7" s="287"/>
-      <c r="M7" s="287"/>
-      <c r="N7" s="99"/>
-      <c r="O7" s="99"/>
-      <c r="P7" s="99"/>
-      <c r="Q7" s="3"/>
-      <c r="S7" s="99"/>
-      <c r="T7" s="163" t="s">
+      <c r="C8" s="98"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="213"/>
+      <c r="G8" s="213"/>
+      <c r="H8" s="213"/>
+      <c r="I8" s="213"/>
+      <c r="J8" s="213"/>
+      <c r="K8" s="213"/>
+      <c r="L8" s="213"/>
+      <c r="M8" s="213"/>
+      <c r="N8" s="99"/>
+      <c r="O8" s="99"/>
+      <c r="P8" s="99"/>
+      <c r="Q8" s="3"/>
+      <c r="S8" s="99"/>
+      <c r="T8" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="U7" s="280"/>
-      <c r="V7" s="281"/>
-      <c r="X7" s="239"/>
-      <c r="AB7" s="92">
+      <c r="U8" s="205"/>
+      <c r="V8" s="206"/>
+      <c r="X8" s="210"/>
+      <c r="AB8" s="92">
         <v>5.25</v>
       </c>
-      <c r="AC7" s="91">
+      <c r="AC8" s="91">
         <v>1.33</v>
       </c>
-      <c r="AE7" s="97" t="s">
+      <c r="AE8" s="97" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="2:35" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="95"/>
-      <c r="C8" s="95"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="95"/>
-      <c r="N8" s="95"/>
-      <c r="O8" s="95"/>
-      <c r="P8" s="95"/>
-      <c r="Q8" s="2"/>
-      <c r="S8" s="95"/>
-      <c r="T8" s="95"/>
-      <c r="U8" s="95"/>
-      <c r="V8" s="95"/>
-    </row>
-    <row r="9" spans="2:35" s="100" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="247" t="s">
+    <row r="9" spans="2:35" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="95"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="95"/>
+      <c r="E9" s="95"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="95"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="95"/>
+      <c r="N9" s="95"/>
+      <c r="O9" s="95"/>
+      <c r="P9" s="95"/>
+      <c r="Q9" s="2"/>
+      <c r="S9" s="95"/>
+      <c r="T9" s="95"/>
+      <c r="U9" s="95"/>
+      <c r="V9" s="95"/>
+    </row>
+    <row r="10" spans="2:35" s="100" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="216" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="250" t="s">
+      <c r="C10" s="219" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="250" t="s">
+      <c r="D10" s="219" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="250" t="s">
+      <c r="E10" s="219" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="253" t="s">
+      <c r="F10" s="222" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="254"/>
-      <c r="H9" s="254"/>
-      <c r="I9" s="254"/>
-      <c r="J9" s="254"/>
-      <c r="K9" s="254"/>
-      <c r="L9" s="254"/>
-      <c r="M9" s="254"/>
-      <c r="N9" s="254"/>
-      <c r="O9" s="254"/>
-      <c r="P9" s="254"/>
-      <c r="Q9" s="255"/>
-      <c r="S9" s="288" t="s">
+      <c r="G10" s="223"/>
+      <c r="H10" s="223"/>
+      <c r="I10" s="223"/>
+      <c r="J10" s="223"/>
+      <c r="K10" s="223"/>
+      <c r="L10" s="223"/>
+      <c r="M10" s="223"/>
+      <c r="N10" s="223"/>
+      <c r="O10" s="223"/>
+      <c r="P10" s="223"/>
+      <c r="Q10" s="224"/>
+      <c r="S10" s="215" t="s">
         <v>17</v>
       </c>
-      <c r="T9" s="288"/>
-      <c r="U9" s="288"/>
-      <c r="V9" s="288"/>
-      <c r="Y9" s="266" t="s">
+      <c r="T10" s="215"/>
+      <c r="U10" s="215"/>
+      <c r="V10" s="215"/>
+      <c r="Y10" s="235" t="s">
         <v>18</v>
       </c>
-      <c r="Z9" s="269" t="s">
+      <c r="Z10" s="238" t="s">
         <v>19</v>
       </c>
-      <c r="AA9" s="101"/>
-      <c r="AB9" s="256" t="s">
+      <c r="AA10" s="101"/>
+      <c r="AB10" s="225" t="s">
         <v>20</v>
       </c>
-      <c r="AC9" s="272" t="s">
+      <c r="AC10" s="241" t="s">
         <v>21</v>
       </c>
-      <c r="AD9" s="275" t="s">
+      <c r="AD10" s="244" t="s">
         <v>84</v>
       </c>
-      <c r="AE9" s="256" t="s">
+      <c r="AE10" s="225" t="s">
         <v>22</v>
       </c>
-      <c r="AG9" s="256" t="s">
+      <c r="AG10" s="225" t="s">
         <v>23</v>
       </c>
-      <c r="AH9" s="101"/>
-      <c r="AI9" s="256" t="s">
+      <c r="AH10" s="101"/>
+      <c r="AI10" s="225" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="2:35" s="100" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="248"/>
-      <c r="C10" s="251"/>
-      <c r="D10" s="251"/>
-      <c r="E10" s="251"/>
-      <c r="F10" s="260" t="s">
+    <row r="11" spans="2:35" s="100" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="217"/>
+      <c r="C11" s="220"/>
+      <c r="D11" s="220"/>
+      <c r="E11" s="220"/>
+      <c r="F11" s="229" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="260" t="s">
+      <c r="G11" s="229" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="260" t="s">
+      <c r="H11" s="229" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="261" t="s">
+      <c r="I11" s="230" t="s">
         <v>28</v>
       </c>
-      <c r="J10" s="261" t="s">
+      <c r="J11" s="230" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="261" t="s">
+      <c r="K11" s="230" t="s">
         <v>30</v>
       </c>
-      <c r="L10" s="261" t="s">
+      <c r="L11" s="230" t="s">
         <v>31</v>
       </c>
-      <c r="M10" s="263" t="s">
+      <c r="M11" s="232" t="s">
         <v>32</v>
       </c>
-      <c r="N10" s="264"/>
-      <c r="O10" s="264"/>
-      <c r="P10" s="264"/>
-      <c r="Q10" s="265"/>
-      <c r="S10" s="288" t="s">
+      <c r="N11" s="233"/>
+      <c r="O11" s="233"/>
+      <c r="P11" s="233"/>
+      <c r="Q11" s="234"/>
+      <c r="S11" s="215" t="s">
         <v>33</v>
       </c>
-      <c r="T10" s="288"/>
-      <c r="U10" s="288"/>
-      <c r="V10" s="288"/>
-      <c r="Y10" s="267"/>
-      <c r="Z10" s="270"/>
-      <c r="AA10" s="101"/>
-      <c r="AB10" s="257"/>
-      <c r="AC10" s="273"/>
-      <c r="AD10" s="276"/>
-      <c r="AE10" s="257"/>
-      <c r="AG10" s="257"/>
-      <c r="AH10" s="101"/>
-      <c r="AI10" s="257"/>
-    </row>
-    <row r="11" spans="2:35" s="102" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="249"/>
-      <c r="C11" s="252"/>
-      <c r="D11" s="252"/>
-      <c r="E11" s="252"/>
-      <c r="F11" s="252"/>
-      <c r="G11" s="252"/>
-      <c r="H11" s="252"/>
-      <c r="I11" s="262"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="262"/>
-      <c r="M11" s="4" t="s">
+      <c r="T11" s="215"/>
+      <c r="U11" s="215"/>
+      <c r="V11" s="215"/>
+      <c r="Y11" s="236"/>
+      <c r="Z11" s="239"/>
+      <c r="AA11" s="101"/>
+      <c r="AB11" s="226"/>
+      <c r="AC11" s="242"/>
+      <c r="AD11" s="245"/>
+      <c r="AE11" s="226"/>
+      <c r="AG11" s="226"/>
+      <c r="AH11" s="101"/>
+      <c r="AI11" s="226"/>
+    </row>
+    <row r="12" spans="2:35" s="102" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="218"/>
+      <c r="C12" s="221"/>
+      <c r="D12" s="221"/>
+      <c r="E12" s="221"/>
+      <c r="F12" s="221"/>
+      <c r="G12" s="221"/>
+      <c r="H12" s="221"/>
+      <c r="I12" s="231"/>
+      <c r="J12" s="231"/>
+      <c r="K12" s="231"/>
+      <c r="L12" s="231"/>
+      <c r="M12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="O12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="P11" s="5" t="s">
+      <c r="P12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="Q11" s="6" t="s">
+      <c r="Q12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="S11" s="188" t="s">
+      <c r="S12" s="188" t="s">
         <v>34</v>
       </c>
-      <c r="T11" s="188" t="s">
+      <c r="T12" s="188" t="s">
         <v>35</v>
       </c>
-      <c r="U11" s="278" t="s">
+      <c r="U12" s="247" t="s">
         <v>36</v>
       </c>
-      <c r="V11" s="278"/>
-      <c r="Y11" s="268"/>
-      <c r="Z11" s="271"/>
-      <c r="AA11" s="101"/>
-      <c r="AB11" s="259"/>
-      <c r="AC11" s="274"/>
-      <c r="AD11" s="277"/>
-      <c r="AE11" s="259"/>
-      <c r="AG11" s="258"/>
-      <c r="AH11" s="101"/>
-      <c r="AI11" s="259"/>
-    </row>
-    <row r="12" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="103" t="s">
+      <c r="V12" s="247"/>
+      <c r="Y12" s="237"/>
+      <c r="Z12" s="240"/>
+      <c r="AA12" s="101"/>
+      <c r="AB12" s="228"/>
+      <c r="AC12" s="243"/>
+      <c r="AD12" s="246"/>
+      <c r="AE12" s="228"/>
+      <c r="AG12" s="227"/>
+      <c r="AH12" s="101"/>
+      <c r="AI12" s="228"/>
+    </row>
+    <row r="13" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="103" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C13" s="7">
         <v>792</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D13" s="7">
         <v>120</v>
       </c>
-      <c r="E12" s="7">
-        <f>C12+D12</f>
+      <c r="E13" s="7">
+        <f>C13+D13</f>
         <v>912</v>
       </c>
-      <c r="F12" s="104"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="13"/>
-      <c r="S12" s="14"/>
-      <c r="T12" s="189"/>
-      <c r="U12" s="282"/>
-      <c r="V12" s="282"/>
-      <c r="Y12" s="105">
-        <f>F12*C12</f>
-        <v>0</v>
-      </c>
-      <c r="Z12" s="106">
-        <f t="shared" ref="Z12:Z70" si="0">F12*AI12</f>
-        <v>0</v>
-      </c>
-      <c r="AA12" s="107"/>
-      <c r="AB12" s="108">
+      <c r="F13" s="104"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="13"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="189"/>
+      <c r="U13" s="201"/>
+      <c r="V13" s="201"/>
+      <c r="Y13" s="105">
+        <f>F13*C13</f>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="106">
+        <f t="shared" ref="Z13:Z71" si="0">F13*AI13</f>
+        <v>0</v>
+      </c>
+      <c r="AA13" s="107"/>
+      <c r="AB13" s="108">
         <f>AB$1</f>
         <v>7.68</v>
       </c>
-      <c r="AC12" s="109">
+      <c r="AC13" s="109">
         <v>1.95</v>
       </c>
-      <c r="AD12" s="109">
+      <c r="AD13" s="109">
         <f>AD$1</f>
         <v>0</v>
       </c>
-      <c r="AE12" s="110">
-        <f>AB12+AC12+AD12</f>
+      <c r="AE13" s="110">
+        <f>AB13+AC13+AD13</f>
         <v>9.629999999999999</v>
       </c>
-      <c r="AF12" s="111"/>
-      <c r="AG12" s="112">
+      <c r="AF13" s="111"/>
+      <c r="AG13" s="112">
         <v>24</v>
       </c>
-      <c r="AH12" s="107"/>
-      <c r="AI12" s="15">
-        <f t="shared" ref="AI12:AI70" si="1">AG12+AE12</f>
+      <c r="AH13" s="107"/>
+      <c r="AI13" s="15">
+        <f t="shared" ref="AI13:AI71" si="1">AG13+AE13</f>
         <v>33.629999999999995</v>
-      </c>
-    </row>
-    <row r="13" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="113" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" s="16">
-        <v>544</v>
-      </c>
-      <c r="D13" s="16">
-        <v>111</v>
-      </c>
-      <c r="E13" s="16">
-        <f t="shared" ref="E13:E70" si="2">C13+D13</f>
-        <v>655</v>
-      </c>
-      <c r="F13" s="114"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="22"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="283"/>
-      <c r="V13" s="283"/>
-      <c r="Y13" s="115">
-        <f t="shared" ref="Y13:Y70" si="3">F13*C13</f>
-        <v>0</v>
-      </c>
-      <c r="Z13" s="116">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA13" s="107"/>
-      <c r="AB13" s="117">
-        <f>AB$4</f>
-        <v>5.07</v>
-      </c>
-      <c r="AC13" s="118">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="AD13" s="118">
-        <f>AD$4</f>
-        <v>0</v>
-      </c>
-      <c r="AE13" s="119">
-        <f t="shared" ref="AE13:AE70" si="4">AB13+AC13+AD13</f>
-        <v>6.2</v>
-      </c>
-      <c r="AF13" s="120"/>
-      <c r="AG13" s="121">
-        <v>24</v>
-      </c>
-      <c r="AH13" s="107"/>
-      <c r="AI13" s="24">
-        <f t="shared" si="1"/>
-        <v>30.2</v>
       </c>
     </row>
     <row r="14" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="113" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C14" s="16">
-        <v>853</v>
+        <v>544</v>
       </c>
       <c r="D14" s="16">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E14" s="16">
-        <f t="shared" si="2"/>
-        <v>973</v>
+        <f t="shared" ref="E14:E71" si="2">C14+D14</f>
+        <v>655</v>
       </c>
       <c r="F14" s="114"/>
       <c r="G14" s="17"/>
-      <c r="H14" s="25"/>
+      <c r="H14" s="18"/>
       <c r="I14" s="19"/>
       <c r="J14" s="20"/>
       <c r="K14" s="20"/>
@@ -3476,10 +3461,10 @@
       <c r="Q14" s="22"/>
       <c r="S14" s="23"/>
       <c r="T14" s="23"/>
-      <c r="U14" s="283"/>
-      <c r="V14" s="283"/>
+      <c r="U14" s="196"/>
+      <c r="V14" s="196"/>
       <c r="Y14" s="115">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="Y14:Y71" si="3">F14*C14</f>
         <v>0</v>
       </c>
       <c r="Z14" s="116">
@@ -3488,19 +3473,19 @@
       </c>
       <c r="AA14" s="107"/>
       <c r="AB14" s="117">
-        <f>AB$2</f>
-        <v>8.76</v>
+        <f>AB$5</f>
+        <v>5.07</v>
       </c>
       <c r="AC14" s="118">
-        <v>1.95</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="AD14" s="118">
-        <f>AD$2</f>
+        <f>AD$5</f>
         <v>0</v>
       </c>
       <c r="AE14" s="119">
-        <f t="shared" si="4"/>
-        <v>10.709999999999999</v>
+        <f t="shared" ref="AE14:AE71" si="4">AB14+AC14+AD14</f>
+        <v>6.2</v>
       </c>
       <c r="AF14" s="120"/>
       <c r="AG14" s="121">
@@ -3509,22 +3494,22 @@
       <c r="AH14" s="107"/>
       <c r="AI14" s="24">
         <f t="shared" si="1"/>
-        <v>34.71</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="15" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="113" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C15" s="16">
-        <v>563</v>
+        <v>853</v>
       </c>
       <c r="D15" s="16">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="E15" s="16">
         <f t="shared" si="2"/>
-        <v>674</v>
+        <v>973</v>
       </c>
       <c r="F15" s="114"/>
       <c r="G15" s="17"/>
@@ -3540,8 +3525,8 @@
       <c r="Q15" s="22"/>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
-      <c r="U15" s="289"/>
-      <c r="V15" s="289"/>
+      <c r="U15" s="196"/>
+      <c r="V15" s="196"/>
       <c r="Y15" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3552,19 +3537,19 @@
       </c>
       <c r="AA15" s="107"/>
       <c r="AB15" s="117">
-        <f>AB$3</f>
-        <v>5.76</v>
+        <f>AB$2</f>
+        <v>8.76</v>
       </c>
       <c r="AC15" s="118">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" s="118">
-        <f>AD$3</f>
+        <f>AD$2</f>
         <v>0</v>
       </c>
       <c r="AE15" s="119">
         <f t="shared" si="4"/>
-        <v>7.05</v>
+        <v>10.709999999999999</v>
       </c>
       <c r="AF15" s="120"/>
       <c r="AG15" s="121">
@@ -3573,39 +3558,39 @@
       <c r="AH15" s="107"/>
       <c r="AI15" s="24">
         <f t="shared" si="1"/>
-        <v>31.05</v>
+        <v>34.71</v>
       </c>
     </row>
     <row r="16" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="113" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C16" s="16">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="D16" s="16">
         <v>111</v>
       </c>
       <c r="E16" s="16">
         <f t="shared" si="2"/>
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="F16" s="114"/>
       <c r="G16" s="17"/>
       <c r="H16" s="25"/>
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
-      <c r="K16" s="61"/>
+      <c r="K16" s="20"/>
       <c r="L16" s="20"/>
       <c r="M16" s="23"/>
-      <c r="N16" s="26"/>
+      <c r="N16" s="23"/>
       <c r="O16" s="23"/>
       <c r="P16" s="21"/>
       <c r="Q16" s="22"/>
       <c r="S16" s="23"/>
-      <c r="T16" s="26"/>
-      <c r="U16" s="291"/>
-      <c r="V16" s="291"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="197"/>
+      <c r="V16" s="197"/>
       <c r="Y16" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3616,19 +3601,19 @@
       </c>
       <c r="AA16" s="107"/>
       <c r="AB16" s="117">
-        <f t="shared" ref="AB16:AD17" si="5">AB$4</f>
-        <v>5.07</v>
+        <f>AB$4</f>
+        <v>5.76</v>
       </c>
       <c r="AC16" s="118">
-        <v>1.1299999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="AD16" s="118">
-        <f t="shared" si="5"/>
+        <f>AD$4</f>
         <v>0</v>
       </c>
       <c r="AE16" s="119">
         <f t="shared" si="4"/>
-        <v>6.2</v>
+        <v>7.05</v>
       </c>
       <c r="AF16" s="120"/>
       <c r="AG16" s="121">
@@ -3637,22 +3622,22 @@
       <c r="AH16" s="107"/>
       <c r="AI16" s="24">
         <f t="shared" si="1"/>
-        <v>30.2</v>
+        <v>31.05</v>
       </c>
     </row>
     <row r="17" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="113" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C17" s="16">
-        <v>520</v>
+        <v>575</v>
       </c>
       <c r="D17" s="16">
         <v>111</v>
       </c>
       <c r="E17" s="16">
         <f t="shared" si="2"/>
-        <v>631</v>
+        <v>686</v>
       </c>
       <c r="F17" s="114"/>
       <c r="G17" s="17"/>
@@ -3668,8 +3653,8 @@
       <c r="Q17" s="22"/>
       <c r="S17" s="23"/>
       <c r="T17" s="26"/>
-      <c r="U17" s="291"/>
-      <c r="V17" s="291"/>
+      <c r="U17" s="199"/>
+      <c r="V17" s="199"/>
       <c r="Y17" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3680,7 +3665,7 @@
       </c>
       <c r="AA17" s="107"/>
       <c r="AB17" s="117">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="AB17:AD18" si="5">AB$5</f>
         <v>5.07</v>
       </c>
       <c r="AC17" s="118">
@@ -3705,35 +3690,35 @@
       </c>
     </row>
     <row r="18" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="122" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="27">
-        <v>945</v>
-      </c>
-      <c r="D18" s="27">
-        <v>120</v>
-      </c>
-      <c r="E18" s="27">
+      <c r="B18" s="113" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="16">
+        <v>520</v>
+      </c>
+      <c r="D18" s="16">
+        <v>111</v>
+      </c>
+      <c r="E18" s="16">
         <f t="shared" si="2"/>
-        <v>1065</v>
-      </c>
-      <c r="F18" s="123"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="124"/>
-      <c r="L18" s="31"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="32"/>
-      <c r="Q18" s="33"/>
-      <c r="S18" s="34"/>
-      <c r="T18" s="35"/>
-      <c r="U18" s="290"/>
-      <c r="V18" s="290"/>
+        <v>631</v>
+      </c>
+      <c r="F18" s="114"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="22"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="26"/>
+      <c r="U18" s="199"/>
+      <c r="V18" s="199"/>
       <c r="Y18" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3744,60 +3729,60 @@
       </c>
       <c r="AA18" s="107"/>
       <c r="AB18" s="117">
-        <f t="shared" ref="AB18:AD26" si="6">AB$2</f>
-        <v>8.76</v>
+        <f t="shared" si="5"/>
+        <v>5.07</v>
       </c>
       <c r="AC18" s="118">
-        <v>1.95</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="AD18" s="118">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE18" s="119">
         <f t="shared" si="4"/>
-        <v>10.709999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AF18" s="120"/>
       <c r="AG18" s="121">
         <v>24</v>
       </c>
       <c r="AH18" s="107"/>
-      <c r="AI18" s="36">
+      <c r="AI18" s="24">
         <f t="shared" si="1"/>
-        <v>34.71</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="19" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="113" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="16">
-        <v>773</v>
-      </c>
-      <c r="D19" s="16">
+      <c r="B19" s="122" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="27">
+        <v>945</v>
+      </c>
+      <c r="D19" s="27">
         <v>120</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="27">
         <f t="shared" si="2"/>
-        <v>893</v>
-      </c>
-      <c r="F19" s="114"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="61"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="22"/>
-      <c r="S19" s="23"/>
-      <c r="T19" s="26"/>
-      <c r="U19" s="289"/>
-      <c r="V19" s="289"/>
+        <v>1065</v>
+      </c>
+      <c r="F19" s="123"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="124"/>
+      <c r="L19" s="31"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="34"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="33"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="203"/>
+      <c r="V19" s="203"/>
       <c r="Y19" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3808,7 +3793,7 @@
       </c>
       <c r="AA19" s="107"/>
       <c r="AB19" s="117">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="AB19:AD27" si="6">AB$2</f>
         <v>8.76</v>
       </c>
       <c r="AC19" s="118">
@@ -3827,41 +3812,41 @@
         <v>24</v>
       </c>
       <c r="AH19" s="107"/>
-      <c r="AI19" s="24">
+      <c r="AI19" s="36">
         <f t="shared" si="1"/>
         <v>34.71</v>
       </c>
     </row>
     <row r="20" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="122" t="s">
-        <v>96</v>
-      </c>
-      <c r="C20" s="27">
+      <c r="B20" s="113" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="16">
         <v>773</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="16">
         <v>120</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="16">
         <f t="shared" si="2"/>
         <v>893</v>
       </c>
-      <c r="F20" s="123"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="124"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="33"/>
-      <c r="S20" s="34"/>
-      <c r="T20" s="35"/>
-      <c r="U20" s="290"/>
-      <c r="V20" s="290"/>
+      <c r="F20" s="114"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="22"/>
+      <c r="S20" s="23"/>
+      <c r="T20" s="26"/>
+      <c r="U20" s="197"/>
+      <c r="V20" s="197"/>
       <c r="Y20" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3891,41 +3876,41 @@
         <v>24</v>
       </c>
       <c r="AH20" s="107"/>
-      <c r="AI20" s="36">
+      <c r="AI20" s="24">
         <f t="shared" si="1"/>
         <v>34.71</v>
       </c>
     </row>
     <row r="21" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="103" t="s">
-        <v>97</v>
-      </c>
-      <c r="C21" s="7">
-        <v>1300</v>
-      </c>
-      <c r="D21" s="7">
+      <c r="B21" s="122" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="27">
+        <v>773</v>
+      </c>
+      <c r="D21" s="27">
         <v>120</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="27">
         <f t="shared" si="2"/>
-        <v>1420</v>
-      </c>
-      <c r="F21" s="125"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="43"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="42"/>
-      <c r="S21" s="43"/>
-      <c r="T21" s="44"/>
-      <c r="U21" s="289"/>
-      <c r="V21" s="289"/>
+        <v>893</v>
+      </c>
+      <c r="F21" s="123"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="124"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="33"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="35"/>
+      <c r="U21" s="203"/>
+      <c r="V21" s="203"/>
       <c r="Y21" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3955,41 +3940,41 @@
         <v>24</v>
       </c>
       <c r="AH21" s="107"/>
-      <c r="AI21" s="15">
+      <c r="AI21" s="36">
         <f t="shared" si="1"/>
         <v>34.71</v>
       </c>
     </row>
     <row r="22" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="113" t="s">
-        <v>98</v>
-      </c>
-      <c r="C22" s="16">
-        <v>1240</v>
-      </c>
-      <c r="D22" s="16">
+      <c r="B22" s="103" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="7">
+        <v>1300</v>
+      </c>
+      <c r="D22" s="7">
         <v>120</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="7">
         <f t="shared" si="2"/>
-        <v>1360</v>
-      </c>
-      <c r="F22" s="114"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="26"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="22"/>
-      <c r="S22" s="23"/>
-      <c r="T22" s="26"/>
-      <c r="U22" s="291"/>
-      <c r="V22" s="291"/>
+        <v>1420</v>
+      </c>
+      <c r="F22" s="125"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="64"/>
+      <c r="L22" s="40"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="43"/>
+      <c r="P22" s="41"/>
+      <c r="Q22" s="42"/>
+      <c r="S22" s="43"/>
+      <c r="T22" s="44"/>
+      <c r="U22" s="197"/>
+      <c r="V22" s="197"/>
       <c r="Y22" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4019,24 +4004,24 @@
         <v>24</v>
       </c>
       <c r="AH22" s="107"/>
-      <c r="AI22" s="24">
+      <c r="AI22" s="15">
         <f t="shared" si="1"/>
         <v>34.71</v>
       </c>
     </row>
     <row r="23" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="113" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C23" s="16">
-        <v>-120</v>
+        <v>1240</v>
       </c>
       <c r="D23" s="16">
         <v>120</v>
       </c>
       <c r="E23" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1360</v>
       </c>
       <c r="F23" s="114"/>
       <c r="G23" s="17"/>
@@ -4052,8 +4037,8 @@
       <c r="Q23" s="22"/>
       <c r="S23" s="23"/>
       <c r="T23" s="26"/>
-      <c r="U23" s="283"/>
-      <c r="V23" s="283"/>
+      <c r="U23" s="199"/>
+      <c r="V23" s="199"/>
       <c r="Y23" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4089,35 +4074,35 @@
       </c>
     </row>
     <row r="24" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="122" t="s">
-        <v>100</v>
-      </c>
-      <c r="C24" s="27">
-        <v>1240</v>
-      </c>
-      <c r="D24" s="27">
+      <c r="B24" s="113" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="16">
+        <v>-120</v>
+      </c>
+      <c r="D24" s="16">
         <v>120</v>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="16">
         <f t="shared" si="2"/>
-        <v>1360</v>
-      </c>
-      <c r="F24" s="123"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="34"/>
-      <c r="P24" s="32"/>
-      <c r="Q24" s="33"/>
-      <c r="S24" s="34"/>
-      <c r="T24" s="35"/>
-      <c r="U24" s="291"/>
-      <c r="V24" s="291"/>
+        <v>0</v>
+      </c>
+      <c r="F24" s="114"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="23"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="22"/>
+      <c r="S24" s="23"/>
+      <c r="T24" s="26"/>
+      <c r="U24" s="196"/>
+      <c r="V24" s="196"/>
       <c r="Y24" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4147,41 +4132,41 @@
         <v>24</v>
       </c>
       <c r="AH24" s="107"/>
-      <c r="AI24" s="36">
+      <c r="AI24" s="24">
         <f t="shared" si="1"/>
         <v>34.71</v>
       </c>
     </row>
     <row r="25" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="103" t="s">
-        <v>101</v>
-      </c>
-      <c r="C25" s="7">
-        <v>500</v>
-      </c>
-      <c r="D25" s="7">
+      <c r="B25" s="122" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" s="27">
+        <v>1240</v>
+      </c>
+      <c r="D25" s="27">
         <v>120</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="27">
         <f t="shared" si="2"/>
-        <v>620</v>
-      </c>
-      <c r="F25" s="125"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="64"/>
-      <c r="L25" s="40"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="44"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="41"/>
-      <c r="Q25" s="42"/>
-      <c r="S25" s="43"/>
-      <c r="T25" s="44"/>
-      <c r="U25" s="292"/>
-      <c r="V25" s="292"/>
+        <v>1360</v>
+      </c>
+      <c r="F25" s="123"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="124"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="34"/>
+      <c r="P25" s="32"/>
+      <c r="Q25" s="33"/>
+      <c r="S25" s="34"/>
+      <c r="T25" s="35"/>
+      <c r="U25" s="199"/>
+      <c r="V25" s="199"/>
       <c r="Y25" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4211,41 +4196,41 @@
         <v>24</v>
       </c>
       <c r="AH25" s="107"/>
-      <c r="AI25" s="15">
+      <c r="AI25" s="36">
         <f t="shared" si="1"/>
         <v>34.71</v>
       </c>
     </row>
     <row r="26" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="122" t="s">
-        <v>102</v>
-      </c>
-      <c r="C26" s="45">
+      <c r="B26" s="103" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="7">
         <v>500</v>
       </c>
-      <c r="D26" s="45">
+      <c r="D26" s="7">
         <v>120</v>
       </c>
-      <c r="E26" s="45">
+      <c r="E26" s="7">
         <f t="shared" si="2"/>
         <v>620</v>
       </c>
-      <c r="F26" s="123"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="124"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="34"/>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="33"/>
-      <c r="S26" s="34"/>
-      <c r="T26" s="35"/>
-      <c r="U26" s="289"/>
-      <c r="V26" s="289"/>
+      <c r="F26" s="125"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="64"/>
+      <c r="L26" s="40"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="44"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="41"/>
+      <c r="Q26" s="42"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="44"/>
+      <c r="U26" s="202"/>
+      <c r="V26" s="202"/>
       <c r="Y26" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4275,41 +4260,41 @@
         <v>24</v>
       </c>
       <c r="AH26" s="107"/>
-      <c r="AI26" s="36">
+      <c r="AI26" s="15">
         <f t="shared" si="1"/>
         <v>34.71</v>
       </c>
     </row>
     <row r="27" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="103" t="s">
-        <v>103</v>
-      </c>
-      <c r="C27" s="7">
-        <v>663</v>
-      </c>
-      <c r="D27" s="7">
+      <c r="B27" s="122" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" s="45">
+        <v>500</v>
+      </c>
+      <c r="D27" s="45">
         <v>120</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="45">
         <f t="shared" si="2"/>
-        <v>783</v>
-      </c>
-      <c r="F27" s="125"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="40"/>
-      <c r="K27" s="64"/>
-      <c r="L27" s="40"/>
-      <c r="M27" s="43"/>
-      <c r="N27" s="44"/>
-      <c r="O27" s="43"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="42"/>
-      <c r="S27" s="43"/>
-      <c r="T27" s="44"/>
-      <c r="U27" s="292"/>
-      <c r="V27" s="292"/>
+        <v>620</v>
+      </c>
+      <c r="F27" s="123"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="124"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="35"/>
+      <c r="O27" s="34"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="33"/>
+      <c r="S27" s="34"/>
+      <c r="T27" s="35"/>
+      <c r="U27" s="197"/>
+      <c r="V27" s="197"/>
       <c r="Y27" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4320,60 +4305,60 @@
       </c>
       <c r="AA27" s="107"/>
       <c r="AB27" s="117">
-        <f>AB$1</f>
-        <v>7.68</v>
+        <f t="shared" si="6"/>
+        <v>8.76</v>
       </c>
       <c r="AC27" s="118">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AD27" s="118">
-        <f>AD$1</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE27" s="119">
         <f t="shared" si="4"/>
-        <v>9.4</v>
+        <v>10.709999999999999</v>
       </c>
       <c r="AF27" s="120"/>
       <c r="AG27" s="121">
         <v>24</v>
       </c>
       <c r="AH27" s="107"/>
-      <c r="AI27" s="15">
+      <c r="AI27" s="36">
         <f t="shared" si="1"/>
-        <v>33.4</v>
-      </c>
-    </row>
-    <row r="28" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="113" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="16">
-        <v>-610</v>
-      </c>
-      <c r="D28" s="16">
-        <v>610</v>
-      </c>
-      <c r="E28" s="16">
+        <v>34.71</v>
+      </c>
+    </row>
+    <row r="28" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="103" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="7">
+        <v>663</v>
+      </c>
+      <c r="D28" s="7">
+        <v>120</v>
+      </c>
+      <c r="E28" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F28" s="114"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="61"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="22"/>
-      <c r="S28" s="23"/>
-      <c r="T28" s="26"/>
-      <c r="U28" s="289"/>
-      <c r="V28" s="289"/>
+        <v>783</v>
+      </c>
+      <c r="F28" s="125"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="64"/>
+      <c r="L28" s="40"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="44"/>
+      <c r="O28" s="43"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="42"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="44"/>
+      <c r="U28" s="202"/>
+      <c r="V28" s="202"/>
       <c r="Y28" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4384,41 +4369,43 @@
       </c>
       <c r="AA28" s="107"/>
       <c r="AB28" s="117">
-        <v>1.92</v>
+        <f>AB$1</f>
+        <v>7.68</v>
       </c>
       <c r="AC28" s="118">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AD28" s="118">
-        <v>1.92</v>
+        <f>AD$1</f>
+        <v>0</v>
       </c>
       <c r="AE28" s="119">
         <f t="shared" si="4"/>
-        <v>5.76</v>
+        <v>9.4</v>
       </c>
       <c r="AF28" s="120"/>
       <c r="AG28" s="121">
         <v>24</v>
       </c>
       <c r="AH28" s="107"/>
-      <c r="AI28" s="24">
+      <c r="AI28" s="15">
         <f t="shared" si="1"/>
-        <v>29.759999999999998</v>
-      </c>
-    </row>
-    <row r="29" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="29" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="113" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="C29" s="16">
-        <v>978</v>
+        <v>-610</v>
       </c>
       <c r="D29" s="16">
-        <v>120</v>
+        <v>610</v>
       </c>
       <c r="E29" s="16">
         <f t="shared" si="2"/>
-        <v>1098</v>
+        <v>0</v>
       </c>
       <c r="F29" s="114"/>
       <c r="G29" s="17"/>
@@ -4434,8 +4421,8 @@
       <c r="Q29" s="22"/>
       <c r="S29" s="23"/>
       <c r="T29" s="26"/>
-      <c r="U29" s="283"/>
-      <c r="V29" s="283"/>
+      <c r="U29" s="197"/>
+      <c r="V29" s="197"/>
       <c r="Y29" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4446,19 +4433,17 @@
       </c>
       <c r="AA29" s="107"/>
       <c r="AB29" s="117">
-        <f>AB$2</f>
-        <v>8.76</v>
+        <v>1.92</v>
       </c>
       <c r="AC29" s="118">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AD29" s="118">
-        <f>AD$2</f>
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE29" s="119">
         <f t="shared" si="4"/>
-        <v>10.709999999999999</v>
+        <v>5.76</v>
       </c>
       <c r="AF29" s="120"/>
       <c r="AG29" s="121">
@@ -4467,20 +4452,22 @@
       <c r="AH29" s="107"/>
       <c r="AI29" s="24">
         <f t="shared" si="1"/>
-        <v>34.71</v>
+        <v>29.759999999999998</v>
       </c>
     </row>
     <row r="30" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="103" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="7">
-        <v>1127</v>
-      </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7">
+      <c r="B30" s="113" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="16">
+        <v>978</v>
+      </c>
+      <c r="D30" s="16">
+        <v>120</v>
+      </c>
+      <c r="E30" s="16">
         <f t="shared" si="2"/>
-        <v>1127</v>
+        <v>1098</v>
       </c>
       <c r="F30" s="114"/>
       <c r="G30" s="17"/>
@@ -4489,15 +4476,15 @@
       <c r="J30" s="20"/>
       <c r="K30" s="61"/>
       <c r="L30" s="20"/>
-      <c r="M30" s="26"/>
+      <c r="M30" s="23"/>
       <c r="N30" s="26"/>
-      <c r="O30" s="26"/>
+      <c r="O30" s="23"/>
       <c r="P30" s="21"/>
       <c r="Q30" s="22"/>
-      <c r="S30" s="26"/>
+      <c r="S30" s="23"/>
       <c r="T30" s="26"/>
-      <c r="U30" s="291"/>
-      <c r="V30" s="291"/>
+      <c r="U30" s="196"/>
+      <c r="V30" s="196"/>
       <c r="Y30" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4508,41 +4495,41 @@
       </c>
       <c r="AA30" s="107"/>
       <c r="AB30" s="117">
-        <f t="shared" ref="AB30:AD40" si="7">AB$6</f>
-        <v>2.81</v>
+        <f>AB$2</f>
+        <v>8.76</v>
       </c>
       <c r="AC30" s="118">
-        <v>0.63</v>
+        <v>1.95</v>
       </c>
       <c r="AD30" s="118">
-        <f t="shared" si="7"/>
+        <f>AD$2</f>
         <v>0</v>
       </c>
       <c r="AE30" s="119">
         <f t="shared" si="4"/>
-        <v>3.44</v>
+        <v>10.709999999999999</v>
       </c>
       <c r="AF30" s="120"/>
       <c r="AG30" s="121">
         <v>24</v>
       </c>
       <c r="AH30" s="107"/>
-      <c r="AI30" s="15">
+      <c r="AI30" s="24">
         <f t="shared" si="1"/>
-        <v>27.44</v>
+        <v>34.71</v>
       </c>
     </row>
     <row r="31" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="113" t="s">
-        <v>106</v>
-      </c>
-      <c r="C31" s="16">
-        <v>1175</v>
-      </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16">
+      <c r="B31" s="103" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="7">
+        <v>1127</v>
+      </c>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7">
         <f t="shared" si="2"/>
-        <v>1175</v>
+        <v>1127</v>
       </c>
       <c r="F31" s="114"/>
       <c r="G31" s="17"/>
@@ -4558,8 +4545,8 @@
       <c r="Q31" s="22"/>
       <c r="S31" s="26"/>
       <c r="T31" s="26"/>
-      <c r="U31" s="283"/>
-      <c r="V31" s="283"/>
+      <c r="U31" s="199"/>
+      <c r="V31" s="199"/>
       <c r="Y31" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4570,7 +4557,7 @@
       </c>
       <c r="AA31" s="107"/>
       <c r="AB31" s="117">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="AB31:AD41" si="7">AB$7</f>
         <v>2.81</v>
       </c>
       <c r="AC31" s="118">
@@ -4589,18 +4576,23 @@
         <v>24</v>
       </c>
       <c r="AH31" s="107"/>
-      <c r="AI31" s="24">
+      <c r="AI31" s="15">
         <f t="shared" si="1"/>
         <v>27.44</v>
       </c>
     </row>
     <row r="32" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="113" t="s">
-        <v>130</v>
-      </c>
-      <c r="C32" s="16"/>
+        <v>106</v>
+      </c>
+      <c r="C32" s="16">
+        <v>1175</v>
+      </c>
       <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
+      <c r="E32" s="16">
+        <f t="shared" si="2"/>
+        <v>1175</v>
+      </c>
       <c r="F32" s="114"/>
       <c r="G32" s="17"/>
       <c r="H32" s="25"/>
@@ -4615,32 +4607,49 @@
       <c r="Q32" s="22"/>
       <c r="S32" s="26"/>
       <c r="T32" s="26"/>
-      <c r="U32" s="283"/>
-      <c r="V32" s="283"/>
-      <c r="Y32" s="115"/>
-      <c r="Z32" s="116"/>
+      <c r="U32" s="196"/>
+      <c r="V32" s="196"/>
+      <c r="Y32" s="115">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z32" s="116">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="AA32" s="107"/>
-      <c r="AB32" s="117"/>
-      <c r="AC32" s="118"/>
-      <c r="AD32" s="118"/>
-      <c r="AE32" s="119"/>
+      <c r="AB32" s="117">
+        <f t="shared" si="7"/>
+        <v>2.81</v>
+      </c>
+      <c r="AC32" s="118">
+        <v>0.63</v>
+      </c>
+      <c r="AD32" s="118">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AE32" s="119">
+        <f t="shared" si="4"/>
+        <v>3.44</v>
+      </c>
       <c r="AF32" s="120"/>
-      <c r="AG32" s="121"/>
+      <c r="AG32" s="121">
+        <v>24</v>
+      </c>
       <c r="AH32" s="107"/>
-      <c r="AI32" s="24"/>
+      <c r="AI32" s="24">
+        <f t="shared" si="1"/>
+        <v>27.44</v>
+      </c>
     </row>
     <row r="33" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="113" t="s">
-        <v>107</v>
-      </c>
-      <c r="C33" s="16">
-        <v>1127</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C33" s="16"/>
       <c r="D33" s="16"/>
-      <c r="E33" s="16">
-        <f t="shared" si="2"/>
-        <v>1127</v>
-      </c>
+      <c r="E33" s="16"/>
       <c r="F33" s="114"/>
       <c r="G33" s="17"/>
       <c r="H33" s="25"/>
@@ -4655,53 +4664,31 @@
       <c r="Q33" s="22"/>
       <c r="S33" s="26"/>
       <c r="T33" s="26"/>
-      <c r="U33" s="283"/>
-      <c r="V33" s="283"/>
-      <c r="Y33" s="115">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Z33" s="116">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="U33" s="196"/>
+      <c r="V33" s="196"/>
+      <c r="Y33" s="115"/>
+      <c r="Z33" s="116"/>
       <c r="AA33" s="107"/>
-      <c r="AB33" s="117">
-        <f t="shared" si="7"/>
-        <v>2.81</v>
-      </c>
-      <c r="AC33" s="118">
-        <v>0.63</v>
-      </c>
-      <c r="AD33" s="118">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AE33" s="119">
-        <f t="shared" si="4"/>
-        <v>3.44</v>
-      </c>
+      <c r="AB33" s="117"/>
+      <c r="AC33" s="118"/>
+      <c r="AD33" s="118"/>
+      <c r="AE33" s="119"/>
       <c r="AF33" s="120"/>
-      <c r="AG33" s="121">
-        <v>24</v>
-      </c>
+      <c r="AG33" s="121"/>
       <c r="AH33" s="107"/>
-      <c r="AI33" s="24">
-        <f t="shared" si="1"/>
-        <v>27.44</v>
-      </c>
+      <c r="AI33" s="24"/>
     </row>
     <row r="34" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="113" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C34" s="16">
-        <v>1534</v>
+        <v>1127</v>
       </c>
       <c r="D34" s="16"/>
       <c r="E34" s="16">
         <f t="shared" si="2"/>
-        <v>1534</v>
+        <v>1127</v>
       </c>
       <c r="F34" s="114"/>
       <c r="G34" s="17"/>
@@ -4717,8 +4704,8 @@
       <c r="Q34" s="22"/>
       <c r="S34" s="26"/>
       <c r="T34" s="26"/>
-      <c r="U34" s="283"/>
-      <c r="V34" s="283"/>
+      <c r="U34" s="196"/>
+      <c r="V34" s="196"/>
       <c r="Y34" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4754,33 +4741,33 @@
       </c>
     </row>
     <row r="35" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="122" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" s="27">
-        <v>1520</v>
-      </c>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27">
+      <c r="B35" s="113" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="16">
+        <v>1534</v>
+      </c>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16">
         <f t="shared" si="2"/>
-        <v>1520</v>
-      </c>
-      <c r="F35" s="123"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="124"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="35"/>
-      <c r="N35" s="35"/>
-      <c r="O35" s="35"/>
-      <c r="P35" s="32"/>
-      <c r="Q35" s="33"/>
-      <c r="S35" s="35"/>
-      <c r="T35" s="35"/>
-      <c r="U35" s="289"/>
-      <c r="V35" s="289"/>
+        <v>1534</v>
+      </c>
+      <c r="F35" s="114"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="61"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="26"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="22"/>
+      <c r="S35" s="26"/>
+      <c r="T35" s="26"/>
+      <c r="U35" s="196"/>
+      <c r="V35" s="196"/>
       <c r="Y35" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4810,39 +4797,39 @@
         <v>24</v>
       </c>
       <c r="AH35" s="107"/>
-      <c r="AI35" s="36">
+      <c r="AI35" s="24">
         <f t="shared" si="1"/>
         <v>27.44</v>
       </c>
     </row>
     <row r="36" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="103" t="s">
-        <v>110</v>
-      </c>
-      <c r="C36" s="7">
-        <v>650</v>
-      </c>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7">
+      <c r="B36" s="122" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" s="27">
+        <v>1520</v>
+      </c>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27">
         <f t="shared" si="2"/>
-        <v>650</v>
-      </c>
-      <c r="F36" s="125"/>
-      <c r="G36" s="37"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="39"/>
-      <c r="J36" s="40"/>
-      <c r="K36" s="64"/>
-      <c r="L36" s="40"/>
-      <c r="M36" s="44"/>
-      <c r="N36" s="44"/>
-      <c r="O36" s="44"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="42"/>
-      <c r="S36" s="44"/>
-      <c r="T36" s="44"/>
-      <c r="U36" s="292"/>
-      <c r="V36" s="292"/>
+        <v>1520</v>
+      </c>
+      <c r="F36" s="123"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="124"/>
+      <c r="L36" s="31"/>
+      <c r="M36" s="35"/>
+      <c r="N36" s="35"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="32"/>
+      <c r="Q36" s="33"/>
+      <c r="S36" s="35"/>
+      <c r="T36" s="35"/>
+      <c r="U36" s="197"/>
+      <c r="V36" s="197"/>
       <c r="Y36" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4872,39 +4859,39 @@
         <v>24</v>
       </c>
       <c r="AH36" s="107"/>
-      <c r="AI36" s="15">
+      <c r="AI36" s="36">
         <f t="shared" si="1"/>
         <v>27.44</v>
       </c>
     </row>
     <row r="37" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="113" t="s">
-        <v>111</v>
-      </c>
-      <c r="C37" s="46">
+      <c r="B37" s="103" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="7">
         <v>650</v>
       </c>
-      <c r="D37" s="46"/>
-      <c r="E37" s="46">
+      <c r="D37" s="7"/>
+      <c r="E37" s="7">
         <f t="shared" si="2"/>
         <v>650</v>
       </c>
-      <c r="F37" s="114"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="61"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="26"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="21"/>
-      <c r="Q37" s="22"/>
-      <c r="S37" s="26"/>
-      <c r="T37" s="26"/>
-      <c r="U37" s="289"/>
-      <c r="V37" s="289"/>
+      <c r="F37" s="125"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="40"/>
+      <c r="K37" s="64"/>
+      <c r="L37" s="40"/>
+      <c r="M37" s="44"/>
+      <c r="N37" s="44"/>
+      <c r="O37" s="44"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="42"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="202"/>
+      <c r="V37" s="202"/>
       <c r="Y37" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4934,39 +4921,39 @@
         <v>24</v>
       </c>
       <c r="AH37" s="107"/>
-      <c r="AI37" s="24">
+      <c r="AI37" s="15">
         <f t="shared" si="1"/>
         <v>27.44</v>
       </c>
     </row>
     <row r="38" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="122" t="s">
-        <v>112</v>
-      </c>
-      <c r="C38" s="45">
+      <c r="B38" s="113" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="46">
         <v>650</v>
       </c>
-      <c r="D38" s="45"/>
-      <c r="E38" s="45">
+      <c r="D38" s="46"/>
+      <c r="E38" s="46">
         <f t="shared" si="2"/>
         <v>650</v>
       </c>
-      <c r="F38" s="123"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="124"/>
-      <c r="L38" s="31"/>
-      <c r="M38" s="35"/>
-      <c r="N38" s="35"/>
-      <c r="O38" s="35"/>
-      <c r="P38" s="32"/>
-      <c r="Q38" s="33"/>
-      <c r="S38" s="35"/>
-      <c r="T38" s="35"/>
-      <c r="U38" s="290"/>
-      <c r="V38" s="290"/>
+      <c r="F38" s="114"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="61"/>
+      <c r="L38" s="20"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
+      <c r="P38" s="21"/>
+      <c r="Q38" s="22"/>
+      <c r="S38" s="26"/>
+      <c r="T38" s="26"/>
+      <c r="U38" s="197"/>
+      <c r="V38" s="197"/>
       <c r="Y38" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4996,39 +4983,39 @@
         <v>24</v>
       </c>
       <c r="AH38" s="107"/>
-      <c r="AI38" s="36">
+      <c r="AI38" s="24">
         <f t="shared" si="1"/>
         <v>27.44</v>
       </c>
     </row>
     <row r="39" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="126" t="s">
-        <v>113</v>
-      </c>
-      <c r="C39" s="47">
-        <v>1038</v>
-      </c>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47">
+      <c r="B39" s="122" t="s">
+        <v>112</v>
+      </c>
+      <c r="C39" s="45">
+        <v>650</v>
+      </c>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45">
         <f t="shared" si="2"/>
-        <v>1038</v>
-      </c>
-      <c r="F39" s="125"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="38"/>
-      <c r="I39" s="39"/>
-      <c r="J39" s="40"/>
-      <c r="K39" s="64"/>
-      <c r="L39" s="40"/>
-      <c r="M39" s="44"/>
-      <c r="N39" s="44"/>
-      <c r="O39" s="44"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="42"/>
-      <c r="S39" s="44"/>
-      <c r="T39" s="44"/>
-      <c r="U39" s="289"/>
-      <c r="V39" s="289"/>
+        <v>650</v>
+      </c>
+      <c r="F39" s="123"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="31"/>
+      <c r="K39" s="124"/>
+      <c r="L39" s="31"/>
+      <c r="M39" s="35"/>
+      <c r="N39" s="35"/>
+      <c r="O39" s="35"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="33"/>
+      <c r="S39" s="35"/>
+      <c r="T39" s="35"/>
+      <c r="U39" s="203"/>
+      <c r="V39" s="203"/>
       <c r="Y39" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5058,39 +5045,39 @@
         <v>24</v>
       </c>
       <c r="AH39" s="107"/>
-      <c r="AI39" s="48">
+      <c r="AI39" s="36">
         <f t="shared" si="1"/>
         <v>27.44</v>
       </c>
     </row>
     <row r="40" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="127" t="s">
-        <v>114</v>
-      </c>
-      <c r="C40" s="49">
+      <c r="B40" s="126" t="s">
+        <v>113</v>
+      </c>
+      <c r="C40" s="47">
         <v>1038</v>
       </c>
-      <c r="D40" s="49"/>
-      <c r="E40" s="49">
+      <c r="D40" s="47"/>
+      <c r="E40" s="47">
         <f t="shared" si="2"/>
         <v>1038</v>
       </c>
-      <c r="F40" s="114"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="61"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="26"/>
-      <c r="N40" s="26"/>
-      <c r="O40" s="26"/>
-      <c r="P40" s="21"/>
-      <c r="Q40" s="22"/>
-      <c r="S40" s="26"/>
-      <c r="T40" s="26"/>
-      <c r="U40" s="291"/>
-      <c r="V40" s="291"/>
+      <c r="F40" s="125"/>
+      <c r="G40" s="37"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="39"/>
+      <c r="J40" s="40"/>
+      <c r="K40" s="64"/>
+      <c r="L40" s="40"/>
+      <c r="M40" s="44"/>
+      <c r="N40" s="44"/>
+      <c r="O40" s="44"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="42"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="197"/>
+      <c r="V40" s="197"/>
       <c r="Y40" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5120,22 +5107,22 @@
         <v>24</v>
       </c>
       <c r="AH40" s="107"/>
-      <c r="AI40" s="50">
+      <c r="AI40" s="48">
         <f t="shared" si="1"/>
         <v>27.44</v>
       </c>
     </row>
     <row r="41" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="127" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C41" s="49">
-        <v>1728</v>
+        <v>1038</v>
       </c>
       <c r="D41" s="49"/>
       <c r="E41" s="49">
         <f t="shared" si="2"/>
-        <v>1728</v>
+        <v>1038</v>
       </c>
       <c r="F41" s="114"/>
       <c r="G41" s="17"/>
@@ -5151,8 +5138,8 @@
       <c r="Q41" s="22"/>
       <c r="S41" s="26"/>
       <c r="T41" s="26"/>
-      <c r="U41" s="291"/>
-      <c r="V41" s="291"/>
+      <c r="U41" s="199"/>
+      <c r="V41" s="199"/>
       <c r="Y41" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5163,14 +5150,19 @@
       </c>
       <c r="AA41" s="107"/>
       <c r="AB41" s="117">
-        <f>AB$7</f>
-        <v>5.25</v>
-      </c>
-      <c r="AC41" s="118"/>
-      <c r="AD41" s="118"/>
+        <f t="shared" si="7"/>
+        <v>2.81</v>
+      </c>
+      <c r="AC41" s="118">
+        <v>0.63</v>
+      </c>
+      <c r="AD41" s="118">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AE41" s="119">
         <f t="shared" si="4"/>
-        <v>5.25</v>
+        <v>3.44</v>
       </c>
       <c r="AF41" s="120"/>
       <c r="AG41" s="121">
@@ -5179,37 +5171,37 @@
       <c r="AH41" s="107"/>
       <c r="AI41" s="50">
         <f t="shared" si="1"/>
-        <v>29.25</v>
+        <v>27.44</v>
       </c>
     </row>
     <row r="42" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="176" t="s">
-        <v>116</v>
-      </c>
-      <c r="C42" s="27">
+      <c r="B42" s="127" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" s="49">
         <v>1728</v>
       </c>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27">
+      <c r="D42" s="49"/>
+      <c r="E42" s="49">
         <f t="shared" si="2"/>
         <v>1728</v>
       </c>
-      <c r="F42" s="123"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="124"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="35"/>
-      <c r="N42" s="35"/>
-      <c r="O42" s="35"/>
-      <c r="P42" s="32"/>
-      <c r="Q42" s="33"/>
-      <c r="S42" s="35"/>
-      <c r="T42" s="35"/>
-      <c r="U42" s="290"/>
-      <c r="V42" s="290"/>
+      <c r="F42" s="114"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="61"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="21"/>
+      <c r="Q42" s="22"/>
+      <c r="S42" s="26"/>
+      <c r="T42" s="26"/>
+      <c r="U42" s="199"/>
+      <c r="V42" s="199"/>
       <c r="Y42" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5220,51 +5212,53 @@
       </c>
       <c r="AA42" s="107"/>
       <c r="AB42" s="117">
-        <f>AB$6</f>
-        <v>2.81</v>
+        <f>AB$8</f>
+        <v>5.25</v>
       </c>
       <c r="AC42" s="118"/>
       <c r="AD42" s="118"/>
       <c r="AE42" s="119">
         <f t="shared" si="4"/>
-        <v>2.81</v>
+        <v>5.25</v>
       </c>
       <c r="AF42" s="120"/>
       <c r="AG42" s="121">
         <v>24</v>
       </c>
       <c r="AH42" s="107"/>
-      <c r="AI42" s="36">
+      <c r="AI42" s="50">
         <f t="shared" si="1"/>
-        <v>26.81</v>
-      </c>
-    </row>
-    <row r="43" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="126" t="s">
-        <v>40</v>
-      </c>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47">
+        <v>29.25</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="176" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" s="27">
+        <v>1728</v>
+      </c>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F43" s="114"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="61"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="23"/>
-      <c r="N43" s="26"/>
-      <c r="O43" s="26"/>
-      <c r="P43" s="21"/>
-      <c r="Q43" s="22"/>
-      <c r="S43" s="23"/>
-      <c r="T43" s="26"/>
-      <c r="U43" s="293"/>
-      <c r="V43" s="293"/>
+        <v>1728</v>
+      </c>
+      <c r="F43" s="123"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="124"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="35"/>
+      <c r="N43" s="35"/>
+      <c r="O43" s="35"/>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="33"/>
+      <c r="S43" s="35"/>
+      <c r="T43" s="35"/>
+      <c r="U43" s="203"/>
+      <c r="V43" s="203"/>
       <c r="Y43" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5274,30 +5268,33 @@
         <v>0</v>
       </c>
       <c r="AA43" s="107"/>
-      <c r="AB43" s="117"/>
+      <c r="AB43" s="117">
+        <f>AB$7</f>
+        <v>2.81</v>
+      </c>
       <c r="AC43" s="118"/>
       <c r="AD43" s="118"/>
       <c r="AE43" s="119">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AF43" s="120"/>
       <c r="AG43" s="121">
         <v>24</v>
       </c>
       <c r="AH43" s="107"/>
-      <c r="AI43" s="48">
+      <c r="AI43" s="36">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>26.81</v>
       </c>
     </row>
     <row r="44" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="127" t="s">
-        <v>41</v>
-      </c>
-      <c r="C44" s="51"/>
-      <c r="D44" s="51"/>
-      <c r="E44" s="51">
+      <c r="B44" s="126" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5315,8 +5312,8 @@
       <c r="Q44" s="22"/>
       <c r="S44" s="23"/>
       <c r="T44" s="26"/>
-      <c r="U44" s="294"/>
-      <c r="V44" s="294"/>
+      <c r="U44" s="200"/>
+      <c r="V44" s="200"/>
       <c r="Y44" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5338,37 +5335,37 @@
         <v>24</v>
       </c>
       <c r="AH44" s="107"/>
-      <c r="AI44" s="50">
+      <c r="AI44" s="48">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
     </row>
     <row r="45" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="127" t="s">
-        <v>42</v>
-      </c>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27">
+        <v>41</v>
+      </c>
+      <c r="C45" s="51"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="51">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F45" s="123"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="29"/>
-      <c r="I45" s="30"/>
-      <c r="J45" s="31"/>
-      <c r="K45" s="124"/>
-      <c r="L45" s="31"/>
-      <c r="M45" s="34"/>
-      <c r="N45" s="35"/>
-      <c r="O45" s="35"/>
-      <c r="P45" s="32"/>
-      <c r="Q45" s="33"/>
-      <c r="S45" s="34"/>
-      <c r="T45" s="35"/>
-      <c r="U45" s="282"/>
-      <c r="V45" s="282"/>
+      <c r="F45" s="114"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="61"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="23"/>
+      <c r="N45" s="26"/>
+      <c r="O45" s="26"/>
+      <c r="P45" s="21"/>
+      <c r="Q45" s="22"/>
+      <c r="S45" s="23"/>
+      <c r="T45" s="26"/>
+      <c r="U45" s="194"/>
+      <c r="V45" s="194"/>
       <c r="Y45" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5390,121 +5387,111 @@
         <v>24</v>
       </c>
       <c r="AH45" s="107"/>
-      <c r="AI45" s="36">
+      <c r="AI45" s="50">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="175" t="s">
-        <v>129</v>
-      </c>
-      <c r="C46" s="47"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="165"/>
-      <c r="G46" s="166"/>
-      <c r="H46" s="167"/>
-      <c r="I46" s="168"/>
-      <c r="J46" s="169"/>
-      <c r="K46" s="170"/>
-      <c r="L46" s="169"/>
-      <c r="M46" s="171"/>
-      <c r="N46" s="172"/>
-      <c r="O46" s="172"/>
-      <c r="P46" s="173"/>
-      <c r="Q46" s="174"/>
-      <c r="S46" s="171"/>
-      <c r="T46" s="172"/>
-      <c r="U46" s="292"/>
-      <c r="V46" s="292"/>
-      <c r="Y46" s="115"/>
-      <c r="Z46" s="116"/>
+    <row r="46" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="127" t="s">
+        <v>42</v>
+      </c>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="123"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="31"/>
+      <c r="K46" s="124"/>
+      <c r="L46" s="31"/>
+      <c r="M46" s="34"/>
+      <c r="N46" s="35"/>
+      <c r="O46" s="35"/>
+      <c r="P46" s="32"/>
+      <c r="Q46" s="33"/>
+      <c r="S46" s="34"/>
+      <c r="T46" s="35"/>
+      <c r="U46" s="201"/>
+      <c r="V46" s="201"/>
+      <c r="Y46" s="115">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z46" s="116">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="AA46" s="107"/>
       <c r="AB46" s="117"/>
       <c r="AC46" s="118"/>
       <c r="AD46" s="118"/>
-      <c r="AE46" s="119"/>
+      <c r="AE46" s="119">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="AF46" s="120"/>
-      <c r="AG46" s="121"/>
+      <c r="AG46" s="121">
+        <v>24</v>
+      </c>
       <c r="AH46" s="107"/>
-      <c r="AI46" s="48"/>
+      <c r="AI46" s="36">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
     </row>
     <row r="47" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="103" t="s">
+      <c r="B47" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="C47" s="47"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="165"/>
+      <c r="G47" s="166"/>
+      <c r="H47" s="167"/>
+      <c r="I47" s="168"/>
+      <c r="J47" s="169"/>
+      <c r="K47" s="170"/>
+      <c r="L47" s="169"/>
+      <c r="M47" s="171"/>
+      <c r="N47" s="172"/>
+      <c r="O47" s="172"/>
+      <c r="P47" s="173"/>
+      <c r="Q47" s="174"/>
+      <c r="S47" s="171"/>
+      <c r="T47" s="172"/>
+      <c r="U47" s="202"/>
+      <c r="V47" s="202"/>
+      <c r="Y47" s="115"/>
+      <c r="Z47" s="116"/>
+      <c r="AA47" s="107"/>
+      <c r="AB47" s="117"/>
+      <c r="AC47" s="118"/>
+      <c r="AD47" s="118"/>
+      <c r="AE47" s="119"/>
+      <c r="AF47" s="120"/>
+      <c r="AG47" s="121"/>
+      <c r="AH47" s="107"/>
+      <c r="AI47" s="48"/>
+    </row>
+    <row r="48" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="103" t="s">
         <v>117</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C48" s="7">
         <v>773</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D48" s="7">
         <v>120</v>
       </c>
-      <c r="E47" s="7">
+      <c r="E48" s="7">
         <f t="shared" si="2"/>
         <v>893</v>
-      </c>
-      <c r="F47" s="114"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="25"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="61"/>
-      <c r="L47" s="20"/>
-      <c r="M47" s="23"/>
-      <c r="N47" s="26"/>
-      <c r="O47" s="26"/>
-      <c r="P47" s="21"/>
-      <c r="Q47" s="22"/>
-      <c r="S47" s="23"/>
-      <c r="T47" s="26"/>
-      <c r="U47" s="283"/>
-      <c r="V47" s="283"/>
-      <c r="Y47" s="115">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Z47" s="116">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA47" s="107"/>
-      <c r="AB47" s="117">
-        <f>AB$2</f>
-        <v>8.76</v>
-      </c>
-      <c r="AC47" s="118">
-        <v>1.95</v>
-      </c>
-      <c r="AD47" s="118">
-        <f>AD$2</f>
-        <v>0</v>
-      </c>
-      <c r="AE47" s="119">
-        <f t="shared" si="4"/>
-        <v>10.709999999999999</v>
-      </c>
-      <c r="AF47" s="120"/>
-      <c r="AG47" s="121">
-        <v>24</v>
-      </c>
-      <c r="AH47" s="107"/>
-      <c r="AI47" s="15">
-        <f t="shared" si="1"/>
-        <v>34.71</v>
-      </c>
-    </row>
-    <row r="48" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="113" t="s">
-        <v>118</v>
-      </c>
-      <c r="C48" s="16">
-        <v>1038</v>
-      </c>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16">
-        <f t="shared" si="2"/>
-        <v>1038</v>
       </c>
       <c r="F48" s="114"/>
       <c r="G48" s="17"/>
@@ -5513,15 +5500,15 @@
       <c r="J48" s="20"/>
       <c r="K48" s="61"/>
       <c r="L48" s="20"/>
-      <c r="M48" s="26"/>
+      <c r="M48" s="23"/>
       <c r="N48" s="26"/>
       <c r="O48" s="26"/>
       <c r="P48" s="21"/>
       <c r="Q48" s="22"/>
-      <c r="S48" s="26"/>
+      <c r="S48" s="23"/>
       <c r="T48" s="26"/>
-      <c r="U48" s="283"/>
-      <c r="V48" s="283"/>
+      <c r="U48" s="196"/>
+      <c r="V48" s="196"/>
       <c r="Y48" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5532,43 +5519,41 @@
       </c>
       <c r="AA48" s="107"/>
       <c r="AB48" s="117">
-        <f>AB$6</f>
-        <v>2.81</v>
+        <f>AB$2</f>
+        <v>8.76</v>
       </c>
       <c r="AC48" s="118">
-        <v>0.63</v>
+        <v>1.95</v>
       </c>
       <c r="AD48" s="118">
-        <f>AD$6</f>
+        <f>AD$2</f>
         <v>0</v>
       </c>
       <c r="AE48" s="119">
         <f t="shared" si="4"/>
-        <v>3.44</v>
+        <v>10.709999999999999</v>
       </c>
       <c r="AF48" s="120"/>
       <c r="AG48" s="121">
         <v>24</v>
       </c>
       <c r="AH48" s="107"/>
-      <c r="AI48" s="24">
+      <c r="AI48" s="15">
         <f t="shared" si="1"/>
-        <v>27.44</v>
+        <v>34.71</v>
       </c>
     </row>
     <row r="49" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="113" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C49" s="16">
-        <v>791</v>
-      </c>
-      <c r="D49" s="16">
-        <v>120</v>
-      </c>
+        <v>1038</v>
+      </c>
+      <c r="D49" s="16"/>
       <c r="E49" s="16">
         <f t="shared" si="2"/>
-        <v>911</v>
+        <v>1038</v>
       </c>
       <c r="F49" s="114"/>
       <c r="G49" s="17"/>
@@ -5577,15 +5562,15 @@
       <c r="J49" s="20"/>
       <c r="K49" s="61"/>
       <c r="L49" s="20"/>
-      <c r="M49" s="23"/>
+      <c r="M49" s="26"/>
       <c r="N49" s="26"/>
       <c r="O49" s="26"/>
       <c r="P49" s="21"/>
       <c r="Q49" s="22"/>
-      <c r="S49" s="23"/>
+      <c r="S49" s="26"/>
       <c r="T49" s="26"/>
-      <c r="U49" s="283"/>
-      <c r="V49" s="283"/>
+      <c r="U49" s="196"/>
+      <c r="V49" s="196"/>
       <c r="Y49" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5596,19 +5581,19 @@
       </c>
       <c r="AA49" s="107"/>
       <c r="AB49" s="117">
-        <f>AB$2</f>
-        <v>8.76</v>
+        <f>AB$7</f>
+        <v>2.81</v>
       </c>
       <c r="AC49" s="118">
-        <v>1.95</v>
+        <v>0.63</v>
       </c>
       <c r="AD49" s="118">
-        <f>AD$2</f>
+        <f>AD$7</f>
         <v>0</v>
       </c>
       <c r="AE49" s="119">
         <f t="shared" si="4"/>
-        <v>10.709999999999999</v>
+        <v>3.44</v>
       </c>
       <c r="AF49" s="120"/>
       <c r="AG49" s="121">
@@ -5617,39 +5602,39 @@
       <c r="AH49" s="107"/>
       <c r="AI49" s="24">
         <f t="shared" si="1"/>
-        <v>34.71</v>
-      </c>
-    </row>
-    <row r="50" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="128" t="s">
+        <v>27.44</v>
+      </c>
+    </row>
+    <row r="50" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="113" t="s">
+        <v>119</v>
+      </c>
+      <c r="C50" s="16">
+        <v>791</v>
+      </c>
+      <c r="D50" s="16">
         <v>120</v>
       </c>
-      <c r="C50" s="52">
-        <v>1102</v>
-      </c>
-      <c r="D50" s="52">
-        <v>0</v>
-      </c>
-      <c r="E50" s="52">
+      <c r="E50" s="16">
         <f t="shared" si="2"/>
-        <v>1102</v>
-      </c>
-      <c r="F50" s="129"/>
-      <c r="G50" s="53"/>
-      <c r="H50" s="54"/>
-      <c r="I50" s="55"/>
-      <c r="J50" s="69"/>
-      <c r="K50" s="70"/>
-      <c r="L50" s="69"/>
-      <c r="M50" s="58"/>
-      <c r="N50" s="58"/>
-      <c r="O50" s="58"/>
-      <c r="P50" s="56"/>
-      <c r="Q50" s="57"/>
-      <c r="S50" s="58"/>
-      <c r="T50" s="58"/>
-      <c r="U50" s="293"/>
-      <c r="V50" s="293"/>
+        <v>911</v>
+      </c>
+      <c r="F50" s="114"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="25"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="61"/>
+      <c r="L50" s="20"/>
+      <c r="M50" s="23"/>
+      <c r="N50" s="26"/>
+      <c r="O50" s="26"/>
+      <c r="P50" s="21"/>
+      <c r="Q50" s="22"/>
+      <c r="S50" s="23"/>
+      <c r="T50" s="26"/>
+      <c r="U50" s="196"/>
+      <c r="V50" s="196"/>
       <c r="Y50" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5660,154 +5645,164 @@
       </c>
       <c r="AA50" s="107"/>
       <c r="AB50" s="117">
-        <f>AB$6</f>
-        <v>2.81</v>
+        <f>AB$2</f>
+        <v>8.76</v>
       </c>
       <c r="AC50" s="118">
-        <v>0.63</v>
+        <v>1.95</v>
       </c>
       <c r="AD50" s="118">
-        <f>AD$6</f>
+        <f>AD$2</f>
         <v>0</v>
       </c>
       <c r="AE50" s="119">
         <f t="shared" si="4"/>
-        <v>3.44</v>
+        <v>10.709999999999999</v>
       </c>
       <c r="AF50" s="120"/>
       <c r="AG50" s="121">
         <v>24</v>
       </c>
       <c r="AH50" s="107"/>
-      <c r="AI50" s="60">
+      <c r="AI50" s="24">
+        <f t="shared" si="1"/>
+        <v>34.71</v>
+      </c>
+    </row>
+    <row r="51" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="128" t="s">
+        <v>120</v>
+      </c>
+      <c r="C51" s="52">
+        <v>1102</v>
+      </c>
+      <c r="D51" s="52">
+        <v>0</v>
+      </c>
+      <c r="E51" s="52">
+        <f t="shared" si="2"/>
+        <v>1102</v>
+      </c>
+      <c r="F51" s="129"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="54"/>
+      <c r="I51" s="55"/>
+      <c r="J51" s="69"/>
+      <c r="K51" s="70"/>
+      <c r="L51" s="69"/>
+      <c r="M51" s="58"/>
+      <c r="N51" s="58"/>
+      <c r="O51" s="58"/>
+      <c r="P51" s="56"/>
+      <c r="Q51" s="57"/>
+      <c r="S51" s="58"/>
+      <c r="T51" s="58"/>
+      <c r="U51" s="200"/>
+      <c r="V51" s="200"/>
+      <c r="Y51" s="115">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z51" s="116">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA51" s="107"/>
+      <c r="AB51" s="117">
+        <f>AB$7</f>
+        <v>2.81</v>
+      </c>
+      <c r="AC51" s="118">
+        <v>0.63</v>
+      </c>
+      <c r="AD51" s="118">
+        <f>AD$7</f>
+        <v>0</v>
+      </c>
+      <c r="AE51" s="119">
+        <f t="shared" si="4"/>
+        <v>3.44</v>
+      </c>
+      <c r="AF51" s="120"/>
+      <c r="AG51" s="121">
+        <v>24</v>
+      </c>
+      <c r="AH51" s="107"/>
+      <c r="AI51" s="60">
         <f t="shared" si="1"/>
         <v>27.44</v>
       </c>
     </row>
-    <row r="51" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="103" t="s">
+    <row r="52" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7">
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F51" s="125"/>
-      <c r="G51" s="37"/>
-      <c r="H51" s="38"/>
-      <c r="I51" s="39"/>
-      <c r="J51" s="40"/>
-      <c r="K51" s="64"/>
-      <c r="L51" s="40"/>
-      <c r="M51" s="44"/>
-      <c r="N51" s="44"/>
-      <c r="O51" s="44"/>
-      <c r="P51" s="41"/>
-      <c r="Q51" s="42"/>
-      <c r="S51" s="44"/>
-      <c r="T51" s="44"/>
-      <c r="U51" s="294"/>
-      <c r="V51" s="294"/>
-      <c r="Y51" s="115">
+      <c r="F52" s="125"/>
+      <c r="G52" s="37"/>
+      <c r="H52" s="38"/>
+      <c r="I52" s="39"/>
+      <c r="J52" s="40"/>
+      <c r="K52" s="64"/>
+      <c r="L52" s="40"/>
+      <c r="M52" s="44"/>
+      <c r="N52" s="44"/>
+      <c r="O52" s="44"/>
+      <c r="P52" s="41"/>
+      <c r="Q52" s="42"/>
+      <c r="S52" s="44"/>
+      <c r="T52" s="44"/>
+      <c r="U52" s="194"/>
+      <c r="V52" s="194"/>
+      <c r="Y52" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z51" s="116">
+      <c r="Z52" s="116">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA51" s="107"/>
-      <c r="AB51" s="117">
+      <c r="AA52" s="107"/>
+      <c r="AB52" s="117">
         <v>1.69</v>
       </c>
-      <c r="AC51" s="118">
+      <c r="AC52" s="118">
         <v>1.69</v>
       </c>
-      <c r="AD51" s="118">
+      <c r="AD52" s="118">
         <v>1.69</v>
       </c>
-      <c r="AE51" s="119">
+      <c r="AE52" s="119">
         <f t="shared" si="4"/>
         <v>5.07</v>
       </c>
-      <c r="AF51" s="120"/>
-      <c r="AG51" s="121"/>
-      <c r="AH51" s="107"/>
-      <c r="AI51" s="15">
+      <c r="AF52" s="120"/>
+      <c r="AG52" s="121"/>
+      <c r="AH52" s="107"/>
+      <c r="AI52" s="15">
         <f t="shared" si="1"/>
         <v>5.07</v>
       </c>
     </row>
-    <row r="52" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="113" t="s">
+    <row r="53" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="113" t="s">
         <v>121</v>
       </c>
-      <c r="C52" s="16">
+      <c r="C53" s="16">
         <v>205</v>
       </c>
-      <c r="D52" s="16">
+      <c r="D53" s="16">
         <v>78</v>
       </c>
-      <c r="E52" s="16">
+      <c r="E53" s="16">
         <f t="shared" si="2"/>
         <v>283</v>
       </c>
-      <c r="F52" s="114"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="25"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="20"/>
-      <c r="K52" s="61"/>
-      <c r="L52" s="20"/>
-      <c r="M52" s="23"/>
-      <c r="N52" s="23"/>
-      <c r="O52" s="23"/>
-      <c r="P52" s="21"/>
-      <c r="Q52" s="22"/>
-      <c r="S52" s="23"/>
-      <c r="T52" s="23"/>
-      <c r="U52" s="282"/>
-      <c r="V52" s="282"/>
-      <c r="Y52" s="115">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Z52" s="116">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA52" s="107"/>
-      <c r="AB52" s="117">
-        <f t="shared" ref="AB52:AB61" si="8">AB$1</f>
-        <v>7.68</v>
-      </c>
-      <c r="AC52" s="118">
-        <v>1.72</v>
-      </c>
-      <c r="AD52" s="118"/>
-      <c r="AE52" s="119">
-        <f t="shared" si="4"/>
-        <v>9.4</v>
-      </c>
-      <c r="AF52" s="120"/>
-      <c r="AG52" s="121">
-        <v>20.5</v>
-      </c>
-      <c r="AH52" s="107"/>
-      <c r="AI52" s="24">
-        <f t="shared" si="1"/>
-        <v>29.9</v>
-      </c>
-    </row>
-    <row r="53" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="113" t="s">
-        <v>122</v>
-      </c>
-      <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
       <c r="F53" s="114"/>
       <c r="G53" s="17"/>
       <c r="H53" s="25"/>
@@ -5815,30 +5810,49 @@
       <c r="J53" s="20"/>
       <c r="K53" s="61"/>
       <c r="L53" s="20"/>
-      <c r="M53" s="43"/>
+      <c r="M53" s="23"/>
       <c r="N53" s="23"/>
       <c r="O53" s="23"/>
       <c r="P53" s="21"/>
       <c r="Q53" s="22"/>
       <c r="S53" s="23"/>
       <c r="T53" s="23"/>
-      <c r="U53" s="291"/>
-      <c r="V53" s="291"/>
-      <c r="Y53" s="115"/>
-      <c r="Z53" s="116"/>
+      <c r="U53" s="201"/>
+      <c r="V53" s="201"/>
+      <c r="Y53" s="115">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z53" s="116">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="AA53" s="107"/>
-      <c r="AB53" s="117"/>
-      <c r="AC53" s="118"/>
+      <c r="AB53" s="117">
+        <f t="shared" ref="AB53:AB62" si="8">AB$1</f>
+        <v>7.68</v>
+      </c>
+      <c r="AC53" s="118">
+        <v>1.72</v>
+      </c>
       <c r="AD53" s="118"/>
-      <c r="AE53" s="119"/>
+      <c r="AE53" s="119">
+        <f t="shared" si="4"/>
+        <v>9.4</v>
+      </c>
       <c r="AF53" s="120"/>
-      <c r="AG53" s="121"/>
+      <c r="AG53" s="121">
+        <v>20.5</v>
+      </c>
       <c r="AH53" s="107"/>
-      <c r="AI53" s="24"/>
+      <c r="AI53" s="24">
+        <f t="shared" si="1"/>
+        <v>29.9</v>
+      </c>
     </row>
     <row r="54" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="113" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C54" s="16"/>
       <c r="D54" s="16"/>
@@ -5857,8 +5871,8 @@
       <c r="Q54" s="22"/>
       <c r="S54" s="23"/>
       <c r="T54" s="23"/>
-      <c r="U54" s="291"/>
-      <c r="V54" s="291"/>
+      <c r="U54" s="199"/>
+      <c r="V54" s="199"/>
       <c r="Y54" s="115"/>
       <c r="Z54" s="116"/>
       <c r="AA54" s="107"/>
@@ -5873,7 +5887,7 @@
     </row>
     <row r="55" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="113" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
@@ -5892,8 +5906,8 @@
       <c r="Q55" s="22"/>
       <c r="S55" s="23"/>
       <c r="T55" s="23"/>
-      <c r="U55" s="283"/>
-      <c r="V55" s="283"/>
+      <c r="U55" s="199"/>
+      <c r="V55" s="199"/>
       <c r="Y55" s="115"/>
       <c r="Z55" s="116"/>
       <c r="AA55" s="107"/>
@@ -5908,18 +5922,11 @@
     </row>
     <row r="56" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="113" t="s">
-        <v>125</v>
-      </c>
-      <c r="C56" s="16">
-        <v>205</v>
-      </c>
-      <c r="D56" s="16">
-        <v>78</v>
-      </c>
-      <c r="E56" s="16">
-        <f t="shared" si="2"/>
-        <v>283</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="C56" s="16"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="16"/>
       <c r="F56" s="114"/>
       <c r="G56" s="17"/>
       <c r="H56" s="25"/>
@@ -5927,53 +5934,41 @@
       <c r="J56" s="20"/>
       <c r="K56" s="61"/>
       <c r="L56" s="20"/>
-      <c r="M56" s="44"/>
-      <c r="N56" s="26"/>
+      <c r="M56" s="43"/>
+      <c r="N56" s="23"/>
       <c r="O56" s="23"/>
       <c r="P56" s="21"/>
       <c r="Q56" s="22"/>
       <c r="S56" s="23"/>
-      <c r="T56" s="26"/>
-      <c r="U56" s="289"/>
-      <c r="V56" s="289"/>
-      <c r="Y56" s="115">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Z56" s="116">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="T56" s="23"/>
+      <c r="U56" s="196"/>
+      <c r="V56" s="196"/>
+      <c r="Y56" s="115"/>
+      <c r="Z56" s="116"/>
       <c r="AA56" s="107"/>
-      <c r="AB56" s="117">
-        <f t="shared" si="8"/>
-        <v>7.68</v>
-      </c>
-      <c r="AC56" s="118">
-        <v>1.72</v>
-      </c>
+      <c r="AB56" s="117"/>
+      <c r="AC56" s="118"/>
       <c r="AD56" s="118"/>
-      <c r="AE56" s="119">
-        <f t="shared" si="4"/>
-        <v>9.4</v>
-      </c>
+      <c r="AE56" s="119"/>
       <c r="AF56" s="120"/>
-      <c r="AG56" s="121">
-        <v>20.5</v>
-      </c>
+      <c r="AG56" s="121"/>
       <c r="AH56" s="107"/>
-      <c r="AI56" s="24">
-        <f t="shared" si="1"/>
-        <v>29.9</v>
-      </c>
+      <c r="AI56" s="24"/>
     </row>
     <row r="57" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="113" t="s">
-        <v>126</v>
-      </c>
-      <c r="C57" s="16"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
+        <v>125</v>
+      </c>
+      <c r="C57" s="16">
+        <v>205</v>
+      </c>
+      <c r="D57" s="16">
+        <v>78</v>
+      </c>
+      <c r="E57" s="16">
+        <f t="shared" si="2"/>
+        <v>283</v>
+      </c>
       <c r="F57" s="114"/>
       <c r="G57" s="17"/>
       <c r="H57" s="25"/>
@@ -5988,23 +5983,42 @@
       <c r="Q57" s="22"/>
       <c r="S57" s="23"/>
       <c r="T57" s="26"/>
-      <c r="U57" s="291"/>
-      <c r="V57" s="291"/>
-      <c r="Y57" s="115"/>
-      <c r="Z57" s="116"/>
+      <c r="U57" s="197"/>
+      <c r="V57" s="197"/>
+      <c r="Y57" s="115">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z57" s="116">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="AA57" s="107"/>
-      <c r="AB57" s="117"/>
-      <c r="AC57" s="118"/>
+      <c r="AB57" s="117">
+        <f t="shared" si="8"/>
+        <v>7.68</v>
+      </c>
+      <c r="AC57" s="118">
+        <v>1.72</v>
+      </c>
       <c r="AD57" s="118"/>
-      <c r="AE57" s="119"/>
+      <c r="AE57" s="119">
+        <f t="shared" si="4"/>
+        <v>9.4</v>
+      </c>
       <c r="AF57" s="120"/>
-      <c r="AG57" s="121"/>
+      <c r="AG57" s="121">
+        <v>20.5</v>
+      </c>
       <c r="AH57" s="107"/>
-      <c r="AI57" s="24"/>
+      <c r="AI57" s="24">
+        <f t="shared" si="1"/>
+        <v>29.9</v>
+      </c>
     </row>
     <row r="58" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="113" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C58" s="16"/>
       <c r="D58" s="16"/>
@@ -6023,8 +6037,8 @@
       <c r="Q58" s="22"/>
       <c r="S58" s="23"/>
       <c r="T58" s="26"/>
-      <c r="U58" s="291"/>
-      <c r="V58" s="291"/>
+      <c r="U58" s="199"/>
+      <c r="V58" s="199"/>
       <c r="Y58" s="115"/>
       <c r="Z58" s="116"/>
       <c r="AA58" s="107"/>
@@ -6039,7 +6053,7 @@
     </row>
     <row r="59" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="113" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C59" s="16"/>
       <c r="D59" s="16"/>
@@ -6058,8 +6072,8 @@
       <c r="Q59" s="22"/>
       <c r="S59" s="23"/>
       <c r="T59" s="26"/>
-      <c r="U59" s="283"/>
-      <c r="V59" s="283"/>
+      <c r="U59" s="199"/>
+      <c r="V59" s="199"/>
       <c r="Y59" s="115"/>
       <c r="Z59" s="116"/>
       <c r="AA59" s="107"/>
@@ -6073,7 +6087,9 @@
       <c r="AI59" s="24"/>
     </row>
     <row r="60" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="113"/>
+      <c r="B60" s="113" t="s">
+        <v>128</v>
+      </c>
       <c r="C60" s="16"/>
       <c r="D60" s="16"/>
       <c r="E60" s="16"/>
@@ -6091,8 +6107,8 @@
       <c r="Q60" s="22"/>
       <c r="S60" s="23"/>
       <c r="T60" s="26"/>
-      <c r="U60" s="289"/>
-      <c r="V60" s="289"/>
+      <c r="U60" s="196"/>
+      <c r="V60" s="196"/>
       <c r="Y60" s="115"/>
       <c r="Z60" s="116"/>
       <c r="AA60" s="107"/>
@@ -6105,74 +6121,46 @@
       <c r="AH60" s="107"/>
       <c r="AI60" s="24"/>
     </row>
-    <row r="61" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="113"/>
-      <c r="C61" s="16">
-        <v>205</v>
-      </c>
-      <c r="D61" s="16">
-        <v>78</v>
-      </c>
-      <c r="E61" s="16">
-        <f t="shared" si="2"/>
-        <v>283</v>
-      </c>
+      <c r="C61" s="16"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="16"/>
       <c r="F61" s="114"/>
       <c r="G61" s="17"/>
-      <c r="H61" s="177"/>
+      <c r="H61" s="25"/>
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
       <c r="K61" s="61"/>
       <c r="L61" s="20"/>
-      <c r="M61" s="59"/>
+      <c r="M61" s="44"/>
       <c r="N61" s="26"/>
-      <c r="O61" s="180"/>
-      <c r="P61" s="181"/>
+      <c r="O61" s="23"/>
+      <c r="P61" s="21"/>
       <c r="Q61" s="22"/>
-      <c r="S61" s="180"/>
-      <c r="T61" s="59"/>
-      <c r="U61" s="295"/>
-      <c r="V61" s="295"/>
-      <c r="Y61" s="115">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Z61" s="116">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="S61" s="23"/>
+      <c r="T61" s="26"/>
+      <c r="U61" s="197"/>
+      <c r="V61" s="197"/>
+      <c r="Y61" s="115"/>
+      <c r="Z61" s="116"/>
       <c r="AA61" s="107"/>
-      <c r="AB61" s="117">
-        <f t="shared" si="8"/>
-        <v>7.68</v>
-      </c>
-      <c r="AC61" s="118">
-        <v>1.72</v>
-      </c>
+      <c r="AB61" s="117"/>
+      <c r="AC61" s="118"/>
       <c r="AD61" s="118"/>
-      <c r="AE61" s="119">
-        <f t="shared" si="4"/>
-        <v>9.4</v>
-      </c>
+      <c r="AE61" s="119"/>
       <c r="AF61" s="120"/>
-      <c r="AG61" s="121">
-        <v>20.5</v>
-      </c>
+      <c r="AG61" s="121"/>
       <c r="AH61" s="107"/>
-      <c r="AI61" s="24">
-        <f t="shared" si="1"/>
-        <v>29.9</v>
-      </c>
-    </row>
-    <row r="62" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="113" t="s">
-        <v>44</v>
-      </c>
+      <c r="AI61" s="24"/>
+    </row>
+    <row r="62" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="113"/>
       <c r="C62" s="16">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="D62" s="16">
-        <v>283</v>
+        <v>78</v>
       </c>
       <c r="E62" s="16">
         <f t="shared" si="2"/>
@@ -6180,20 +6168,20 @@
       </c>
       <c r="F62" s="114"/>
       <c r="G62" s="17"/>
-      <c r="H62" s="38"/>
+      <c r="H62" s="177"/>
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
       <c r="K62" s="61"/>
       <c r="L62" s="20"/>
-      <c r="M62" s="44"/>
+      <c r="M62" s="59"/>
       <c r="N62" s="26"/>
-      <c r="O62" s="43"/>
-      <c r="P62" s="41"/>
+      <c r="O62" s="180"/>
+      <c r="P62" s="181"/>
       <c r="Q62" s="22"/>
-      <c r="S62" s="43"/>
-      <c r="T62" s="44"/>
-      <c r="U62" s="294"/>
-      <c r="V62" s="294"/>
+      <c r="S62" s="180"/>
+      <c r="T62" s="59"/>
+      <c r="U62" s="198"/>
+      <c r="V62" s="198"/>
       <c r="Y62" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6204,15 +6192,16 @@
       </c>
       <c r="AA62" s="107"/>
       <c r="AB62" s="117">
-        <v>1.69</v>
+        <f t="shared" si="8"/>
+        <v>7.68</v>
       </c>
       <c r="AC62" s="118">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AD62" s="118"/>
       <c r="AE62" s="119">
         <f t="shared" si="4"/>
-        <v>3.38</v>
+        <v>9.4</v>
       </c>
       <c r="AF62" s="120"/>
       <c r="AG62" s="121">
@@ -6221,39 +6210,39 @@
       <c r="AH62" s="107"/>
       <c r="AI62" s="24">
         <f t="shared" si="1"/>
-        <v>23.88</v>
-      </c>
-    </row>
-    <row r="63" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="122" t="s">
-        <v>45</v>
-      </c>
-      <c r="C63" s="27">
-        <v>205</v>
-      </c>
-      <c r="D63" s="27">
-        <v>78</v>
-      </c>
-      <c r="E63" s="27">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="63" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="113" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="16">
+        <v>0</v>
+      </c>
+      <c r="D63" s="16">
+        <v>283</v>
+      </c>
+      <c r="E63" s="16">
         <f t="shared" si="2"/>
         <v>283</v>
       </c>
-      <c r="F63" s="123"/>
-      <c r="G63" s="28"/>
-      <c r="H63" s="29"/>
-      <c r="I63" s="30"/>
-      <c r="J63" s="31"/>
-      <c r="K63" s="124"/>
-      <c r="L63" s="31"/>
+      <c r="F63" s="114"/>
+      <c r="G63" s="17"/>
+      <c r="H63" s="38"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="20"/>
+      <c r="K63" s="61"/>
+      <c r="L63" s="20"/>
       <c r="M63" s="44"/>
-      <c r="N63" s="35"/>
-      <c r="O63" s="34"/>
-      <c r="P63" s="32"/>
-      <c r="Q63" s="33"/>
-      <c r="S63" s="34"/>
-      <c r="T63" s="35"/>
-      <c r="U63" s="294"/>
-      <c r="V63" s="294"/>
+      <c r="N63" s="26"/>
+      <c r="O63" s="43"/>
+      <c r="P63" s="41"/>
+      <c r="Q63" s="22"/>
+      <c r="S63" s="43"/>
+      <c r="T63" s="44"/>
+      <c r="U63" s="194"/>
+      <c r="V63" s="194"/>
       <c r="Y63" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6264,117 +6253,115 @@
       </c>
       <c r="AA63" s="107"/>
       <c r="AB63" s="117">
-        <f>AB$1</f>
-        <v>7.68</v>
+        <v>1.69</v>
       </c>
       <c r="AC63" s="118">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AD63" s="118"/>
       <c r="AE63" s="119">
         <f t="shared" si="4"/>
-        <v>9.4</v>
+        <v>3.38</v>
       </c>
       <c r="AF63" s="120"/>
       <c r="AG63" s="121">
         <v>20.5</v>
       </c>
       <c r="AH63" s="107"/>
-      <c r="AI63" s="36">
+      <c r="AI63" s="24">
+        <f t="shared" si="1"/>
+        <v>23.88</v>
+      </c>
+    </row>
+    <row r="64" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="122" t="s">
+        <v>45</v>
+      </c>
+      <c r="C64" s="27">
+        <v>205</v>
+      </c>
+      <c r="D64" s="27">
+        <v>78</v>
+      </c>
+      <c r="E64" s="27">
+        <f t="shared" si="2"/>
+        <v>283</v>
+      </c>
+      <c r="F64" s="123"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="29"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="31"/>
+      <c r="K64" s="124"/>
+      <c r="L64" s="31"/>
+      <c r="M64" s="44"/>
+      <c r="N64" s="35"/>
+      <c r="O64" s="34"/>
+      <c r="P64" s="32"/>
+      <c r="Q64" s="33"/>
+      <c r="S64" s="34"/>
+      <c r="T64" s="35"/>
+      <c r="U64" s="194"/>
+      <c r="V64" s="194"/>
+      <c r="Y64" s="115">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z64" s="116">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA64" s="107"/>
+      <c r="AB64" s="117">
+        <f>AB$1</f>
+        <v>7.68</v>
+      </c>
+      <c r="AC64" s="118">
+        <v>1.72</v>
+      </c>
+      <c r="AD64" s="118"/>
+      <c r="AE64" s="119">
+        <f t="shared" si="4"/>
+        <v>9.4</v>
+      </c>
+      <c r="AF64" s="120"/>
+      <c r="AG64" s="121">
+        <v>20.5</v>
+      </c>
+      <c r="AH64" s="107"/>
+      <c r="AI64" s="36">
         <f t="shared" si="1"/>
         <v>29.9</v>
       </c>
     </row>
-    <row r="64" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="103" t="s">
+    <row r="65" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="103" t="s">
         <v>46</v>
       </c>
-      <c r="C64" s="7">
+      <c r="C65" s="7">
         <v>1534</v>
       </c>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7">
+      <c r="D65" s="7"/>
+      <c r="E65" s="7">
         <f t="shared" si="2"/>
         <v>1534</v>
       </c>
-      <c r="F64" s="125"/>
-      <c r="G64" s="37"/>
-      <c r="H64" s="38"/>
-      <c r="I64" s="39"/>
-      <c r="J64" s="40"/>
-      <c r="K64" s="64"/>
-      <c r="L64" s="40"/>
-      <c r="M64" s="44"/>
-      <c r="N64" s="44"/>
-      <c r="O64" s="44"/>
-      <c r="P64" s="41"/>
-      <c r="Q64" s="42"/>
-      <c r="S64" s="44"/>
-      <c r="T64" s="44"/>
-      <c r="U64" s="294"/>
-      <c r="V64" s="294"/>
-      <c r="Y64" s="115">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Z64" s="116">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA64" s="107"/>
-      <c r="AB64" s="117">
-        <f t="shared" ref="AB64:AD70" si="9">AB$6</f>
-        <v>2.81</v>
-      </c>
-      <c r="AC64" s="118">
-        <v>0.63</v>
-      </c>
-      <c r="AD64" s="118">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AE64" s="119">
-        <f t="shared" si="4"/>
-        <v>3.44</v>
-      </c>
-      <c r="AF64" s="120"/>
-      <c r="AG64" s="121">
-        <v>24</v>
-      </c>
-      <c r="AH64" s="107"/>
-      <c r="AI64" s="15">
-        <f t="shared" si="1"/>
-        <v>27.44</v>
-      </c>
-    </row>
-    <row r="65" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="C65" s="16">
-        <v>1520</v>
-      </c>
-      <c r="D65" s="16"/>
-      <c r="E65" s="16">
-        <f t="shared" si="2"/>
-        <v>1520</v>
-      </c>
-      <c r="F65" s="114"/>
-      <c r="G65" s="17"/>
-      <c r="H65" s="25"/>
-      <c r="I65" s="19"/>
-      <c r="J65" s="20"/>
-      <c r="K65" s="61"/>
-      <c r="L65" s="20"/>
-      <c r="M65" s="26"/>
-      <c r="N65" s="26"/>
+      <c r="F65" s="125"/>
+      <c r="G65" s="37"/>
+      <c r="H65" s="38"/>
+      <c r="I65" s="39"/>
+      <c r="J65" s="40"/>
+      <c r="K65" s="64"/>
+      <c r="L65" s="40"/>
+      <c r="M65" s="44"/>
+      <c r="N65" s="44"/>
       <c r="O65" s="44"/>
-      <c r="P65" s="21"/>
-      <c r="Q65" s="22"/>
-      <c r="S65" s="26"/>
-      <c r="T65" s="26"/>
-      <c r="U65" s="294"/>
-      <c r="V65" s="294"/>
+      <c r="P65" s="41"/>
+      <c r="Q65" s="42"/>
+      <c r="S65" s="44"/>
+      <c r="T65" s="44"/>
+      <c r="U65" s="194"/>
+      <c r="V65" s="194"/>
       <c r="Y65" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6385,7 +6372,7 @@
       </c>
       <c r="AA65" s="107"/>
       <c r="AB65" s="117">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="AB65:AD71" si="9">AB$7</f>
         <v>2.81</v>
       </c>
       <c r="AC65" s="118">
@@ -6404,22 +6391,22 @@
         <v>24</v>
       </c>
       <c r="AH65" s="107"/>
-      <c r="AI65" s="24">
+      <c r="AI65" s="15">
         <f t="shared" si="1"/>
         <v>27.44</v>
       </c>
     </row>
     <row r="66" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="113" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C66" s="16">
-        <v>1038</v>
+        <v>1520</v>
       </c>
       <c r="D66" s="16"/>
       <c r="E66" s="16">
         <f t="shared" si="2"/>
-        <v>1038</v>
+        <v>1520</v>
       </c>
       <c r="F66" s="114"/>
       <c r="G66" s="17"/>
@@ -6435,8 +6422,8 @@
       <c r="Q66" s="22"/>
       <c r="S66" s="26"/>
       <c r="T66" s="26"/>
-      <c r="U66" s="294"/>
-      <c r="V66" s="294"/>
+      <c r="U66" s="194"/>
+      <c r="V66" s="194"/>
       <c r="Y66" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6473,7 +6460,7 @@
     </row>
     <row r="67" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="113" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C67" s="16">
         <v>1038</v>
@@ -6497,8 +6484,8 @@
       <c r="Q67" s="22"/>
       <c r="S67" s="26"/>
       <c r="T67" s="26"/>
-      <c r="U67" s="294"/>
-      <c r="V67" s="294"/>
+      <c r="U67" s="194"/>
+      <c r="V67" s="194"/>
       <c r="Y67" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6535,15 +6522,15 @@
     </row>
     <row r="68" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="113" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C68" s="16">
-        <v>1127</v>
+        <v>1038</v>
       </c>
       <c r="D68" s="16"/>
       <c r="E68" s="16">
         <f t="shared" si="2"/>
-        <v>1127</v>
+        <v>1038</v>
       </c>
       <c r="F68" s="114"/>
       <c r="G68" s="17"/>
@@ -6559,8 +6546,8 @@
       <c r="Q68" s="22"/>
       <c r="S68" s="26"/>
       <c r="T68" s="26"/>
-      <c r="U68" s="294"/>
-      <c r="V68" s="294"/>
+      <c r="U68" s="194"/>
+      <c r="V68" s="194"/>
       <c r="Y68" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6597,15 +6584,15 @@
     </row>
     <row r="69" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="113" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C69" s="16">
-        <v>1175</v>
+        <v>1127</v>
       </c>
       <c r="D69" s="16"/>
       <c r="E69" s="16">
         <f t="shared" si="2"/>
-        <v>1175</v>
+        <v>1127</v>
       </c>
       <c r="F69" s="114"/>
       <c r="G69" s="17"/>
@@ -6621,8 +6608,8 @@
       <c r="Q69" s="22"/>
       <c r="S69" s="26"/>
       <c r="T69" s="26"/>
-      <c r="U69" s="294"/>
-      <c r="V69" s="294"/>
+      <c r="U69" s="194"/>
+      <c r="V69" s="194"/>
       <c r="Y69" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6657,231 +6644,258 @@
         <v>27.44</v>
       </c>
     </row>
-    <row r="70" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="128" t="s">
+    <row r="70" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="C70" s="16">
+        <v>1175</v>
+      </c>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16">
+        <f t="shared" si="2"/>
+        <v>1175</v>
+      </c>
+      <c r="F70" s="114"/>
+      <c r="G70" s="17"/>
+      <c r="H70" s="25"/>
+      <c r="I70" s="19"/>
+      <c r="J70" s="20"/>
+      <c r="K70" s="61"/>
+      <c r="L70" s="20"/>
+      <c r="M70" s="26"/>
+      <c r="N70" s="26"/>
+      <c r="O70" s="44"/>
+      <c r="P70" s="21"/>
+      <c r="Q70" s="22"/>
+      <c r="S70" s="26"/>
+      <c r="T70" s="26"/>
+      <c r="U70" s="194"/>
+      <c r="V70" s="194"/>
+      <c r="Y70" s="115">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z70" s="116">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA70" s="107"/>
+      <c r="AB70" s="117">
+        <f t="shared" si="9"/>
+        <v>2.81</v>
+      </c>
+      <c r="AC70" s="118">
+        <v>0.63</v>
+      </c>
+      <c r="AD70" s="118">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AE70" s="119">
+        <f t="shared" si="4"/>
+        <v>3.44</v>
+      </c>
+      <c r="AF70" s="120"/>
+      <c r="AG70" s="121">
+        <v>24</v>
+      </c>
+      <c r="AH70" s="107"/>
+      <c r="AI70" s="24">
+        <f t="shared" si="1"/>
+        <v>27.44</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" s="102" customFormat="1" ht="32.1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="128" t="s">
         <v>52</v>
       </c>
-      <c r="C70" s="52">
+      <c r="C71" s="52">
         <v>1127</v>
       </c>
-      <c r="D70" s="52"/>
-      <c r="E70" s="52">
+      <c r="D71" s="52"/>
+      <c r="E71" s="52">
         <f t="shared" si="2"/>
         <v>1127</v>
       </c>
-      <c r="F70" s="129"/>
-      <c r="G70" s="53"/>
-      <c r="H70" s="54"/>
-      <c r="I70" s="55"/>
-      <c r="J70" s="69"/>
-      <c r="K70" s="70"/>
-      <c r="L70" s="69"/>
-      <c r="M70" s="58"/>
-      <c r="N70" s="58"/>
-      <c r="O70" s="130"/>
-      <c r="P70" s="56"/>
-      <c r="Q70" s="57"/>
-      <c r="S70" s="58"/>
-      <c r="T70" s="58"/>
-      <c r="U70" s="294"/>
-      <c r="V70" s="294"/>
-      <c r="Y70" s="131">
+      <c r="F71" s="129"/>
+      <c r="G71" s="53"/>
+      <c r="H71" s="54"/>
+      <c r="I71" s="55"/>
+      <c r="J71" s="69"/>
+      <c r="K71" s="70"/>
+      <c r="L71" s="69"/>
+      <c r="M71" s="58"/>
+      <c r="N71" s="58"/>
+      <c r="O71" s="130"/>
+      <c r="P71" s="56"/>
+      <c r="Q71" s="57"/>
+      <c r="S71" s="58"/>
+      <c r="T71" s="58"/>
+      <c r="U71" s="194"/>
+      <c r="V71" s="194"/>
+      <c r="Y71" s="131">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z70" s="132">
+      <c r="Z71" s="132">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA70" s="107"/>
-      <c r="AB70" s="133">
+      <c r="AA71" s="107"/>
+      <c r="AB71" s="133">
         <f t="shared" si="9"/>
         <v>2.81</v>
       </c>
-      <c r="AC70" s="134">
+      <c r="AC71" s="134">
         <v>0.63</v>
       </c>
-      <c r="AD70" s="134">
+      <c r="AD71" s="134">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AE70" s="135">
+      <c r="AE71" s="135">
         <f t="shared" si="4"/>
         <v>3.44</v>
       </c>
-      <c r="AF70" s="120"/>
-      <c r="AG70" s="136">
+      <c r="AF71" s="120"/>
+      <c r="AG71" s="136">
         <v>24</v>
       </c>
-      <c r="AH70" s="107"/>
-      <c r="AI70" s="60">
+      <c r="AH71" s="107"/>
+      <c r="AI71" s="60">
         <f t="shared" si="1"/>
         <v>27.44</v>
       </c>
     </row>
-    <row r="71" spans="2:35" s="102" customFormat="1" ht="24" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="137" t="s">
+    <row r="72" spans="2:35" s="102" customFormat="1" ht="24" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="137" t="s">
         <v>53</v>
       </c>
-      <c r="C71" s="7">
+      <c r="C72" s="7">
         <v>20.5</v>
       </c>
-      <c r="D71" s="7">
+      <c r="D72" s="7">
         <v>283</v>
       </c>
-      <c r="E71" s="7">
-        <f t="shared" ref="E71:E72" si="10">+D71-C71</f>
+      <c r="E72" s="7">
+        <f t="shared" ref="E72:E73" si="10">+D72-C72</f>
         <v>262.5</v>
       </c>
-      <c r="F71" s="62"/>
-      <c r="G71" s="37">
+      <c r="F72" s="62"/>
+      <c r="G72" s="37">
         <v>72</v>
       </c>
-      <c r="H71" s="63" t="str">
-        <f t="shared" ref="H71:H72" si="11">(F71/G71)&amp;" pallets"</f>
+      <c r="H72" s="63" t="str">
+        <f t="shared" ref="H72:H73" si="11">(F72/G72)&amp;" pallets"</f>
         <v>0 pallets</v>
       </c>
-      <c r="I71" s="40">
-        <f t="shared" ref="I71:I72" si="12">E71*F71</f>
-        <v>0</v>
-      </c>
-      <c r="J71" s="40"/>
-      <c r="K71" s="64"/>
-      <c r="L71" s="40"/>
-      <c r="M71" s="64"/>
-      <c r="N71" s="64"/>
-      <c r="O71" s="64"/>
-      <c r="P71" s="63" t="str">
-        <f t="shared" ref="P71:P72" si="13">((M71+N71)/G71)&amp;" pallets"</f>
+      <c r="I72" s="40">
+        <f t="shared" ref="I72:I73" si="12">E72*F72</f>
+        <v>0</v>
+      </c>
+      <c r="J72" s="40"/>
+      <c r="K72" s="64"/>
+      <c r="L72" s="40"/>
+      <c r="M72" s="64"/>
+      <c r="N72" s="64"/>
+      <c r="O72" s="64"/>
+      <c r="P72" s="63" t="str">
+        <f t="shared" ref="P72:P73" si="13">((M72+N72)/G72)&amp;" pallets"</f>
         <v>0 pallets</v>
       </c>
-      <c r="Q71" s="65">
-        <f t="shared" ref="Q71:Q72" si="14">(J71*M71)+(K71*N71)+(O71*L71)</f>
-        <v>0</v>
-      </c>
-      <c r="S71" s="64"/>
-      <c r="T71" s="64"/>
-      <c r="U71" s="294"/>
-      <c r="V71" s="294"/>
-      <c r="AB71" s="102">
+      <c r="Q72" s="65">
+        <f t="shared" ref="Q72:Q73" si="14">(J72*M72)+(K72*N72)+(O72*L72)</f>
+        <v>0</v>
+      </c>
+      <c r="S72" s="64"/>
+      <c r="T72" s="64"/>
+      <c r="U72" s="194"/>
+      <c r="V72" s="194"/>
+      <c r="AB72" s="102">
         <v>0.61</v>
       </c>
     </row>
-    <row r="72" spans="2:35" s="102" customFormat="1" ht="24" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="138" t="s">
+    <row r="73" spans="2:35" s="102" customFormat="1" ht="24" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="138" t="s">
         <v>54</v>
       </c>
-      <c r="C72" s="66">
+      <c r="C73" s="66">
         <v>20.5</v>
       </c>
-      <c r="D72" s="66">
+      <c r="D73" s="66">
         <v>283</v>
       </c>
-      <c r="E72" s="66">
+      <c r="E73" s="66">
         <f t="shared" si="10"/>
         <v>262.5</v>
       </c>
-      <c r="F72" s="67"/>
-      <c r="G72" s="53">
+      <c r="F73" s="67"/>
+      <c r="G73" s="53">
         <v>72</v>
       </c>
-      <c r="H72" s="68" t="str">
+      <c r="H73" s="68" t="str">
         <f t="shared" si="11"/>
         <v>0 pallets</v>
       </c>
-      <c r="I72" s="69">
+      <c r="I73" s="69">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J72" s="69"/>
-      <c r="K72" s="70"/>
-      <c r="L72" s="69"/>
-      <c r="M72" s="70"/>
-      <c r="N72" s="70"/>
-      <c r="O72" s="70"/>
-      <c r="P72" s="68" t="str">
+      <c r="J73" s="69"/>
+      <c r="K73" s="70"/>
+      <c r="L73" s="69"/>
+      <c r="M73" s="70"/>
+      <c r="N73" s="70"/>
+      <c r="O73" s="70"/>
+      <c r="P73" s="68" t="str">
         <f t="shared" si="13"/>
         <v>0 pallets</v>
       </c>
-      <c r="Q72" s="71">
+      <c r="Q73" s="71">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="S72" s="70"/>
-      <c r="T72" s="70"/>
-      <c r="U72" s="294"/>
-      <c r="V72" s="294"/>
-      <c r="AB72" s="102">
+      <c r="S73" s="70"/>
+      <c r="T73" s="70"/>
+      <c r="U73" s="194"/>
+      <c r="V73" s="194"/>
+      <c r="AB73" s="102">
         <v>0.61</v>
       </c>
     </row>
-    <row r="73" spans="2:35" s="102" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B73" s="232" t="s">
+    <row r="74" spans="2:35" s="102" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B74" s="248" t="s">
         <v>55</v>
       </c>
-      <c r="C73" s="232"/>
-      <c r="D73" s="232"/>
-      <c r="E73" s="232"/>
-      <c r="F73" s="232"/>
-      <c r="G73" s="232"/>
-      <c r="H73" s="72" t="str">
-        <f>ROUND(((F12+F27+F51+F52+F56+F61+F62+F63)/72+(F13+F16+F17)/108+(F14+SUM(F18:F26)+F28+F29+F47+F49+F41)/63+F15/96+SUM(F30:F40)/100+SUM(F43:F45)/24+SUM(F64:F70)/100+(F50+F42+F48)/100),1)&amp;" pallets"</f>
+      <c r="C74" s="248"/>
+      <c r="D74" s="248"/>
+      <c r="E74" s="248"/>
+      <c r="F74" s="248"/>
+      <c r="G74" s="248"/>
+      <c r="H74" s="72" t="str">
+        <f>ROUND(((F13+F28+F52+F53+F57+F62+F63+F64)/72+(F14+F17+F18)/108+(F15+SUM(F19:F27)+F29+F30+F48+F50+F42)/63+F16/96+SUM(F31:F41)/100+SUM(F44:F46)/24+SUM(F65:F71)/100+(F51+F43+F49)/100),1)&amp;" pallets"</f>
         <v>0 pallets</v>
       </c>
-      <c r="I73" s="178"/>
-      <c r="J73" s="73"/>
-      <c r="K73" s="74"/>
-      <c r="L73" s="73"/>
-      <c r="M73" s="74"/>
-      <c r="N73" s="179"/>
-      <c r="O73" s="139"/>
-      <c r="P73" s="163" t="str">
-        <f>ROUND((((M12+N12+M27+M52+M56+M61+M62+M63+N52)/72+(M13+N13+M16+M17)/108+(M15+N15)/96+SUM(M14,M18:M26,M28:M29,M49,N14)/63)),1)&amp;" pallets"</f>
-        <v>0 pallets</v>
-      </c>
-      <c r="Q73" s="182"/>
-      <c r="R73" s="139"/>
-      <c r="S73" s="139"/>
-      <c r="T73" s="139"/>
-      <c r="U73" s="179"/>
-      <c r="V73" s="184"/>
-      <c r="W73" s="139"/>
-      <c r="X73" s="139"/>
-      <c r="Z73" s="139"/>
-      <c r="AA73" s="139"/>
-      <c r="AB73" s="139"/>
-      <c r="AC73" s="139"/>
-      <c r="AD73" s="139"/>
-      <c r="AE73" s="139"/>
-      <c r="AF73" s="139"/>
-      <c r="AG73" s="139"/>
-      <c r="AH73" s="139"/>
-    </row>
-    <row r="74" spans="2:35" s="102" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="140"/>
-      <c r="C74" s="76"/>
-      <c r="D74" s="76"/>
-      <c r="E74" s="76"/>
-      <c r="F74" s="74"/>
-      <c r="G74" s="74"/>
-      <c r="H74" s="74"/>
-      <c r="I74" s="73"/>
+      <c r="I74" s="178"/>
       <c r="J74" s="73"/>
       <c r="K74" s="74"/>
       <c r="L74" s="73"/>
       <c r="M74" s="74"/>
-      <c r="N74" s="139"/>
+      <c r="N74" s="179"/>
       <c r="O74" s="139"/>
-      <c r="P74" s="139"/>
-      <c r="Q74" s="75"/>
+      <c r="P74" s="163" t="str">
+        <f>ROUND((((M13+N13+M28+M53+M57+M62+M63+M64+N53)/72+(M14+N14+M17+M18)/108+(M16+N16)/96+SUM(M15,M19:M27,M29:M30,M50,N15)/63)),1)&amp;" pallets"</f>
+        <v>0 pallets</v>
+      </c>
+      <c r="Q74" s="182"/>
       <c r="R74" s="139"/>
       <c r="S74" s="139"/>
       <c r="T74" s="139"/>
-      <c r="U74" s="139"/>
-      <c r="V74" s="139"/>
+      <c r="U74" s="179"/>
+      <c r="V74" s="184"/>
       <c r="W74" s="139"/>
       <c r="X74" s="139"/>
-      <c r="Y74" s="139"/>
       <c r="Z74" s="139"/>
       <c r="AA74" s="139"/>
       <c r="AB74" s="139"/>
@@ -6892,67 +6906,69 @@
       <c r="AG74" s="139"/>
       <c r="AH74" s="139"/>
     </row>
-    <row r="75" spans="2:35" s="143" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="141" t="s">
+    <row r="75" spans="2:35" s="102" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="140"/>
+      <c r="C75" s="76"/>
+      <c r="D75" s="76"/>
+      <c r="E75" s="76"/>
+      <c r="F75" s="74"/>
+      <c r="G75" s="74"/>
+      <c r="H75" s="74"/>
+      <c r="I75" s="73"/>
+      <c r="J75" s="73"/>
+      <c r="K75" s="74"/>
+      <c r="L75" s="73"/>
+      <c r="M75" s="74"/>
+      <c r="N75" s="139"/>
+      <c r="O75" s="139"/>
+      <c r="P75" s="139"/>
+      <c r="Q75" s="75"/>
+      <c r="R75" s="139"/>
+      <c r="S75" s="139"/>
+      <c r="T75" s="139"/>
+      <c r="U75" s="139"/>
+      <c r="V75" s="139"/>
+      <c r="W75" s="139"/>
+      <c r="X75" s="139"/>
+      <c r="Y75" s="139"/>
+      <c r="Z75" s="139"/>
+      <c r="AA75" s="139"/>
+      <c r="AB75" s="139"/>
+      <c r="AC75" s="139"/>
+      <c r="AD75" s="139"/>
+      <c r="AE75" s="139"/>
+      <c r="AF75" s="139"/>
+      <c r="AG75" s="139"/>
+      <c r="AH75" s="139"/>
+    </row>
+    <row r="76" spans="2:35" s="143" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="141" t="s">
         <v>56</v>
       </c>
-      <c r="C75" s="142"/>
-      <c r="D75" s="142"/>
-      <c r="E75" s="142"/>
-      <c r="F75" s="233"/>
-      <c r="G75" s="233"/>
-      <c r="H75" s="233"/>
-      <c r="I75" s="234"/>
-      <c r="J75" s="77"/>
-      <c r="K75" s="77"/>
-      <c r="L75" s="77"/>
-      <c r="M75" s="235" t="s">
+      <c r="C76" s="142"/>
+      <c r="D76" s="142"/>
+      <c r="E76" s="142"/>
+      <c r="F76" s="249"/>
+      <c r="G76" s="249"/>
+      <c r="H76" s="249"/>
+      <c r="I76" s="250"/>
+      <c r="J76" s="77"/>
+      <c r="K76" s="77"/>
+      <c r="L76" s="77"/>
+      <c r="M76" s="251" t="s">
         <v>57</v>
       </c>
-      <c r="N75" s="236"/>
-      <c r="O75" s="233"/>
-      <c r="P75" s="233"/>
-      <c r="Q75" s="234"/>
-      <c r="R75" s="139"/>
-      <c r="S75" s="244" t="s">
+      <c r="N76" s="252"/>
+      <c r="O76" s="249"/>
+      <c r="P76" s="249"/>
+      <c r="Q76" s="250"/>
+      <c r="R76" s="139"/>
+      <c r="S76" s="195" t="s">
         <v>58</v>
       </c>
-      <c r="T75" s="244"/>
-      <c r="U75" s="244"/>
-      <c r="V75" s="244"/>
-      <c r="W75" s="78"/>
-      <c r="X75" s="78"/>
-      <c r="Y75" s="78"/>
-      <c r="Z75" s="78"/>
-      <c r="AA75" s="78"/>
-      <c r="AB75" s="78"/>
-      <c r="AC75" s="78"/>
-      <c r="AD75" s="78"/>
-      <c r="AE75" s="78"/>
-      <c r="AF75" s="78"/>
-      <c r="AG75" s="78"/>
-      <c r="AH75" s="78"/>
-      <c r="AI75" s="78"/>
-    </row>
-    <row r="76" spans="2:35" s="143" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="144"/>
-      <c r="F76" s="79"/>
-      <c r="G76" s="79"/>
-      <c r="H76" s="79"/>
-      <c r="I76" s="79"/>
-      <c r="J76" s="80"/>
-      <c r="K76" s="80"/>
-      <c r="L76" s="80"/>
-      <c r="M76" s="145"/>
-      <c r="N76" s="145"/>
-      <c r="O76" s="79"/>
-      <c r="P76" s="79"/>
-      <c r="Q76" s="79"/>
-      <c r="R76" s="79"/>
-      <c r="S76" s="144"/>
-      <c r="T76" s="81"/>
-      <c r="U76" s="81"/>
-      <c r="V76" s="81"/>
+      <c r="T76" s="195"/>
+      <c r="U76" s="195"/>
+      <c r="V76" s="195"/>
       <c r="W76" s="78"/>
       <c r="X76" s="78"/>
       <c r="Y76" s="78"/>
@@ -6967,40 +6983,27 @@
       <c r="AH76" s="78"/>
       <c r="AI76" s="78"/>
     </row>
-    <row r="77" spans="2:35" s="143" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="146" t="s">
-        <v>59</v>
-      </c>
-      <c r="C77" s="142"/>
-      <c r="D77" s="142"/>
-      <c r="E77" s="142"/>
-      <c r="F77" s="233"/>
-      <c r="G77" s="233"/>
-      <c r="H77" s="233"/>
-      <c r="I77" s="234"/>
+    <row r="77" spans="2:35" s="143" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="144"/>
+      <c r="F77" s="79"/>
+      <c r="G77" s="79"/>
+      <c r="H77" s="79"/>
+      <c r="I77" s="79"/>
       <c r="J77" s="80"/>
       <c r="K77" s="80"/>
       <c r="L77" s="80"/>
-      <c r="M77" s="243" t="s">
-        <v>60</v>
-      </c>
-      <c r="N77" s="243"/>
-      <c r="O77" s="82" t="s">
-        <v>61</v>
-      </c>
-      <c r="P77" s="242"/>
-      <c r="Q77" s="234"/>
-      <c r="R77" s="139"/>
-      <c r="S77" s="244" t="s">
-        <v>62</v>
-      </c>
-      <c r="T77" s="244"/>
-      <c r="U77" s="244"/>
-      <c r="V77" s="244"/>
+      <c r="M77" s="145"/>
+      <c r="N77" s="145"/>
+      <c r="O77" s="79"/>
+      <c r="P77" s="79"/>
+      <c r="Q77" s="79"/>
+      <c r="R77" s="79"/>
+      <c r="S77" s="144"/>
+      <c r="T77" s="81"/>
+      <c r="U77" s="81"/>
+      <c r="V77" s="81"/>
       <c r="W77" s="78"/>
-      <c r="X77" s="237" t="s">
-        <v>63</v>
-      </c>
+      <c r="X77" s="78"/>
       <c r="Y77" s="78"/>
       <c r="Z77" s="78"/>
       <c r="AA77" s="78"/>
@@ -7013,27 +7016,40 @@
       <c r="AH77" s="78"/>
       <c r="AI77" s="78"/>
     </row>
-    <row r="78" spans="2:35" s="143" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="144"/>
-      <c r="F78" s="79"/>
-      <c r="G78" s="79"/>
-      <c r="H78" s="79"/>
-      <c r="I78" s="79"/>
+    <row r="78" spans="2:35" s="143" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="146" t="s">
+        <v>59</v>
+      </c>
+      <c r="C78" s="142"/>
+      <c r="D78" s="142"/>
+      <c r="E78" s="142"/>
+      <c r="F78" s="249"/>
+      <c r="G78" s="249"/>
+      <c r="H78" s="249"/>
+      <c r="I78" s="250"/>
       <c r="J78" s="80"/>
       <c r="K78" s="80"/>
       <c r="L78" s="80"/>
-      <c r="M78" s="145"/>
-      <c r="N78" s="145"/>
-      <c r="O78" s="83"/>
-      <c r="P78" s="79"/>
-      <c r="Q78" s="79"/>
-      <c r="R78" s="79"/>
-      <c r="S78" s="144"/>
-      <c r="T78" s="81"/>
-      <c r="U78" s="81"/>
-      <c r="V78" s="81"/>
+      <c r="M78" s="256" t="s">
+        <v>60</v>
+      </c>
+      <c r="N78" s="256"/>
+      <c r="O78" s="82" t="s">
+        <v>61</v>
+      </c>
+      <c r="P78" s="255"/>
+      <c r="Q78" s="250"/>
+      <c r="R78" s="139"/>
+      <c r="S78" s="195" t="s">
+        <v>62</v>
+      </c>
+      <c r="T78" s="195"/>
+      <c r="U78" s="195"/>
+      <c r="V78" s="195"/>
       <c r="W78" s="78"/>
-      <c r="X78" s="238"/>
+      <c r="X78" s="208" t="s">
+        <v>63</v>
+      </c>
       <c r="Y78" s="78"/>
       <c r="Z78" s="78"/>
       <c r="AA78" s="78"/>
@@ -7046,42 +7062,27 @@
       <c r="AH78" s="78"/>
       <c r="AI78" s="78"/>
     </row>
-    <row r="79" spans="2:35" s="143" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="146" t="s">
-        <v>64</v>
-      </c>
-      <c r="C79" s="142"/>
-      <c r="D79" s="142"/>
-      <c r="E79" s="142"/>
-      <c r="F79" s="233" t="str">
-        <f>IF(U6&gt;0,"",F75-T79)</f>
-        <v/>
-      </c>
-      <c r="G79" s="233"/>
-      <c r="H79" s="233"/>
-      <c r="I79" s="234"/>
+    <row r="79" spans="2:35" s="143" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="144"/>
+      <c r="F79" s="79"/>
+      <c r="G79" s="79"/>
+      <c r="H79" s="79"/>
+      <c r="I79" s="79"/>
       <c r="J79" s="80"/>
       <c r="K79" s="80"/>
       <c r="L79" s="80"/>
-      <c r="M79" s="240" t="str">
-        <f>IF(U6&gt;0,"",T4+30)</f>
-        <v/>
-      </c>
-      <c r="N79" s="241"/>
-      <c r="O79" s="82" t="s">
-        <v>65</v>
-      </c>
-      <c r="P79" s="242"/>
-      <c r="Q79" s="234"/>
-      <c r="R79" s="139"/>
-      <c r="S79" s="245" t="s">
-        <v>66</v>
-      </c>
-      <c r="T79" s="246"/>
-      <c r="U79" s="246"/>
-      <c r="V79" s="246"/>
+      <c r="M79" s="145"/>
+      <c r="N79" s="145"/>
+      <c r="O79" s="83"/>
+      <c r="P79" s="79"/>
+      <c r="Q79" s="79"/>
+      <c r="R79" s="79"/>
+      <c r="S79" s="144"/>
+      <c r="T79" s="81"/>
+      <c r="U79" s="81"/>
+      <c r="V79" s="81"/>
       <c r="W79" s="78"/>
-      <c r="X79" s="239"/>
+      <c r="X79" s="209"/>
       <c r="Y79" s="78"/>
       <c r="Z79" s="78"/>
       <c r="AA79" s="78"/>
@@ -7094,30 +7095,42 @@
       <c r="AH79" s="78"/>
       <c r="AI79" s="78"/>
     </row>
-    <row r="80" spans="2:35" s="143" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="147"/>
-      <c r="C80" s="147"/>
-      <c r="D80" s="147"/>
-      <c r="E80" s="147"/>
-      <c r="F80" s="147"/>
-      <c r="G80" s="147"/>
-      <c r="H80" s="147"/>
-      <c r="I80" s="147"/>
-      <c r="J80" s="147"/>
-      <c r="K80" s="147"/>
-      <c r="L80" s="147"/>
-      <c r="M80" s="147"/>
-      <c r="N80" s="147"/>
-      <c r="O80" s="147"/>
-      <c r="P80" s="147"/>
-      <c r="Q80" s="147"/>
-      <c r="R80" s="147"/>
-      <c r="S80" s="147"/>
-      <c r="T80" s="147"/>
-      <c r="U80" s="147"/>
-      <c r="V80" s="147"/>
+    <row r="80" spans="2:35" s="143" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="146" t="s">
+        <v>64</v>
+      </c>
+      <c r="C80" s="142"/>
+      <c r="D80" s="142"/>
+      <c r="E80" s="142"/>
+      <c r="F80" s="249" t="str">
+        <f>IF(U7&gt;0,"",F76-T80)</f>
+        <v/>
+      </c>
+      <c r="G80" s="249"/>
+      <c r="H80" s="249"/>
+      <c r="I80" s="250"/>
+      <c r="J80" s="80"/>
+      <c r="K80" s="80"/>
+      <c r="L80" s="80"/>
+      <c r="M80" s="253" t="str">
+        <f>IF(U7&gt;0,"",T5+30)</f>
+        <v/>
+      </c>
+      <c r="N80" s="254"/>
+      <c r="O80" s="82" t="s">
+        <v>65</v>
+      </c>
+      <c r="P80" s="255"/>
+      <c r="Q80" s="250"/>
+      <c r="R80" s="139"/>
+      <c r="S80" s="257" t="s">
+        <v>66</v>
+      </c>
+      <c r="T80" s="258"/>
+      <c r="U80" s="258"/>
+      <c r="V80" s="258"/>
       <c r="W80" s="78"/>
-      <c r="X80" s="147"/>
+      <c r="X80" s="210"/>
       <c r="Y80" s="78"/>
       <c r="Z80" s="78"/>
       <c r="AA80" s="78"/>
@@ -7130,449 +7143,485 @@
       <c r="AH80" s="78"/>
       <c r="AI80" s="78"/>
     </row>
-    <row r="81" spans="2:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="212" t="s">
+    <row r="81" spans="2:35" s="143" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="147"/>
+      <c r="C81" s="147"/>
+      <c r="D81" s="147"/>
+      <c r="E81" s="147"/>
+      <c r="F81" s="147"/>
+      <c r="G81" s="147"/>
+      <c r="H81" s="147"/>
+      <c r="I81" s="147"/>
+      <c r="J81" s="147"/>
+      <c r="K81" s="147"/>
+      <c r="L81" s="147"/>
+      <c r="M81" s="147"/>
+      <c r="N81" s="147"/>
+      <c r="O81" s="147"/>
+      <c r="P81" s="147"/>
+      <c r="Q81" s="147"/>
+      <c r="R81" s="147"/>
+      <c r="S81" s="147"/>
+      <c r="T81" s="147"/>
+      <c r="U81" s="147"/>
+      <c r="V81" s="147"/>
+      <c r="W81" s="78"/>
+      <c r="X81" s="147"/>
+      <c r="Y81" s="78"/>
+      <c r="Z81" s="78"/>
+      <c r="AA81" s="78"/>
+      <c r="AB81" s="78"/>
+      <c r="AC81" s="78"/>
+      <c r="AD81" s="78"/>
+      <c r="AE81" s="78"/>
+      <c r="AF81" s="78"/>
+      <c r="AG81" s="78"/>
+      <c r="AH81" s="78"/>
+      <c r="AI81" s="78"/>
+    </row>
+    <row r="82" spans="2:35" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="277" t="s">
         <v>67</v>
       </c>
-      <c r="C81" s="213"/>
-      <c r="D81" s="213"/>
-      <c r="E81" s="213"/>
-      <c r="F81" s="213"/>
-      <c r="G81" s="213"/>
-      <c r="H81" s="214"/>
-      <c r="I81" s="221" t="s">
+      <c r="C82" s="278"/>
+      <c r="D82" s="278"/>
+      <c r="E82" s="278"/>
+      <c r="F82" s="278"/>
+      <c r="G82" s="278"/>
+      <c r="H82" s="279"/>
+      <c r="I82" s="286" t="s">
         <v>68</v>
       </c>
-      <c r="J81" s="148"/>
-      <c r="K81" s="148"/>
-      <c r="L81" s="148"/>
-      <c r="M81" s="223"/>
-      <c r="N81" s="226" t="s">
+      <c r="J82" s="148"/>
+      <c r="K82" s="148"/>
+      <c r="L82" s="148"/>
+      <c r="M82" s="288"/>
+      <c r="N82" s="291" t="s">
         <v>69</v>
       </c>
-      <c r="O81" s="229"/>
-      <c r="P81" s="223"/>
-      <c r="Q81" s="203" t="s">
+      <c r="O82" s="294"/>
+      <c r="P82" s="288"/>
+      <c r="Q82" s="268" t="s">
         <v>70</v>
       </c>
-      <c r="R81" s="204"/>
-      <c r="S81" s="209"/>
-      <c r="T81" s="203" t="s">
+      <c r="R82" s="269"/>
+      <c r="S82" s="274"/>
+      <c r="T82" s="268" t="s">
         <v>71</v>
       </c>
-      <c r="U81" s="193"/>
-      <c r="V81" s="193"/>
-    </row>
-    <row r="82" spans="2:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="215"/>
-      <c r="C82" s="216"/>
-      <c r="D82" s="216"/>
-      <c r="E82" s="216"/>
-      <c r="F82" s="216"/>
-      <c r="G82" s="216"/>
-      <c r="H82" s="217"/>
-      <c r="I82" s="197"/>
-      <c r="J82" s="91"/>
-      <c r="K82" s="91"/>
-      <c r="L82" s="91"/>
-      <c r="M82" s="224"/>
-      <c r="N82" s="227"/>
-      <c r="O82" s="230"/>
-      <c r="P82" s="224"/>
-      <c r="Q82" s="205"/>
-      <c r="R82" s="206"/>
-      <c r="S82" s="210"/>
-      <c r="T82" s="205"/>
-      <c r="U82" s="193"/>
-      <c r="V82" s="193"/>
-    </row>
-    <row r="83" spans="2:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="218"/>
-      <c r="C83" s="219"/>
-      <c r="D83" s="219"/>
-      <c r="E83" s="219"/>
-      <c r="F83" s="219"/>
-      <c r="G83" s="219"/>
-      <c r="H83" s="220"/>
-      <c r="I83" s="222"/>
-      <c r="J83" s="149"/>
-      <c r="K83" s="149"/>
-      <c r="L83" s="149"/>
-      <c r="M83" s="225"/>
-      <c r="N83" s="228"/>
-      <c r="O83" s="231"/>
-      <c r="P83" s="225"/>
-      <c r="Q83" s="207"/>
-      <c r="R83" s="208"/>
-      <c r="S83" s="211"/>
-      <c r="T83" s="207"/>
-      <c r="U83" s="193"/>
-      <c r="V83" s="193"/>
-    </row>
-    <row r="84" spans="2:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="V84" s="190"/>
-    </row>
-    <row r="85" spans="2:23" s="152" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="B85" s="150" t="s">
+      <c r="U82" s="214"/>
+      <c r="V82" s="214"/>
+    </row>
+    <row r="83" spans="2:35" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="280"/>
+      <c r="C83" s="281"/>
+      <c r="D83" s="281"/>
+      <c r="E83" s="281"/>
+      <c r="F83" s="281"/>
+      <c r="G83" s="281"/>
+      <c r="H83" s="282"/>
+      <c r="I83" s="262"/>
+      <c r="J83" s="91"/>
+      <c r="K83" s="91"/>
+      <c r="L83" s="91"/>
+      <c r="M83" s="289"/>
+      <c r="N83" s="292"/>
+      <c r="O83" s="295"/>
+      <c r="P83" s="289"/>
+      <c r="Q83" s="270"/>
+      <c r="R83" s="271"/>
+      <c r="S83" s="275"/>
+      <c r="T83" s="270"/>
+      <c r="U83" s="214"/>
+      <c r="V83" s="214"/>
+    </row>
+    <row r="84" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="283"/>
+      <c r="C84" s="284"/>
+      <c r="D84" s="284"/>
+      <c r="E84" s="284"/>
+      <c r="F84" s="284"/>
+      <c r="G84" s="284"/>
+      <c r="H84" s="285"/>
+      <c r="I84" s="287"/>
+      <c r="J84" s="149"/>
+      <c r="K84" s="149"/>
+      <c r="L84" s="149"/>
+      <c r="M84" s="290"/>
+      <c r="N84" s="293"/>
+      <c r="O84" s="296"/>
+      <c r="P84" s="290"/>
+      <c r="Q84" s="272"/>
+      <c r="R84" s="273"/>
+      <c r="S84" s="276"/>
+      <c r="T84" s="272"/>
+      <c r="U84" s="214"/>
+      <c r="V84" s="214"/>
+    </row>
+    <row r="85" spans="2:35" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V85" s="190"/>
+    </row>
+    <row r="86" spans="2:35" s="152" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+      <c r="B86" s="150" t="s">
         <v>72</v>
       </c>
-      <c r="C85" s="151"/>
-      <c r="D85" s="151"/>
-      <c r="E85" s="151"/>
-      <c r="F85" s="151"/>
-      <c r="G85" s="151"/>
-      <c r="H85" s="151"/>
-      <c r="I85" s="84"/>
-      <c r="J85" s="85"/>
-      <c r="K85" s="85"/>
-      <c r="L85" s="85"/>
-      <c r="M85" s="150" t="s">
+      <c r="C86" s="151"/>
+      <c r="D86" s="151"/>
+      <c r="E86" s="151"/>
+      <c r="F86" s="151"/>
+      <c r="G86" s="151"/>
+      <c r="H86" s="151"/>
+      <c r="I86" s="84"/>
+      <c r="J86" s="85"/>
+      <c r="K86" s="85"/>
+      <c r="L86" s="85"/>
+      <c r="M86" s="150" t="s">
         <v>73</v>
       </c>
-      <c r="N85" s="151"/>
-      <c r="O85" s="151"/>
-      <c r="P85" s="151"/>
-      <c r="Q85" s="84"/>
-      <c r="R85" s="150" t="s">
+      <c r="N86" s="151"/>
+      <c r="O86" s="151"/>
+      <c r="P86" s="151"/>
+      <c r="Q86" s="84"/>
+      <c r="R86" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="S85" s="151"/>
-      <c r="T85" s="151"/>
-      <c r="U85" s="151"/>
-      <c r="V85" s="185"/>
-      <c r="W85" s="191"/>
-    </row>
-    <row r="86" spans="2:23" ht="12.75" x14ac:dyDescent="0.25">
-      <c r="B86" s="153"/>
-      <c r="I86" s="86"/>
-      <c r="M86" s="153"/>
-      <c r="Q86" s="86"/>
-      <c r="R86" s="153"/>
-      <c r="U86" s="186"/>
-      <c r="V86" s="186"/>
-      <c r="W86" s="153"/>
-    </row>
-    <row r="87" spans="2:23" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B87" s="155" t="s">
+      <c r="S86" s="151"/>
+      <c r="T86" s="151"/>
+      <c r="U86" s="151"/>
+      <c r="V86" s="185"/>
+      <c r="W86" s="191"/>
+    </row>
+    <row r="87" spans="2:35" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="B87" s="153"/>
+      <c r="I87" s="86"/>
+      <c r="M87" s="153"/>
+      <c r="Q87" s="86"/>
+      <c r="R87" s="153"/>
+      <c r="U87" s="186"/>
+      <c r="V87" s="186"/>
+      <c r="W87" s="153"/>
+    </row>
+    <row r="88" spans="2:35" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B88" s="155" t="s">
         <v>75</v>
       </c>
-      <c r="I87" s="87"/>
-      <c r="J87" s="88"/>
-      <c r="K87" s="88"/>
-      <c r="L87" s="88"/>
-      <c r="M87" s="155" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q87" s="87"/>
-      <c r="R87" s="155"/>
-      <c r="U87" s="187"/>
-      <c r="V87" s="157"/>
-    </row>
-    <row r="88" spans="2:23" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B88" s="200"/>
-      <c r="C88" s="201"/>
-      <c r="D88" s="201"/>
-      <c r="E88" s="201"/>
-      <c r="F88" s="201"/>
-      <c r="G88" s="201"/>
-      <c r="H88" s="201"/>
-      <c r="I88" s="202"/>
+      <c r="I88" s="87"/>
       <c r="J88" s="88"/>
       <c r="K88" s="88"/>
       <c r="L88" s="88"/>
-      <c r="M88" s="200"/>
-      <c r="N88" s="201"/>
-      <c r="O88" s="201"/>
-      <c r="P88" s="201"/>
-      <c r="Q88" s="202"/>
-      <c r="R88" s="158"/>
-      <c r="S88" s="159"/>
-      <c r="T88" s="159"/>
-      <c r="U88" s="159"/>
-      <c r="V88" s="187"/>
-      <c r="W88" s="155"/>
-    </row>
-    <row r="89" spans="2:23" ht="18" x14ac:dyDescent="0.25">
-      <c r="B89" s="194" t="s">
+      <c r="M88" s="155" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q88" s="87"/>
+      <c r="R88" s="155"/>
+      <c r="U88" s="187"/>
+      <c r="V88" s="157"/>
+    </row>
+    <row r="89" spans="2:35" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B89" s="265"/>
+      <c r="C89" s="266"/>
+      <c r="D89" s="266"/>
+      <c r="E89" s="266"/>
+      <c r="F89" s="266"/>
+      <c r="G89" s="266"/>
+      <c r="H89" s="266"/>
+      <c r="I89" s="267"/>
+      <c r="J89" s="88"/>
+      <c r="K89" s="88"/>
+      <c r="L89" s="88"/>
+      <c r="M89" s="265"/>
+      <c r="N89" s="266"/>
+      <c r="O89" s="266"/>
+      <c r="P89" s="266"/>
+      <c r="Q89" s="267"/>
+      <c r="R89" s="158"/>
+      <c r="S89" s="159"/>
+      <c r="T89" s="159"/>
+      <c r="U89" s="159"/>
+      <c r="V89" s="187"/>
+      <c r="W89" s="155"/>
+    </row>
+    <row r="90" spans="2:35" ht="18" x14ac:dyDescent="0.25">
+      <c r="B90" s="259" t="s">
         <v>76</v>
       </c>
-      <c r="C89" s="195"/>
-      <c r="D89" s="195"/>
-      <c r="E89" s="195"/>
-      <c r="F89" s="195"/>
-      <c r="G89" s="195"/>
-      <c r="H89" s="195"/>
-      <c r="I89" s="196"/>
-      <c r="M89" s="194" t="s">
+      <c r="C90" s="260"/>
+      <c r="D90" s="260"/>
+      <c r="E90" s="260"/>
+      <c r="F90" s="260"/>
+      <c r="G90" s="260"/>
+      <c r="H90" s="260"/>
+      <c r="I90" s="261"/>
+      <c r="M90" s="259" t="s">
         <v>76</v>
       </c>
-      <c r="N89" s="195"/>
-      <c r="O89" s="195"/>
-      <c r="P89" s="195"/>
-      <c r="Q89" s="196"/>
-      <c r="R89" s="197" t="s">
+      <c r="N90" s="260"/>
+      <c r="O90" s="260"/>
+      <c r="P90" s="260"/>
+      <c r="Q90" s="261"/>
+      <c r="R90" s="262" t="s">
         <v>77</v>
       </c>
-      <c r="S89" s="198"/>
-      <c r="T89" s="198"/>
-      <c r="U89" s="199"/>
-      <c r="V89" s="192"/>
-      <c r="W89" s="153"/>
-    </row>
-    <row r="90" spans="2:23" ht="12.75" x14ac:dyDescent="0.25">
-      <c r="B90" s="153"/>
-      <c r="I90" s="86"/>
-      <c r="M90" s="153"/>
-      <c r="Q90" s="86"/>
-      <c r="R90" s="153"/>
-      <c r="U90" s="186"/>
-      <c r="V90" s="186"/>
+      <c r="S90" s="263"/>
+      <c r="T90" s="263"/>
+      <c r="U90" s="264"/>
+      <c r="V90" s="192"/>
       <c r="W90" s="153"/>
     </row>
-    <row r="91" spans="2:23" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B91" s="155" t="s">
+    <row r="91" spans="2:35" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="B91" s="153"/>
+      <c r="I91" s="86"/>
+      <c r="M91" s="153"/>
+      <c r="Q91" s="86"/>
+      <c r="R91" s="153"/>
+      <c r="U91" s="186"/>
+      <c r="V91" s="186"/>
+      <c r="W91" s="153"/>
+    </row>
+    <row r="92" spans="2:35" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B92" s="155" t="s">
         <v>78</v>
       </c>
-      <c r="I91" s="87"/>
-      <c r="J91" s="88"/>
-      <c r="K91" s="88"/>
-      <c r="L91" s="88"/>
-      <c r="M91" s="155"/>
-      <c r="Q91" s="87"/>
-      <c r="R91" s="155" t="s">
+      <c r="I92" s="87"/>
+      <c r="J92" s="88"/>
+      <c r="K92" s="88"/>
+      <c r="L92" s="88"/>
+      <c r="M92" s="155"/>
+      <c r="Q92" s="87"/>
+      <c r="R92" s="155" t="s">
         <v>79</v>
       </c>
-      <c r="U91" s="187"/>
-      <c r="V91" s="187"/>
-      <c r="W91" s="155"/>
-    </row>
-    <row r="92" spans="2:23" ht="12.75" x14ac:dyDescent="0.25">
-      <c r="B92" s="153"/>
-      <c r="I92" s="86"/>
-      <c r="M92" s="153"/>
-      <c r="Q92" s="86"/>
-      <c r="R92" s="153"/>
-      <c r="U92" s="186"/>
-      <c r="V92" s="154"/>
-    </row>
-    <row r="93" spans="2:23" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B93" s="200" t="s">
+      <c r="U92" s="187"/>
+      <c r="V92" s="187"/>
+      <c r="W92" s="155"/>
+    </row>
+    <row r="93" spans="2:35" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="B93" s="153"/>
+      <c r="I93" s="86"/>
+      <c r="M93" s="153"/>
+      <c r="Q93" s="86"/>
+      <c r="R93" s="153"/>
+      <c r="U93" s="186"/>
+      <c r="V93" s="154"/>
+    </row>
+    <row r="94" spans="2:35" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B94" s="265" t="s">
         <v>87</v>
       </c>
-      <c r="C93" s="201"/>
-      <c r="D93" s="201"/>
-      <c r="E93" s="201"/>
-      <c r="F93" s="201"/>
-      <c r="G93" s="201"/>
-      <c r="H93" s="201"/>
-      <c r="I93" s="202"/>
-      <c r="J93" s="88"/>
-      <c r="K93" s="88"/>
-      <c r="L93" s="88"/>
-      <c r="M93" s="153"/>
-      <c r="N93" s="91"/>
-      <c r="O93" s="91"/>
-      <c r="P93" s="91"/>
-      <c r="Q93" s="86"/>
-      <c r="R93" s="158"/>
-      <c r="S93" s="159"/>
-      <c r="T93" s="162" t="s">
+      <c r="C94" s="266"/>
+      <c r="D94" s="266"/>
+      <c r="E94" s="266"/>
+      <c r="F94" s="266"/>
+      <c r="G94" s="266"/>
+      <c r="H94" s="266"/>
+      <c r="I94" s="267"/>
+      <c r="J94" s="88"/>
+      <c r="K94" s="88"/>
+      <c r="L94" s="88"/>
+      <c r="M94" s="153"/>
+      <c r="N94" s="91"/>
+      <c r="O94" s="91"/>
+      <c r="P94" s="91"/>
+      <c r="Q94" s="86"/>
+      <c r="R94" s="158"/>
+      <c r="S94" s="159"/>
+      <c r="T94" s="162" t="s">
         <v>86</v>
       </c>
-      <c r="U93" s="159"/>
-      <c r="V93" s="160"/>
-      <c r="W93" s="155"/>
-    </row>
-    <row r="94" spans="2:23" ht="18" x14ac:dyDescent="0.25">
-      <c r="B94" s="194" t="s">
+      <c r="U94" s="159"/>
+      <c r="V94" s="160"/>
+      <c r="W94" s="155"/>
+    </row>
+    <row r="95" spans="2:35" ht="18" x14ac:dyDescent="0.25">
+      <c r="B95" s="259" t="s">
         <v>80</v>
       </c>
-      <c r="C94" s="195"/>
-      <c r="D94" s="195"/>
-      <c r="E94" s="195"/>
-      <c r="F94" s="195"/>
-      <c r="G94" s="195"/>
-      <c r="H94" s="195"/>
-      <c r="I94" s="196"/>
-      <c r="M94" s="153"/>
-      <c r="Q94" s="86"/>
-      <c r="R94" s="197" t="s">
-        <v>81</v>
-      </c>
-      <c r="S94" s="198"/>
-      <c r="T94" s="198"/>
-      <c r="U94" s="199"/>
-      <c r="V94" s="164"/>
-    </row>
-    <row r="95" spans="2:23" ht="12.75" x14ac:dyDescent="0.25">
-      <c r="B95" s="153"/>
-      <c r="I95" s="86"/>
+      <c r="C95" s="260"/>
+      <c r="D95" s="260"/>
+      <c r="E95" s="260"/>
+      <c r="F95" s="260"/>
+      <c r="G95" s="260"/>
+      <c r="H95" s="260"/>
+      <c r="I95" s="261"/>
       <c r="M95" s="153"/>
       <c r="Q95" s="86"/>
-      <c r="R95" s="153"/>
-      <c r="U95" s="186"/>
-      <c r="V95" s="186"/>
-      <c r="W95" s="153"/>
-    </row>
-    <row r="96" spans="2:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B96" s="161"/>
-      <c r="C96" s="149"/>
-      <c r="D96" s="149"/>
-      <c r="E96" s="149"/>
-      <c r="F96" s="149"/>
-      <c r="G96" s="149"/>
-      <c r="H96" s="149"/>
-      <c r="I96" s="89"/>
-      <c r="M96" s="161"/>
-      <c r="N96" s="149"/>
-      <c r="O96" s="149"/>
-      <c r="P96" s="149"/>
-      <c r="Q96" s="89"/>
-      <c r="R96" s="161"/>
-      <c r="S96" s="149"/>
-      <c r="T96" s="149"/>
-      <c r="U96" s="149"/>
-      <c r="V96" s="149"/>
+      <c r="R95" s="262" t="s">
+        <v>81</v>
+      </c>
+      <c r="S95" s="263"/>
+      <c r="T95" s="263"/>
+      <c r="U95" s="264"/>
+      <c r="V95" s="164"/>
+    </row>
+    <row r="96" spans="2:35" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="B96" s="153"/>
+      <c r="I96" s="86"/>
+      <c r="M96" s="153"/>
+      <c r="Q96" s="86"/>
+      <c r="R96" s="153"/>
+      <c r="U96" s="186"/>
+      <c r="V96" s="186"/>
       <c r="W96" s="153"/>
     </row>
-    <row r="97" ht="12.75" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="12.75" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="12.75" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="12.75" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="2:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B97" s="161"/>
+      <c r="C97" s="149"/>
+      <c r="D97" s="149"/>
+      <c r="E97" s="149"/>
+      <c r="F97" s="149"/>
+      <c r="G97" s="149"/>
+      <c r="H97" s="149"/>
+      <c r="I97" s="89"/>
+      <c r="M97" s="161"/>
+      <c r="N97" s="149"/>
+      <c r="O97" s="149"/>
+      <c r="P97" s="149"/>
+      <c r="Q97" s="89"/>
+      <c r="R97" s="161"/>
+      <c r="S97" s="149"/>
+      <c r="T97" s="149"/>
+      <c r="U97" s="149"/>
+      <c r="V97" s="149"/>
+      <c r="W97" s="153"/>
+    </row>
+    <row r="98" spans="2:23" ht="12.75" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="2:23" ht="12.75" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="2:23" ht="12.75" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="2:23" ht="12.75" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="2:23" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="2:23" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="126">
-    <mergeCell ref="U69:V69"/>
+    <mergeCell ref="U82:V84"/>
+    <mergeCell ref="B90:I90"/>
+    <mergeCell ref="M90:Q90"/>
+    <mergeCell ref="R90:U90"/>
+    <mergeCell ref="B94:I94"/>
+    <mergeCell ref="B95:I95"/>
+    <mergeCell ref="R95:U95"/>
+    <mergeCell ref="Q82:R84"/>
+    <mergeCell ref="S82:S84"/>
+    <mergeCell ref="T82:T84"/>
+    <mergeCell ref="B89:I89"/>
+    <mergeCell ref="M89:Q89"/>
+    <mergeCell ref="B82:H84"/>
+    <mergeCell ref="I82:I84"/>
+    <mergeCell ref="M82:M84"/>
+    <mergeCell ref="N82:N84"/>
+    <mergeCell ref="O82:P84"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="F76:I76"/>
+    <mergeCell ref="M76:N76"/>
+    <mergeCell ref="O76:Q76"/>
+    <mergeCell ref="X78:X80"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="S78:V78"/>
+    <mergeCell ref="S80:V80"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="F10:Q10"/>
+    <mergeCell ref="AG10:AG12"/>
+    <mergeCell ref="AI10:AI12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:Q11"/>
+    <mergeCell ref="Y10:Y12"/>
+    <mergeCell ref="Z10:Z12"/>
+    <mergeCell ref="AB10:AB12"/>
+    <mergeCell ref="AC10:AC12"/>
+    <mergeCell ref="AD10:AD12"/>
+    <mergeCell ref="AE10:AE12"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="F2:S2"/>
+    <mergeCell ref="X2:X5"/>
+    <mergeCell ref="F5:M5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="F8:M8"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="S10:V10"/>
+    <mergeCell ref="S11:V11"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="U21:V21"/>
+    <mergeCell ref="U22:V22"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="U30:V30"/>
+    <mergeCell ref="U31:V31"/>
+    <mergeCell ref="U32:V32"/>
+    <mergeCell ref="U33:V33"/>
+    <mergeCell ref="U34:V34"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="U29:V29"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="U41:V41"/>
+    <mergeCell ref="U42:V42"/>
+    <mergeCell ref="U43:V43"/>
+    <mergeCell ref="U44:V44"/>
+    <mergeCell ref="U35:V35"/>
+    <mergeCell ref="U36:V36"/>
+    <mergeCell ref="U37:V37"/>
+    <mergeCell ref="U38:V38"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="U50:V50"/>
+    <mergeCell ref="U51:V51"/>
+    <mergeCell ref="U52:V52"/>
+    <mergeCell ref="U53:V53"/>
+    <mergeCell ref="U54:V54"/>
+    <mergeCell ref="U45:V45"/>
+    <mergeCell ref="U46:V46"/>
+    <mergeCell ref="U47:V47"/>
+    <mergeCell ref="U48:V48"/>
+    <mergeCell ref="U49:V49"/>
+    <mergeCell ref="U60:V60"/>
+    <mergeCell ref="U61:V61"/>
+    <mergeCell ref="U62:V62"/>
+    <mergeCell ref="U63:V63"/>
+    <mergeCell ref="U64:V64"/>
+    <mergeCell ref="U55:V55"/>
+    <mergeCell ref="U56:V56"/>
+    <mergeCell ref="U57:V57"/>
+    <mergeCell ref="U58:V58"/>
+    <mergeCell ref="U59:V59"/>
     <mergeCell ref="U70:V70"/>
     <mergeCell ref="U71:V71"/>
     <mergeCell ref="U72:V72"/>
-    <mergeCell ref="S75:V75"/>
-    <mergeCell ref="U64:V64"/>
+    <mergeCell ref="U73:V73"/>
+    <mergeCell ref="S76:V76"/>
     <mergeCell ref="U65:V65"/>
     <mergeCell ref="U66:V66"/>
     <mergeCell ref="U67:V67"/>
     <mergeCell ref="U68:V68"/>
-    <mergeCell ref="U59:V59"/>
-    <mergeCell ref="U60:V60"/>
-    <mergeCell ref="U61:V61"/>
-    <mergeCell ref="U62:V62"/>
-    <mergeCell ref="U63:V63"/>
-    <mergeCell ref="U54:V54"/>
-    <mergeCell ref="U55:V55"/>
-    <mergeCell ref="U56:V56"/>
-    <mergeCell ref="U57:V57"/>
-    <mergeCell ref="U58:V58"/>
-    <mergeCell ref="U49:V49"/>
-    <mergeCell ref="U50:V50"/>
-    <mergeCell ref="U51:V51"/>
-    <mergeCell ref="U52:V52"/>
-    <mergeCell ref="U53:V53"/>
-    <mergeCell ref="U44:V44"/>
-    <mergeCell ref="U45:V45"/>
-    <mergeCell ref="U46:V46"/>
-    <mergeCell ref="U47:V47"/>
-    <mergeCell ref="U48:V48"/>
-    <mergeCell ref="U39:V39"/>
-    <mergeCell ref="U40:V40"/>
-    <mergeCell ref="U41:V41"/>
-    <mergeCell ref="U42:V42"/>
-    <mergeCell ref="U43:V43"/>
-    <mergeCell ref="U34:V34"/>
-    <mergeCell ref="U35:V35"/>
-    <mergeCell ref="U36:V36"/>
-    <mergeCell ref="U37:V37"/>
-    <mergeCell ref="U38:V38"/>
-    <mergeCell ref="U29:V29"/>
-    <mergeCell ref="U30:V30"/>
-    <mergeCell ref="U31:V31"/>
-    <mergeCell ref="U32:V32"/>
-    <mergeCell ref="U33:V33"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="U21:V21"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="F2:S2"/>
-    <mergeCell ref="X2:X4"/>
-    <mergeCell ref="F4:M4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="F6:M6"/>
-    <mergeCell ref="X6:X7"/>
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="S9:V9"/>
-    <mergeCell ref="S10:V10"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="F9:Q9"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="M10:Q10"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="F75:I75"/>
-    <mergeCell ref="M75:N75"/>
-    <mergeCell ref="O75:Q75"/>
-    <mergeCell ref="X77:X79"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="M79:N79"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="F77:I77"/>
-    <mergeCell ref="M77:N77"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="S77:V77"/>
-    <mergeCell ref="S79:V79"/>
-    <mergeCell ref="U81:V83"/>
-    <mergeCell ref="B89:I89"/>
-    <mergeCell ref="M89:Q89"/>
-    <mergeCell ref="R89:U89"/>
-    <mergeCell ref="B93:I93"/>
-    <mergeCell ref="B94:I94"/>
-    <mergeCell ref="R94:U94"/>
-    <mergeCell ref="Q81:R83"/>
-    <mergeCell ref="S81:S83"/>
-    <mergeCell ref="T81:T83"/>
-    <mergeCell ref="B88:I88"/>
-    <mergeCell ref="M88:Q88"/>
-    <mergeCell ref="B81:H83"/>
-    <mergeCell ref="I81:I83"/>
-    <mergeCell ref="M81:M83"/>
-    <mergeCell ref="N81:N83"/>
-    <mergeCell ref="O81:P83"/>
+    <mergeCell ref="U69:V69"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0" top="0" bottom="0" header="0" footer="0.19685039370078741"/>
-  <pageSetup scale="38" orientation="portrait" blackAndWhite="1" r:id="rId1"/>
+  <pageSetup scale="37" orientation="portrait" blackAndWhite="1" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/GBDS MARCH FILES 2026/Guillermo DOS 2 - Neilven.xlsx
+++ b/GBDS MARCH FILES 2026/Guillermo DOS 2 - Neilven.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A141150-A9BA-43D0-A05C-FBE4AD438B38}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BA40FE-2FD9-4E1E-AF82-EB2EABB3ED2A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2082,344 +2082,344 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="51" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="167" fontId="19" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="51" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2972,28 +2972,28 @@
       <c r="C2" s="93"/>
       <c r="D2" s="93"/>
       <c r="E2" s="93"/>
-      <c r="F2" s="207" t="s">
+      <c r="F2" s="286" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="207"/>
-      <c r="I2" s="207"/>
-      <c r="J2" s="207"/>
-      <c r="K2" s="207"/>
-      <c r="L2" s="207"/>
-      <c r="M2" s="207"/>
-      <c r="N2" s="207"/>
-      <c r="O2" s="207"/>
-      <c r="P2" s="207"/>
-      <c r="Q2" s="207"/>
-      <c r="R2" s="207"/>
-      <c r="S2" s="207"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="286"/>
+      <c r="I2" s="286"/>
+      <c r="J2" s="286"/>
+      <c r="K2" s="286"/>
+      <c r="L2" s="286"/>
+      <c r="M2" s="286"/>
+      <c r="N2" s="286"/>
+      <c r="O2" s="286"/>
+      <c r="P2" s="286"/>
+      <c r="Q2" s="286"/>
+      <c r="R2" s="286"/>
+      <c r="S2" s="286"/>
       <c r="T2" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="U2" s="214"/>
-      <c r="V2" s="214"/>
-      <c r="X2" s="208" t="s">
+      <c r="U2" s="195"/>
+      <c r="V2" s="195"/>
+      <c r="X2" s="239" t="s">
         <v>2</v>
       </c>
       <c r="AB2" s="92">
@@ -3031,9 +3031,9 @@
       <c r="T3" s="94" t="s">
         <v>131</v>
       </c>
-      <c r="U3" s="297"/>
-      <c r="V3" s="297"/>
-      <c r="X3" s="209"/>
+      <c r="U3" s="194"/>
+      <c r="V3" s="194"/>
+      <c r="X3" s="240"/>
       <c r="AB3" s="92"/>
       <c r="AE3" s="92"/>
     </row>
@@ -3042,7 +3042,7 @@
       <c r="C4" s="93"/>
       <c r="D4" s="93"/>
       <c r="E4" s="93"/>
-      <c r="X4" s="209"/>
+      <c r="X4" s="240"/>
       <c r="AB4" s="92">
         <v>5.76</v>
       </c>
@@ -3063,21 +3063,21 @@
       <c r="C5" s="93"/>
       <c r="D5" s="93"/>
       <c r="E5" s="93"/>
-      <c r="F5" s="211"/>
-      <c r="G5" s="211"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="211"/>
-      <c r="K5" s="211"/>
-      <c r="L5" s="211"/>
-      <c r="M5" s="211"/>
+      <c r="F5" s="287"/>
+      <c r="G5" s="287"/>
+      <c r="H5" s="287"/>
+      <c r="I5" s="287"/>
+      <c r="J5" s="287"/>
+      <c r="K5" s="287"/>
+      <c r="L5" s="287"/>
+      <c r="M5" s="287"/>
       <c r="S5" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T5" s="212"/>
-      <c r="U5" s="212"/>
+      <c r="T5" s="288"/>
+      <c r="U5" s="288"/>
       <c r="V5" s="183"/>
-      <c r="X5" s="210"/>
+      <c r="X5" s="241"/>
       <c r="AB5" s="92">
         <v>5.07</v>
       </c>
@@ -3119,25 +3119,25 @@
       <c r="B7" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="213"/>
-      <c r="G7" s="213"/>
-      <c r="H7" s="213"/>
-      <c r="I7" s="213"/>
-      <c r="J7" s="213"/>
-      <c r="K7" s="213"/>
-      <c r="L7" s="213"/>
-      <c r="M7" s="213"/>
+      <c r="F7" s="289"/>
+      <c r="G7" s="289"/>
+      <c r="H7" s="289"/>
+      <c r="I7" s="289"/>
+      <c r="J7" s="289"/>
+      <c r="K7" s="289"/>
+      <c r="L7" s="289"/>
+      <c r="M7" s="289"/>
       <c r="S7" s="97" t="s">
         <v>6</v>
       </c>
       <c r="T7" s="163" t="s">
         <v>7</v>
       </c>
-      <c r="U7" s="204" t="s">
+      <c r="U7" s="281" t="s">
         <v>8</v>
       </c>
-      <c r="V7" s="204"/>
-      <c r="X7" s="208" t="s">
+      <c r="V7" s="281"/>
+      <c r="X7" s="239" t="s">
         <v>9</v>
       </c>
       <c r="AB7" s="92">
@@ -3160,14 +3160,14 @@
       <c r="C8" s="98"/>
       <c r="D8" s="98"/>
       <c r="E8" s="98"/>
-      <c r="F8" s="213"/>
-      <c r="G8" s="213"/>
-      <c r="H8" s="213"/>
-      <c r="I8" s="213"/>
-      <c r="J8" s="213"/>
-      <c r="K8" s="213"/>
-      <c r="L8" s="213"/>
-      <c r="M8" s="213"/>
+      <c r="F8" s="289"/>
+      <c r="G8" s="289"/>
+      <c r="H8" s="289"/>
+      <c r="I8" s="289"/>
+      <c r="J8" s="289"/>
+      <c r="K8" s="289"/>
+      <c r="L8" s="289"/>
+      <c r="M8" s="289"/>
       <c r="N8" s="99"/>
       <c r="O8" s="99"/>
       <c r="P8" s="99"/>
@@ -3176,9 +3176,9 @@
       <c r="T8" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="U8" s="205"/>
-      <c r="V8" s="206"/>
-      <c r="X8" s="210"/>
+      <c r="U8" s="282"/>
+      <c r="V8" s="283"/>
+      <c r="X8" s="241"/>
       <c r="AB8" s="92">
         <v>5.25</v>
       </c>
@@ -3212,127 +3212,127 @@
       <c r="V9" s="95"/>
     </row>
     <row r="10" spans="2:35" s="100" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="216" t="s">
+      <c r="B10" s="249" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="219" t="s">
+      <c r="C10" s="252" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="219" t="s">
+      <c r="D10" s="252" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="219" t="s">
+      <c r="E10" s="252" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="222" t="s">
+      <c r="F10" s="255" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="223"/>
-      <c r="H10" s="223"/>
-      <c r="I10" s="223"/>
-      <c r="J10" s="223"/>
-      <c r="K10" s="223"/>
-      <c r="L10" s="223"/>
-      <c r="M10" s="223"/>
-      <c r="N10" s="223"/>
-      <c r="O10" s="223"/>
-      <c r="P10" s="223"/>
-      <c r="Q10" s="224"/>
-      <c r="S10" s="215" t="s">
+      <c r="G10" s="256"/>
+      <c r="H10" s="256"/>
+      <c r="I10" s="256"/>
+      <c r="J10" s="256"/>
+      <c r="K10" s="256"/>
+      <c r="L10" s="256"/>
+      <c r="M10" s="256"/>
+      <c r="N10" s="256"/>
+      <c r="O10" s="256"/>
+      <c r="P10" s="256"/>
+      <c r="Q10" s="257"/>
+      <c r="S10" s="290" t="s">
         <v>17</v>
       </c>
-      <c r="T10" s="215"/>
-      <c r="U10" s="215"/>
-      <c r="V10" s="215"/>
-      <c r="Y10" s="235" t="s">
+      <c r="T10" s="290"/>
+      <c r="U10" s="290"/>
+      <c r="V10" s="290"/>
+      <c r="Y10" s="268" t="s">
         <v>18</v>
       </c>
-      <c r="Z10" s="238" t="s">
+      <c r="Z10" s="271" t="s">
         <v>19</v>
       </c>
       <c r="AA10" s="101"/>
-      <c r="AB10" s="225" t="s">
+      <c r="AB10" s="258" t="s">
         <v>20</v>
       </c>
-      <c r="AC10" s="241" t="s">
+      <c r="AC10" s="274" t="s">
         <v>21</v>
       </c>
-      <c r="AD10" s="244" t="s">
+      <c r="AD10" s="277" t="s">
         <v>84</v>
       </c>
-      <c r="AE10" s="225" t="s">
+      <c r="AE10" s="258" t="s">
         <v>22</v>
       </c>
-      <c r="AG10" s="225" t="s">
+      <c r="AG10" s="258" t="s">
         <v>23</v>
       </c>
       <c r="AH10" s="101"/>
-      <c r="AI10" s="225" t="s">
+      <c r="AI10" s="258" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="2:35" s="100" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="217"/>
-      <c r="C11" s="220"/>
-      <c r="D11" s="220"/>
-      <c r="E11" s="220"/>
-      <c r="F11" s="229" t="s">
+      <c r="B11" s="250"/>
+      <c r="C11" s="253"/>
+      <c r="D11" s="253"/>
+      <c r="E11" s="253"/>
+      <c r="F11" s="262" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="229" t="s">
+      <c r="G11" s="262" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="229" t="s">
+      <c r="H11" s="262" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="230" t="s">
+      <c r="I11" s="263" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="230" t="s">
+      <c r="J11" s="263" t="s">
         <v>29</v>
       </c>
-      <c r="K11" s="230" t="s">
+      <c r="K11" s="263" t="s">
         <v>30</v>
       </c>
-      <c r="L11" s="230" t="s">
+      <c r="L11" s="263" t="s">
         <v>31</v>
       </c>
-      <c r="M11" s="232" t="s">
+      <c r="M11" s="265" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="233"/>
-      <c r="O11" s="233"/>
-      <c r="P11" s="233"/>
-      <c r="Q11" s="234"/>
-      <c r="S11" s="215" t="s">
+      <c r="N11" s="266"/>
+      <c r="O11" s="266"/>
+      <c r="P11" s="266"/>
+      <c r="Q11" s="267"/>
+      <c r="S11" s="290" t="s">
         <v>33</v>
       </c>
-      <c r="T11" s="215"/>
-      <c r="U11" s="215"/>
-      <c r="V11" s="215"/>
-      <c r="Y11" s="236"/>
-      <c r="Z11" s="239"/>
+      <c r="T11" s="290"/>
+      <c r="U11" s="290"/>
+      <c r="V11" s="290"/>
+      <c r="Y11" s="269"/>
+      <c r="Z11" s="272"/>
       <c r="AA11" s="101"/>
-      <c r="AB11" s="226"/>
-      <c r="AC11" s="242"/>
-      <c r="AD11" s="245"/>
-      <c r="AE11" s="226"/>
-      <c r="AG11" s="226"/>
+      <c r="AB11" s="259"/>
+      <c r="AC11" s="275"/>
+      <c r="AD11" s="278"/>
+      <c r="AE11" s="259"/>
+      <c r="AG11" s="259"/>
       <c r="AH11" s="101"/>
-      <c r="AI11" s="226"/>
+      <c r="AI11" s="259"/>
     </row>
     <row r="12" spans="2:35" s="102" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="218"/>
-      <c r="C12" s="221"/>
-      <c r="D12" s="221"/>
-      <c r="E12" s="221"/>
-      <c r="F12" s="221"/>
-      <c r="G12" s="221"/>
-      <c r="H12" s="221"/>
-      <c r="I12" s="231"/>
-      <c r="J12" s="231"/>
-      <c r="K12" s="231"/>
-      <c r="L12" s="231"/>
+      <c r="B12" s="251"/>
+      <c r="C12" s="254"/>
+      <c r="D12" s="254"/>
+      <c r="E12" s="254"/>
+      <c r="F12" s="254"/>
+      <c r="G12" s="254"/>
+      <c r="H12" s="254"/>
+      <c r="I12" s="264"/>
+      <c r="J12" s="264"/>
+      <c r="K12" s="264"/>
+      <c r="L12" s="264"/>
       <c r="M12" s="4" t="s">
         <v>34</v>
       </c>
@@ -3354,20 +3354,20 @@
       <c r="T12" s="188" t="s">
         <v>35</v>
       </c>
-      <c r="U12" s="247" t="s">
+      <c r="U12" s="280" t="s">
         <v>36</v>
       </c>
-      <c r="V12" s="247"/>
-      <c r="Y12" s="237"/>
-      <c r="Z12" s="240"/>
+      <c r="V12" s="280"/>
+      <c r="Y12" s="270"/>
+      <c r="Z12" s="273"/>
       <c r="AA12" s="101"/>
-      <c r="AB12" s="228"/>
-      <c r="AC12" s="243"/>
-      <c r="AD12" s="246"/>
-      <c r="AE12" s="228"/>
-      <c r="AG12" s="227"/>
+      <c r="AB12" s="261"/>
+      <c r="AC12" s="276"/>
+      <c r="AD12" s="279"/>
+      <c r="AE12" s="261"/>
+      <c r="AG12" s="260"/>
       <c r="AH12" s="101"/>
-      <c r="AI12" s="228"/>
+      <c r="AI12" s="261"/>
     </row>
     <row r="13" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="103" t="s">
@@ -3397,8 +3397,8 @@
       <c r="Q13" s="13"/>
       <c r="S13" s="14"/>
       <c r="T13" s="189"/>
-      <c r="U13" s="201"/>
-      <c r="V13" s="201"/>
+      <c r="U13" s="284"/>
+      <c r="V13" s="284"/>
       <c r="Y13" s="105">
         <f>F13*C13</f>
         <v>0</v>
@@ -3461,8 +3461,8 @@
       <c r="Q14" s="22"/>
       <c r="S14" s="23"/>
       <c r="T14" s="23"/>
-      <c r="U14" s="196"/>
-      <c r="V14" s="196"/>
+      <c r="U14" s="285"/>
+      <c r="V14" s="285"/>
       <c r="Y14" s="115">
         <f t="shared" ref="Y14:Y71" si="3">F14*C14</f>
         <v>0</v>
@@ -3525,8 +3525,8 @@
       <c r="Q15" s="22"/>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
-      <c r="U15" s="196"/>
-      <c r="V15" s="196"/>
+      <c r="U15" s="285"/>
+      <c r="V15" s="285"/>
       <c r="Y15" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3589,8 +3589,8 @@
       <c r="Q16" s="22"/>
       <c r="S16" s="23"/>
       <c r="T16" s="23"/>
-      <c r="U16" s="197"/>
-      <c r="V16" s="197"/>
+      <c r="U16" s="291"/>
+      <c r="V16" s="291"/>
       <c r="Y16" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3653,8 +3653,8 @@
       <c r="Q17" s="22"/>
       <c r="S17" s="23"/>
       <c r="T17" s="26"/>
-      <c r="U17" s="199"/>
-      <c r="V17" s="199"/>
+      <c r="U17" s="293"/>
+      <c r="V17" s="293"/>
       <c r="Y17" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3717,8 +3717,8 @@
       <c r="Q18" s="22"/>
       <c r="S18" s="23"/>
       <c r="T18" s="26"/>
-      <c r="U18" s="199"/>
-      <c r="V18" s="199"/>
+      <c r="U18" s="293"/>
+      <c r="V18" s="293"/>
       <c r="Y18" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3781,8 +3781,8 @@
       <c r="Q19" s="33"/>
       <c r="S19" s="34"/>
       <c r="T19" s="35"/>
-      <c r="U19" s="203"/>
-      <c r="V19" s="203"/>
+      <c r="U19" s="292"/>
+      <c r="V19" s="292"/>
       <c r="Y19" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3845,8 +3845,8 @@
       <c r="Q20" s="22"/>
       <c r="S20" s="23"/>
       <c r="T20" s="26"/>
-      <c r="U20" s="197"/>
-      <c r="V20" s="197"/>
+      <c r="U20" s="291"/>
+      <c r="V20" s="291"/>
       <c r="Y20" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3909,8 +3909,8 @@
       <c r="Q21" s="33"/>
       <c r="S21" s="34"/>
       <c r="T21" s="35"/>
-      <c r="U21" s="203"/>
-      <c r="V21" s="203"/>
+      <c r="U21" s="292"/>
+      <c r="V21" s="292"/>
       <c r="Y21" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3973,8 +3973,8 @@
       <c r="Q22" s="42"/>
       <c r="S22" s="43"/>
       <c r="T22" s="44"/>
-      <c r="U22" s="197"/>
-      <c r="V22" s="197"/>
+      <c r="U22" s="291"/>
+      <c r="V22" s="291"/>
       <c r="Y22" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4037,8 +4037,8 @@
       <c r="Q23" s="22"/>
       <c r="S23" s="23"/>
       <c r="T23" s="26"/>
-      <c r="U23" s="199"/>
-      <c r="V23" s="199"/>
+      <c r="U23" s="293"/>
+      <c r="V23" s="293"/>
       <c r="Y23" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4101,8 +4101,8 @@
       <c r="Q24" s="22"/>
       <c r="S24" s="23"/>
       <c r="T24" s="26"/>
-      <c r="U24" s="196"/>
-      <c r="V24" s="196"/>
+      <c r="U24" s="285"/>
+      <c r="V24" s="285"/>
       <c r="Y24" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4165,8 +4165,8 @@
       <c r="Q25" s="33"/>
       <c r="S25" s="34"/>
       <c r="T25" s="35"/>
-      <c r="U25" s="199"/>
-      <c r="V25" s="199"/>
+      <c r="U25" s="293"/>
+      <c r="V25" s="293"/>
       <c r="Y25" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4229,8 +4229,8 @@
       <c r="Q26" s="42"/>
       <c r="S26" s="43"/>
       <c r="T26" s="44"/>
-      <c r="U26" s="202"/>
-      <c r="V26" s="202"/>
+      <c r="U26" s="294"/>
+      <c r="V26" s="294"/>
       <c r="Y26" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4293,8 +4293,8 @@
       <c r="Q27" s="33"/>
       <c r="S27" s="34"/>
       <c r="T27" s="35"/>
-      <c r="U27" s="197"/>
-      <c r="V27" s="197"/>
+      <c r="U27" s="291"/>
+      <c r="V27" s="291"/>
       <c r="Y27" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4357,8 +4357,8 @@
       <c r="Q28" s="42"/>
       <c r="S28" s="43"/>
       <c r="T28" s="44"/>
-      <c r="U28" s="202"/>
-      <c r="V28" s="202"/>
+      <c r="U28" s="294"/>
+      <c r="V28" s="294"/>
       <c r="Y28" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4421,8 +4421,8 @@
       <c r="Q29" s="22"/>
       <c r="S29" s="23"/>
       <c r="T29" s="26"/>
-      <c r="U29" s="197"/>
-      <c r="V29" s="197"/>
+      <c r="U29" s="291"/>
+      <c r="V29" s="291"/>
       <c r="Y29" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4483,8 +4483,8 @@
       <c r="Q30" s="22"/>
       <c r="S30" s="23"/>
       <c r="T30" s="26"/>
-      <c r="U30" s="196"/>
-      <c r="V30" s="196"/>
+      <c r="U30" s="285"/>
+      <c r="V30" s="285"/>
       <c r="Y30" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4545,8 +4545,8 @@
       <c r="Q31" s="22"/>
       <c r="S31" s="26"/>
       <c r="T31" s="26"/>
-      <c r="U31" s="199"/>
-      <c r="V31" s="199"/>
+      <c r="U31" s="293"/>
+      <c r="V31" s="293"/>
       <c r="Y31" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4607,8 +4607,8 @@
       <c r="Q32" s="22"/>
       <c r="S32" s="26"/>
       <c r="T32" s="26"/>
-      <c r="U32" s="196"/>
-      <c r="V32" s="196"/>
+      <c r="U32" s="285"/>
+      <c r="V32" s="285"/>
       <c r="Y32" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4664,8 +4664,8 @@
       <c r="Q33" s="22"/>
       <c r="S33" s="26"/>
       <c r="T33" s="26"/>
-      <c r="U33" s="196"/>
-      <c r="V33" s="196"/>
+      <c r="U33" s="285"/>
+      <c r="V33" s="285"/>
       <c r="Y33" s="115"/>
       <c r="Z33" s="116"/>
       <c r="AA33" s="107"/>
@@ -4704,8 +4704,8 @@
       <c r="Q34" s="22"/>
       <c r="S34" s="26"/>
       <c r="T34" s="26"/>
-      <c r="U34" s="196"/>
-      <c r="V34" s="196"/>
+      <c r="U34" s="285"/>
+      <c r="V34" s="285"/>
       <c r="Y34" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4766,8 +4766,8 @@
       <c r="Q35" s="22"/>
       <c r="S35" s="26"/>
       <c r="T35" s="26"/>
-      <c r="U35" s="196"/>
-      <c r="V35" s="196"/>
+      <c r="U35" s="285"/>
+      <c r="V35" s="285"/>
       <c r="Y35" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4828,8 +4828,8 @@
       <c r="Q36" s="33"/>
       <c r="S36" s="35"/>
       <c r="T36" s="35"/>
-      <c r="U36" s="197"/>
-      <c r="V36" s="197"/>
+      <c r="U36" s="291"/>
+      <c r="V36" s="291"/>
       <c r="Y36" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4890,8 +4890,8 @@
       <c r="Q37" s="42"/>
       <c r="S37" s="44"/>
       <c r="T37" s="44"/>
-      <c r="U37" s="202"/>
-      <c r="V37" s="202"/>
+      <c r="U37" s="294"/>
+      <c r="V37" s="294"/>
       <c r="Y37" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4952,8 +4952,8 @@
       <c r="Q38" s="22"/>
       <c r="S38" s="26"/>
       <c r="T38" s="26"/>
-      <c r="U38" s="197"/>
-      <c r="V38" s="197"/>
+      <c r="U38" s="291"/>
+      <c r="V38" s="291"/>
       <c r="Y38" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5014,8 +5014,8 @@
       <c r="Q39" s="33"/>
       <c r="S39" s="35"/>
       <c r="T39" s="35"/>
-      <c r="U39" s="203"/>
-      <c r="V39" s="203"/>
+      <c r="U39" s="292"/>
+      <c r="V39" s="292"/>
       <c r="Y39" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5076,8 +5076,8 @@
       <c r="Q40" s="42"/>
       <c r="S40" s="44"/>
       <c r="T40" s="44"/>
-      <c r="U40" s="197"/>
-      <c r="V40" s="197"/>
+      <c r="U40" s="291"/>
+      <c r="V40" s="291"/>
       <c r="Y40" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5138,8 +5138,8 @@
       <c r="Q41" s="22"/>
       <c r="S41" s="26"/>
       <c r="T41" s="26"/>
-      <c r="U41" s="199"/>
-      <c r="V41" s="199"/>
+      <c r="U41" s="293"/>
+      <c r="V41" s="293"/>
       <c r="Y41" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5200,8 +5200,8 @@
       <c r="Q42" s="22"/>
       <c r="S42" s="26"/>
       <c r="T42" s="26"/>
-      <c r="U42" s="199"/>
-      <c r="V42" s="199"/>
+      <c r="U42" s="293"/>
+      <c r="V42" s="293"/>
       <c r="Y42" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5257,8 +5257,8 @@
       <c r="Q43" s="33"/>
       <c r="S43" s="35"/>
       <c r="T43" s="35"/>
-      <c r="U43" s="203"/>
-      <c r="V43" s="203"/>
+      <c r="U43" s="292"/>
+      <c r="V43" s="292"/>
       <c r="Y43" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5312,8 +5312,8 @@
       <c r="Q44" s="22"/>
       <c r="S44" s="23"/>
       <c r="T44" s="26"/>
-      <c r="U44" s="200"/>
-      <c r="V44" s="200"/>
+      <c r="U44" s="295"/>
+      <c r="V44" s="295"/>
       <c r="Y44" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5364,8 +5364,8 @@
       <c r="Q45" s="22"/>
       <c r="S45" s="23"/>
       <c r="T45" s="26"/>
-      <c r="U45" s="194"/>
-      <c r="V45" s="194"/>
+      <c r="U45" s="296"/>
+      <c r="V45" s="296"/>
       <c r="Y45" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5416,8 +5416,8 @@
       <c r="Q46" s="33"/>
       <c r="S46" s="34"/>
       <c r="T46" s="35"/>
-      <c r="U46" s="201"/>
-      <c r="V46" s="201"/>
+      <c r="U46" s="284"/>
+      <c r="V46" s="284"/>
       <c r="Y46" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5465,8 +5465,8 @@
       <c r="Q47" s="174"/>
       <c r="S47" s="171"/>
       <c r="T47" s="172"/>
-      <c r="U47" s="202"/>
-      <c r="V47" s="202"/>
+      <c r="U47" s="294"/>
+      <c r="V47" s="294"/>
       <c r="Y47" s="115"/>
       <c r="Z47" s="116"/>
       <c r="AA47" s="107"/>
@@ -5507,8 +5507,8 @@
       <c r="Q48" s="22"/>
       <c r="S48" s="23"/>
       <c r="T48" s="26"/>
-      <c r="U48" s="196"/>
-      <c r="V48" s="196"/>
+      <c r="U48" s="285"/>
+      <c r="V48" s="285"/>
       <c r="Y48" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5569,8 +5569,8 @@
       <c r="Q49" s="22"/>
       <c r="S49" s="26"/>
       <c r="T49" s="26"/>
-      <c r="U49" s="196"/>
-      <c r="V49" s="196"/>
+      <c r="U49" s="285"/>
+      <c r="V49" s="285"/>
       <c r="Y49" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5633,8 +5633,8 @@
       <c r="Q50" s="22"/>
       <c r="S50" s="23"/>
       <c r="T50" s="26"/>
-      <c r="U50" s="196"/>
-      <c r="V50" s="196"/>
+      <c r="U50" s="285"/>
+      <c r="V50" s="285"/>
       <c r="Y50" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5697,8 +5697,8 @@
       <c r="Q51" s="57"/>
       <c r="S51" s="58"/>
       <c r="T51" s="58"/>
-      <c r="U51" s="200"/>
-      <c r="V51" s="200"/>
+      <c r="U51" s="295"/>
+      <c r="V51" s="295"/>
       <c r="Y51" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5757,8 +5757,8 @@
       <c r="Q52" s="42"/>
       <c r="S52" s="44"/>
       <c r="T52" s="44"/>
-      <c r="U52" s="194"/>
-      <c r="V52" s="194"/>
+      <c r="U52" s="296"/>
+      <c r="V52" s="296"/>
       <c r="Y52" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5817,8 +5817,8 @@
       <c r="Q53" s="22"/>
       <c r="S53" s="23"/>
       <c r="T53" s="23"/>
-      <c r="U53" s="201"/>
-      <c r="V53" s="201"/>
+      <c r="U53" s="284"/>
+      <c r="V53" s="284"/>
       <c r="Y53" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5871,8 +5871,8 @@
       <c r="Q54" s="22"/>
       <c r="S54" s="23"/>
       <c r="T54" s="23"/>
-      <c r="U54" s="199"/>
-      <c r="V54" s="199"/>
+      <c r="U54" s="293"/>
+      <c r="V54" s="293"/>
       <c r="Y54" s="115"/>
       <c r="Z54" s="116"/>
       <c r="AA54" s="107"/>
@@ -5906,8 +5906,8 @@
       <c r="Q55" s="22"/>
       <c r="S55" s="23"/>
       <c r="T55" s="23"/>
-      <c r="U55" s="199"/>
-      <c r="V55" s="199"/>
+      <c r="U55" s="293"/>
+      <c r="V55" s="293"/>
       <c r="Y55" s="115"/>
       <c r="Z55" s="116"/>
       <c r="AA55" s="107"/>
@@ -5941,8 +5941,8 @@
       <c r="Q56" s="22"/>
       <c r="S56" s="23"/>
       <c r="T56" s="23"/>
-      <c r="U56" s="196"/>
-      <c r="V56" s="196"/>
+      <c r="U56" s="285"/>
+      <c r="V56" s="285"/>
       <c r="Y56" s="115"/>
       <c r="Z56" s="116"/>
       <c r="AA56" s="107"/>
@@ -5983,8 +5983,8 @@
       <c r="Q57" s="22"/>
       <c r="S57" s="23"/>
       <c r="T57" s="26"/>
-      <c r="U57" s="197"/>
-      <c r="V57" s="197"/>
+      <c r="U57" s="291"/>
+      <c r="V57" s="291"/>
       <c r="Y57" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6037,8 +6037,8 @@
       <c r="Q58" s="22"/>
       <c r="S58" s="23"/>
       <c r="T58" s="26"/>
-      <c r="U58" s="199"/>
-      <c r="V58" s="199"/>
+      <c r="U58" s="293"/>
+      <c r="V58" s="293"/>
       <c r="Y58" s="115"/>
       <c r="Z58" s="116"/>
       <c r="AA58" s="107"/>
@@ -6072,8 +6072,8 @@
       <c r="Q59" s="22"/>
       <c r="S59" s="23"/>
       <c r="T59" s="26"/>
-      <c r="U59" s="199"/>
-      <c r="V59" s="199"/>
+      <c r="U59" s="293"/>
+      <c r="V59" s="293"/>
       <c r="Y59" s="115"/>
       <c r="Z59" s="116"/>
       <c r="AA59" s="107"/>
@@ -6107,8 +6107,8 @@
       <c r="Q60" s="22"/>
       <c r="S60" s="23"/>
       <c r="T60" s="26"/>
-      <c r="U60" s="196"/>
-      <c r="V60" s="196"/>
+      <c r="U60" s="285"/>
+      <c r="V60" s="285"/>
       <c r="Y60" s="115"/>
       <c r="Z60" s="116"/>
       <c r="AA60" s="107"/>
@@ -6140,8 +6140,8 @@
       <c r="Q61" s="22"/>
       <c r="S61" s="23"/>
       <c r="T61" s="26"/>
-      <c r="U61" s="197"/>
-      <c r="V61" s="197"/>
+      <c r="U61" s="291"/>
+      <c r="V61" s="291"/>
       <c r="Y61" s="115"/>
       <c r="Z61" s="116"/>
       <c r="AA61" s="107"/>
@@ -6180,8 +6180,8 @@
       <c r="Q62" s="22"/>
       <c r="S62" s="180"/>
       <c r="T62" s="59"/>
-      <c r="U62" s="198"/>
-      <c r="V62" s="198"/>
+      <c r="U62" s="297"/>
+      <c r="V62" s="297"/>
       <c r="Y62" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6241,8 +6241,8 @@
       <c r="Q63" s="22"/>
       <c r="S63" s="43"/>
       <c r="T63" s="44"/>
-      <c r="U63" s="194"/>
-      <c r="V63" s="194"/>
+      <c r="U63" s="296"/>
+      <c r="V63" s="296"/>
       <c r="Y63" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6301,8 +6301,8 @@
       <c r="Q64" s="33"/>
       <c r="S64" s="34"/>
       <c r="T64" s="35"/>
-      <c r="U64" s="194"/>
-      <c r="V64" s="194"/>
+      <c r="U64" s="296"/>
+      <c r="V64" s="296"/>
       <c r="Y64" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6360,8 +6360,8 @@
       <c r="Q65" s="42"/>
       <c r="S65" s="44"/>
       <c r="T65" s="44"/>
-      <c r="U65" s="194"/>
-      <c r="V65" s="194"/>
+      <c r="U65" s="296"/>
+      <c r="V65" s="296"/>
       <c r="Y65" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6422,8 +6422,8 @@
       <c r="Q66" s="22"/>
       <c r="S66" s="26"/>
       <c r="T66" s="26"/>
-      <c r="U66" s="194"/>
-      <c r="V66" s="194"/>
+      <c r="U66" s="296"/>
+      <c r="V66" s="296"/>
       <c r="Y66" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6484,8 +6484,8 @@
       <c r="Q67" s="22"/>
       <c r="S67" s="26"/>
       <c r="T67" s="26"/>
-      <c r="U67" s="194"/>
-      <c r="V67" s="194"/>
+      <c r="U67" s="296"/>
+      <c r="V67" s="296"/>
       <c r="Y67" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6546,8 +6546,8 @@
       <c r="Q68" s="22"/>
       <c r="S68" s="26"/>
       <c r="T68" s="26"/>
-      <c r="U68" s="194"/>
-      <c r="V68" s="194"/>
+      <c r="U68" s="296"/>
+      <c r="V68" s="296"/>
       <c r="Y68" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6608,8 +6608,8 @@
       <c r="Q69" s="22"/>
       <c r="S69" s="26"/>
       <c r="T69" s="26"/>
-      <c r="U69" s="194"/>
-      <c r="V69" s="194"/>
+      <c r="U69" s="296"/>
+      <c r="V69" s="296"/>
       <c r="Y69" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6670,8 +6670,8 @@
       <c r="Q70" s="22"/>
       <c r="S70" s="26"/>
       <c r="T70" s="26"/>
-      <c r="U70" s="194"/>
-      <c r="V70" s="194"/>
+      <c r="U70" s="296"/>
+      <c r="V70" s="296"/>
       <c r="Y70" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6732,8 +6732,8 @@
       <c r="Q71" s="57"/>
       <c r="S71" s="58"/>
       <c r="T71" s="58"/>
-      <c r="U71" s="194"/>
-      <c r="V71" s="194"/>
+      <c r="U71" s="296"/>
+      <c r="V71" s="296"/>
       <c r="Y71" s="131">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6810,8 +6810,8 @@
       </c>
       <c r="S72" s="64"/>
       <c r="T72" s="64"/>
-      <c r="U72" s="194"/>
-      <c r="V72" s="194"/>
+      <c r="U72" s="296"/>
+      <c r="V72" s="296"/>
       <c r="AB72" s="102">
         <v>0.61</v>
       </c>
@@ -6858,21 +6858,21 @@
       </c>
       <c r="S73" s="70"/>
       <c r="T73" s="70"/>
-      <c r="U73" s="194"/>
-      <c r="V73" s="194"/>
+      <c r="U73" s="296"/>
+      <c r="V73" s="296"/>
       <c r="AB73" s="102">
         <v>0.61</v>
       </c>
     </row>
     <row r="74" spans="2:35" s="102" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B74" s="248" t="s">
+      <c r="B74" s="234" t="s">
         <v>55</v>
       </c>
-      <c r="C74" s="248"/>
-      <c r="D74" s="248"/>
-      <c r="E74" s="248"/>
-      <c r="F74" s="248"/>
-      <c r="G74" s="248"/>
+      <c r="C74" s="234"/>
+      <c r="D74" s="234"/>
+      <c r="E74" s="234"/>
+      <c r="F74" s="234"/>
+      <c r="G74" s="234"/>
       <c r="H74" s="72" t="str">
         <f>ROUND(((F13+F28+F52+F53+F57+F62+F63+F64)/72+(F14+F17+F18)/108+(F15+SUM(F19:F27)+F29+F30+F48+F50+F42)/63+F16/96+SUM(F31:F41)/100+SUM(F44:F46)/24+SUM(F65:F71)/100+(F51+F43+F49)/100),1)&amp;" pallets"</f>
         <v>0 pallets</v>
@@ -6948,27 +6948,27 @@
       <c r="C76" s="142"/>
       <c r="D76" s="142"/>
       <c r="E76" s="142"/>
-      <c r="F76" s="249"/>
-      <c r="G76" s="249"/>
-      <c r="H76" s="249"/>
-      <c r="I76" s="250"/>
+      <c r="F76" s="235"/>
+      <c r="G76" s="235"/>
+      <c r="H76" s="235"/>
+      <c r="I76" s="236"/>
       <c r="J76" s="77"/>
       <c r="K76" s="77"/>
       <c r="L76" s="77"/>
-      <c r="M76" s="251" t="s">
+      <c r="M76" s="237" t="s">
         <v>57</v>
       </c>
-      <c r="N76" s="252"/>
-      <c r="O76" s="249"/>
-      <c r="P76" s="249"/>
-      <c r="Q76" s="250"/>
+      <c r="N76" s="238"/>
+      <c r="O76" s="235"/>
+      <c r="P76" s="235"/>
+      <c r="Q76" s="236"/>
       <c r="R76" s="139"/>
-      <c r="S76" s="195" t="s">
+      <c r="S76" s="246" t="s">
         <v>58</v>
       </c>
-      <c r="T76" s="195"/>
-      <c r="U76" s="195"/>
-      <c r="V76" s="195"/>
+      <c r="T76" s="246"/>
+      <c r="U76" s="246"/>
+      <c r="V76" s="246"/>
       <c r="W76" s="78"/>
       <c r="X76" s="78"/>
       <c r="Y76" s="78"/>
@@ -7023,31 +7023,31 @@
       <c r="C78" s="142"/>
       <c r="D78" s="142"/>
       <c r="E78" s="142"/>
-      <c r="F78" s="249"/>
-      <c r="G78" s="249"/>
-      <c r="H78" s="249"/>
-      <c r="I78" s="250"/>
+      <c r="F78" s="235"/>
+      <c r="G78" s="235"/>
+      <c r="H78" s="235"/>
+      <c r="I78" s="236"/>
       <c r="J78" s="80"/>
       <c r="K78" s="80"/>
       <c r="L78" s="80"/>
-      <c r="M78" s="256" t="s">
+      <c r="M78" s="245" t="s">
         <v>60</v>
       </c>
-      <c r="N78" s="256"/>
+      <c r="N78" s="245"/>
       <c r="O78" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="P78" s="255"/>
-      <c r="Q78" s="250"/>
+      <c r="P78" s="244"/>
+      <c r="Q78" s="236"/>
       <c r="R78" s="139"/>
-      <c r="S78" s="195" t="s">
+      <c r="S78" s="246" t="s">
         <v>62</v>
       </c>
-      <c r="T78" s="195"/>
-      <c r="U78" s="195"/>
-      <c r="V78" s="195"/>
+      <c r="T78" s="246"/>
+      <c r="U78" s="246"/>
+      <c r="V78" s="246"/>
       <c r="W78" s="78"/>
-      <c r="X78" s="208" t="s">
+      <c r="X78" s="239" t="s">
         <v>63</v>
       </c>
       <c r="Y78" s="78"/>
@@ -7082,7 +7082,7 @@
       <c r="U79" s="81"/>
       <c r="V79" s="81"/>
       <c r="W79" s="78"/>
-      <c r="X79" s="209"/>
+      <c r="X79" s="240"/>
       <c r="Y79" s="78"/>
       <c r="Z79" s="78"/>
       <c r="AA79" s="78"/>
@@ -7102,35 +7102,35 @@
       <c r="C80" s="142"/>
       <c r="D80" s="142"/>
       <c r="E80" s="142"/>
-      <c r="F80" s="249" t="str">
+      <c r="F80" s="235" t="str">
         <f>IF(U7&gt;0,"",F76-T80)</f>
         <v/>
       </c>
-      <c r="G80" s="249"/>
-      <c r="H80" s="249"/>
-      <c r="I80" s="250"/>
+      <c r="G80" s="235"/>
+      <c r="H80" s="235"/>
+      <c r="I80" s="236"/>
       <c r="J80" s="80"/>
       <c r="K80" s="80"/>
       <c r="L80" s="80"/>
-      <c r="M80" s="253" t="str">
+      <c r="M80" s="242" t="str">
         <f>IF(U7&gt;0,"",T5+30)</f>
         <v/>
       </c>
-      <c r="N80" s="254"/>
+      <c r="N80" s="243"/>
       <c r="O80" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="P80" s="255"/>
-      <c r="Q80" s="250"/>
+      <c r="P80" s="244"/>
+      <c r="Q80" s="236"/>
       <c r="R80" s="139"/>
-      <c r="S80" s="257" t="s">
+      <c r="S80" s="247" t="s">
         <v>66</v>
       </c>
-      <c r="T80" s="258"/>
-      <c r="U80" s="258"/>
-      <c r="V80" s="258"/>
+      <c r="T80" s="248"/>
+      <c r="U80" s="248"/>
+      <c r="V80" s="248"/>
       <c r="W80" s="78"/>
-      <c r="X80" s="210"/>
+      <c r="X80" s="241"/>
       <c r="Y80" s="78"/>
       <c r="Z80" s="78"/>
       <c r="AA80" s="78"/>
@@ -7180,83 +7180,83 @@
       <c r="AI81" s="78"/>
     </row>
     <row r="82" spans="2:35" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="277" t="s">
+      <c r="B82" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="C82" s="278"/>
-      <c r="D82" s="278"/>
-      <c r="E82" s="278"/>
-      <c r="F82" s="278"/>
-      <c r="G82" s="278"/>
-      <c r="H82" s="279"/>
-      <c r="I82" s="286" t="s">
+      <c r="C82" s="215"/>
+      <c r="D82" s="215"/>
+      <c r="E82" s="215"/>
+      <c r="F82" s="215"/>
+      <c r="G82" s="215"/>
+      <c r="H82" s="216"/>
+      <c r="I82" s="223" t="s">
         <v>68</v>
       </c>
       <c r="J82" s="148"/>
       <c r="K82" s="148"/>
       <c r="L82" s="148"/>
-      <c r="M82" s="288"/>
-      <c r="N82" s="291" t="s">
+      <c r="M82" s="225"/>
+      <c r="N82" s="228" t="s">
         <v>69</v>
       </c>
-      <c r="O82" s="294"/>
-      <c r="P82" s="288"/>
-      <c r="Q82" s="268" t="s">
+      <c r="O82" s="231"/>
+      <c r="P82" s="225"/>
+      <c r="Q82" s="205" t="s">
         <v>70</v>
       </c>
-      <c r="R82" s="269"/>
-      <c r="S82" s="274"/>
-      <c r="T82" s="268" t="s">
+      <c r="R82" s="206"/>
+      <c r="S82" s="211"/>
+      <c r="T82" s="205" t="s">
         <v>71</v>
       </c>
-      <c r="U82" s="214"/>
-      <c r="V82" s="214"/>
+      <c r="U82" s="195"/>
+      <c r="V82" s="195"/>
     </row>
     <row r="83" spans="2:35" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="280"/>
-      <c r="C83" s="281"/>
-      <c r="D83" s="281"/>
-      <c r="E83" s="281"/>
-      <c r="F83" s="281"/>
-      <c r="G83" s="281"/>
-      <c r="H83" s="282"/>
-      <c r="I83" s="262"/>
+      <c r="B83" s="217"/>
+      <c r="C83" s="218"/>
+      <c r="D83" s="218"/>
+      <c r="E83" s="218"/>
+      <c r="F83" s="218"/>
+      <c r="G83" s="218"/>
+      <c r="H83" s="219"/>
+      <c r="I83" s="199"/>
       <c r="J83" s="91"/>
       <c r="K83" s="91"/>
       <c r="L83" s="91"/>
-      <c r="M83" s="289"/>
-      <c r="N83" s="292"/>
-      <c r="O83" s="295"/>
-      <c r="P83" s="289"/>
-      <c r="Q83" s="270"/>
-      <c r="R83" s="271"/>
-      <c r="S83" s="275"/>
-      <c r="T83" s="270"/>
-      <c r="U83" s="214"/>
-      <c r="V83" s="214"/>
+      <c r="M83" s="226"/>
+      <c r="N83" s="229"/>
+      <c r="O83" s="232"/>
+      <c r="P83" s="226"/>
+      <c r="Q83" s="207"/>
+      <c r="R83" s="208"/>
+      <c r="S83" s="212"/>
+      <c r="T83" s="207"/>
+      <c r="U83" s="195"/>
+      <c r="V83" s="195"/>
     </row>
     <row r="84" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="283"/>
-      <c r="C84" s="284"/>
-      <c r="D84" s="284"/>
-      <c r="E84" s="284"/>
-      <c r="F84" s="284"/>
-      <c r="G84" s="284"/>
-      <c r="H84" s="285"/>
-      <c r="I84" s="287"/>
+      <c r="B84" s="220"/>
+      <c r="C84" s="221"/>
+      <c r="D84" s="221"/>
+      <c r="E84" s="221"/>
+      <c r="F84" s="221"/>
+      <c r="G84" s="221"/>
+      <c r="H84" s="222"/>
+      <c r="I84" s="224"/>
       <c r="J84" s="149"/>
       <c r="K84" s="149"/>
       <c r="L84" s="149"/>
-      <c r="M84" s="290"/>
-      <c r="N84" s="293"/>
-      <c r="O84" s="296"/>
-      <c r="P84" s="290"/>
-      <c r="Q84" s="272"/>
-      <c r="R84" s="273"/>
-      <c r="S84" s="276"/>
-      <c r="T84" s="272"/>
-      <c r="U84" s="214"/>
-      <c r="V84" s="214"/>
+      <c r="M84" s="227"/>
+      <c r="N84" s="230"/>
+      <c r="O84" s="233"/>
+      <c r="P84" s="227"/>
+      <c r="Q84" s="209"/>
+      <c r="R84" s="210"/>
+      <c r="S84" s="213"/>
+      <c r="T84" s="209"/>
+      <c r="U84" s="195"/>
+      <c r="V84" s="195"/>
     </row>
     <row r="85" spans="2:35" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="V85" s="190"/>
@@ -7318,22 +7318,22 @@
       <c r="V88" s="157"/>
     </row>
     <row r="89" spans="2:35" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B89" s="265"/>
-      <c r="C89" s="266"/>
-      <c r="D89" s="266"/>
-      <c r="E89" s="266"/>
-      <c r="F89" s="266"/>
-      <c r="G89" s="266"/>
-      <c r="H89" s="266"/>
-      <c r="I89" s="267"/>
+      <c r="B89" s="202"/>
+      <c r="C89" s="203"/>
+      <c r="D89" s="203"/>
+      <c r="E89" s="203"/>
+      <c r="F89" s="203"/>
+      <c r="G89" s="203"/>
+      <c r="H89" s="203"/>
+      <c r="I89" s="204"/>
       <c r="J89" s="88"/>
       <c r="K89" s="88"/>
       <c r="L89" s="88"/>
-      <c r="M89" s="265"/>
-      <c r="N89" s="266"/>
-      <c r="O89" s="266"/>
-      <c r="P89" s="266"/>
-      <c r="Q89" s="267"/>
+      <c r="M89" s="202"/>
+      <c r="N89" s="203"/>
+      <c r="O89" s="203"/>
+      <c r="P89" s="203"/>
+      <c r="Q89" s="204"/>
       <c r="R89" s="158"/>
       <c r="S89" s="159"/>
       <c r="T89" s="159"/>
@@ -7342,29 +7342,29 @@
       <c r="W89" s="155"/>
     </row>
     <row r="90" spans="2:35" ht="18" x14ac:dyDescent="0.25">
-      <c r="B90" s="259" t="s">
+      <c r="B90" s="196" t="s">
         <v>76</v>
       </c>
-      <c r="C90" s="260"/>
-      <c r="D90" s="260"/>
-      <c r="E90" s="260"/>
-      <c r="F90" s="260"/>
-      <c r="G90" s="260"/>
-      <c r="H90" s="260"/>
-      <c r="I90" s="261"/>
-      <c r="M90" s="259" t="s">
+      <c r="C90" s="197"/>
+      <c r="D90" s="197"/>
+      <c r="E90" s="197"/>
+      <c r="F90" s="197"/>
+      <c r="G90" s="197"/>
+      <c r="H90" s="197"/>
+      <c r="I90" s="198"/>
+      <c r="M90" s="196" t="s">
         <v>76</v>
       </c>
-      <c r="N90" s="260"/>
-      <c r="O90" s="260"/>
-      <c r="P90" s="260"/>
-      <c r="Q90" s="261"/>
-      <c r="R90" s="262" t="s">
+      <c r="N90" s="197"/>
+      <c r="O90" s="197"/>
+      <c r="P90" s="197"/>
+      <c r="Q90" s="198"/>
+      <c r="R90" s="199" t="s">
         <v>77</v>
       </c>
-      <c r="S90" s="263"/>
-      <c r="T90" s="263"/>
-      <c r="U90" s="264"/>
+      <c r="S90" s="200"/>
+      <c r="T90" s="200"/>
+      <c r="U90" s="201"/>
       <c r="V90" s="192"/>
       <c r="W90" s="153"/>
     </row>
@@ -7405,16 +7405,16 @@
       <c r="V93" s="154"/>
     </row>
     <row r="94" spans="2:35" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B94" s="265" t="s">
+      <c r="B94" s="202" t="s">
         <v>87</v>
       </c>
-      <c r="C94" s="266"/>
-      <c r="D94" s="266"/>
-      <c r="E94" s="266"/>
-      <c r="F94" s="266"/>
-      <c r="G94" s="266"/>
-      <c r="H94" s="266"/>
-      <c r="I94" s="267"/>
+      <c r="C94" s="203"/>
+      <c r="D94" s="203"/>
+      <c r="E94" s="203"/>
+      <c r="F94" s="203"/>
+      <c r="G94" s="203"/>
+      <c r="H94" s="203"/>
+      <c r="I94" s="204"/>
       <c r="J94" s="88"/>
       <c r="K94" s="88"/>
       <c r="L94" s="88"/>
@@ -7433,24 +7433,24 @@
       <c r="W94" s="155"/>
     </row>
     <row r="95" spans="2:35" ht="18" x14ac:dyDescent="0.25">
-      <c r="B95" s="259" t="s">
+      <c r="B95" s="196" t="s">
         <v>80</v>
       </c>
-      <c r="C95" s="260"/>
-      <c r="D95" s="260"/>
-      <c r="E95" s="260"/>
-      <c r="F95" s="260"/>
-      <c r="G95" s="260"/>
-      <c r="H95" s="260"/>
-      <c r="I95" s="261"/>
+      <c r="C95" s="197"/>
+      <c r="D95" s="197"/>
+      <c r="E95" s="197"/>
+      <c r="F95" s="197"/>
+      <c r="G95" s="197"/>
+      <c r="H95" s="197"/>
+      <c r="I95" s="198"/>
       <c r="M95" s="153"/>
       <c r="Q95" s="86"/>
-      <c r="R95" s="262" t="s">
+      <c r="R95" s="199" t="s">
         <v>81</v>
       </c>
-      <c r="S95" s="263"/>
-      <c r="T95" s="263"/>
-      <c r="U95" s="264"/>
+      <c r="S95" s="200"/>
+      <c r="T95" s="200"/>
+      <c r="U95" s="201"/>
       <c r="V95" s="164"/>
     </row>
     <row r="96" spans="2:35" ht="12.75" x14ac:dyDescent="0.25">
@@ -7492,36 +7492,80 @@
     <row r="103" spans="2:23" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="126">
-    <mergeCell ref="U82:V84"/>
-    <mergeCell ref="B90:I90"/>
-    <mergeCell ref="M90:Q90"/>
-    <mergeCell ref="R90:U90"/>
-    <mergeCell ref="B94:I94"/>
-    <mergeCell ref="B95:I95"/>
-    <mergeCell ref="R95:U95"/>
-    <mergeCell ref="Q82:R84"/>
-    <mergeCell ref="S82:S84"/>
-    <mergeCell ref="T82:T84"/>
-    <mergeCell ref="B89:I89"/>
-    <mergeCell ref="M89:Q89"/>
-    <mergeCell ref="B82:H84"/>
-    <mergeCell ref="I82:I84"/>
-    <mergeCell ref="M82:M84"/>
-    <mergeCell ref="N82:N84"/>
-    <mergeCell ref="O82:P84"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="F76:I76"/>
-    <mergeCell ref="M76:N76"/>
-    <mergeCell ref="O76:Q76"/>
-    <mergeCell ref="X78:X80"/>
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="M80:N80"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="M78:N78"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="S78:V78"/>
-    <mergeCell ref="S80:V80"/>
+    <mergeCell ref="U70:V70"/>
+    <mergeCell ref="U71:V71"/>
+    <mergeCell ref="U72:V72"/>
+    <mergeCell ref="U73:V73"/>
+    <mergeCell ref="S76:V76"/>
+    <mergeCell ref="U65:V65"/>
+    <mergeCell ref="U66:V66"/>
+    <mergeCell ref="U67:V67"/>
+    <mergeCell ref="U68:V68"/>
+    <mergeCell ref="U69:V69"/>
+    <mergeCell ref="U60:V60"/>
+    <mergeCell ref="U61:V61"/>
+    <mergeCell ref="U62:V62"/>
+    <mergeCell ref="U63:V63"/>
+    <mergeCell ref="U64:V64"/>
+    <mergeCell ref="U55:V55"/>
+    <mergeCell ref="U56:V56"/>
+    <mergeCell ref="U57:V57"/>
+    <mergeCell ref="U58:V58"/>
+    <mergeCell ref="U59:V59"/>
+    <mergeCell ref="U50:V50"/>
+    <mergeCell ref="U51:V51"/>
+    <mergeCell ref="U52:V52"/>
+    <mergeCell ref="U53:V53"/>
+    <mergeCell ref="U54:V54"/>
+    <mergeCell ref="U45:V45"/>
+    <mergeCell ref="U46:V46"/>
+    <mergeCell ref="U47:V47"/>
+    <mergeCell ref="U48:V48"/>
+    <mergeCell ref="U49:V49"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="U41:V41"/>
+    <mergeCell ref="U42:V42"/>
+    <mergeCell ref="U43:V43"/>
+    <mergeCell ref="U44:V44"/>
+    <mergeCell ref="U35:V35"/>
+    <mergeCell ref="U36:V36"/>
+    <mergeCell ref="U37:V37"/>
+    <mergeCell ref="U38:V38"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="U30:V30"/>
+    <mergeCell ref="U31:V31"/>
+    <mergeCell ref="U32:V32"/>
+    <mergeCell ref="U33:V33"/>
+    <mergeCell ref="U34:V34"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="U29:V29"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="U21:V21"/>
+    <mergeCell ref="U22:V22"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="F2:S2"/>
+    <mergeCell ref="X2:X5"/>
+    <mergeCell ref="F5:M5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="F8:M8"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="S10:V10"/>
+    <mergeCell ref="S11:V11"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="D10:D12"/>
@@ -7544,80 +7588,36 @@
     <mergeCell ref="AD10:AD12"/>
     <mergeCell ref="AE10:AE12"/>
     <mergeCell ref="U12:V12"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="F2:S2"/>
-    <mergeCell ref="X2:X5"/>
-    <mergeCell ref="F5:M5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="X7:X8"/>
-    <mergeCell ref="F8:M8"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="S10:V10"/>
-    <mergeCell ref="S11:V11"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="U21:V21"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="U30:V30"/>
-    <mergeCell ref="U31:V31"/>
-    <mergeCell ref="U32:V32"/>
-    <mergeCell ref="U33:V33"/>
-    <mergeCell ref="U34:V34"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="U29:V29"/>
-    <mergeCell ref="U40:V40"/>
-    <mergeCell ref="U41:V41"/>
-    <mergeCell ref="U42:V42"/>
-    <mergeCell ref="U43:V43"/>
-    <mergeCell ref="U44:V44"/>
-    <mergeCell ref="U35:V35"/>
-    <mergeCell ref="U36:V36"/>
-    <mergeCell ref="U37:V37"/>
-    <mergeCell ref="U38:V38"/>
-    <mergeCell ref="U39:V39"/>
-    <mergeCell ref="U50:V50"/>
-    <mergeCell ref="U51:V51"/>
-    <mergeCell ref="U52:V52"/>
-    <mergeCell ref="U53:V53"/>
-    <mergeCell ref="U54:V54"/>
-    <mergeCell ref="U45:V45"/>
-    <mergeCell ref="U46:V46"/>
-    <mergeCell ref="U47:V47"/>
-    <mergeCell ref="U48:V48"/>
-    <mergeCell ref="U49:V49"/>
-    <mergeCell ref="U60:V60"/>
-    <mergeCell ref="U61:V61"/>
-    <mergeCell ref="U62:V62"/>
-    <mergeCell ref="U63:V63"/>
-    <mergeCell ref="U64:V64"/>
-    <mergeCell ref="U55:V55"/>
-    <mergeCell ref="U56:V56"/>
-    <mergeCell ref="U57:V57"/>
-    <mergeCell ref="U58:V58"/>
-    <mergeCell ref="U59:V59"/>
-    <mergeCell ref="U70:V70"/>
-    <mergeCell ref="U71:V71"/>
-    <mergeCell ref="U72:V72"/>
-    <mergeCell ref="U73:V73"/>
-    <mergeCell ref="S76:V76"/>
-    <mergeCell ref="U65:V65"/>
-    <mergeCell ref="U66:V66"/>
-    <mergeCell ref="U67:V67"/>
-    <mergeCell ref="U68:V68"/>
-    <mergeCell ref="U69:V69"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="F76:I76"/>
+    <mergeCell ref="M76:N76"/>
+    <mergeCell ref="O76:Q76"/>
+    <mergeCell ref="X78:X80"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="S78:V78"/>
+    <mergeCell ref="S80:V80"/>
+    <mergeCell ref="U82:V84"/>
+    <mergeCell ref="B90:I90"/>
+    <mergeCell ref="M90:Q90"/>
+    <mergeCell ref="R90:U90"/>
+    <mergeCell ref="B94:I94"/>
+    <mergeCell ref="B95:I95"/>
+    <mergeCell ref="R95:U95"/>
+    <mergeCell ref="Q82:R84"/>
+    <mergeCell ref="S82:S84"/>
+    <mergeCell ref="T82:T84"/>
+    <mergeCell ref="B89:I89"/>
+    <mergeCell ref="M89:Q89"/>
+    <mergeCell ref="B82:H84"/>
+    <mergeCell ref="I82:I84"/>
+    <mergeCell ref="M82:M84"/>
+    <mergeCell ref="N82:N84"/>
+    <mergeCell ref="O82:P84"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0" top="0" bottom="0" header="0" footer="0.19685039370078741"/>

--- a/GBDS MARCH FILES 2026/Guillermo DOS 2 - Neilven.xlsx
+++ b/GBDS MARCH FILES 2026/Guillermo DOS 2 - Neilven.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BA40FE-2FD9-4E1E-AF82-EB2EABB3ED2A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C75C33-B3F2-4CAC-BD6A-27817E9292B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2086,9 +2086,216 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="51" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2213,213 +2420,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="51" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2972,28 +2972,28 @@
       <c r="C2" s="93"/>
       <c r="D2" s="93"/>
       <c r="E2" s="93"/>
-      <c r="F2" s="286" t="s">
+      <c r="F2" s="208" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="286"/>
-      <c r="H2" s="286"/>
-      <c r="I2" s="286"/>
-      <c r="J2" s="286"/>
-      <c r="K2" s="286"/>
-      <c r="L2" s="286"/>
-      <c r="M2" s="286"/>
-      <c r="N2" s="286"/>
-      <c r="O2" s="286"/>
-      <c r="P2" s="286"/>
-      <c r="Q2" s="286"/>
-      <c r="R2" s="286"/>
-      <c r="S2" s="286"/>
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="208"/>
+      <c r="N2" s="208"/>
+      <c r="O2" s="208"/>
+      <c r="P2" s="208"/>
+      <c r="Q2" s="208"/>
+      <c r="R2" s="208"/>
+      <c r="S2" s="208"/>
       <c r="T2" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="U2" s="195"/>
-      <c r="V2" s="195"/>
-      <c r="X2" s="239" t="s">
+      <c r="U2" s="215"/>
+      <c r="V2" s="215"/>
+      <c r="X2" s="209" t="s">
         <v>2</v>
       </c>
       <c r="AB2" s="92">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="U3" s="194"/>
       <c r="V3" s="194"/>
-      <c r="X3" s="240"/>
+      <c r="X3" s="210"/>
       <c r="AB3" s="92"/>
       <c r="AE3" s="92"/>
     </row>
@@ -3042,7 +3042,7 @@
       <c r="C4" s="93"/>
       <c r="D4" s="93"/>
       <c r="E4" s="93"/>
-      <c r="X4" s="240"/>
+      <c r="X4" s="210"/>
       <c r="AB4" s="92">
         <v>5.76</v>
       </c>
@@ -3063,21 +3063,21 @@
       <c r="C5" s="93"/>
       <c r="D5" s="93"/>
       <c r="E5" s="93"/>
-      <c r="F5" s="287"/>
-      <c r="G5" s="287"/>
-      <c r="H5" s="287"/>
-      <c r="I5" s="287"/>
-      <c r="J5" s="287"/>
-      <c r="K5" s="287"/>
-      <c r="L5" s="287"/>
-      <c r="M5" s="287"/>
+      <c r="F5" s="212"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="212"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="212"/>
+      <c r="K5" s="212"/>
+      <c r="L5" s="212"/>
+      <c r="M5" s="212"/>
       <c r="S5" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T5" s="288"/>
-      <c r="U5" s="288"/>
+      <c r="T5" s="213"/>
+      <c r="U5" s="213"/>
       <c r="V5" s="183"/>
-      <c r="X5" s="241"/>
+      <c r="X5" s="211"/>
       <c r="AB5" s="92">
         <v>5.07</v>
       </c>
@@ -3119,25 +3119,25 @@
       <c r="B7" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="289"/>
-      <c r="G7" s="289"/>
-      <c r="H7" s="289"/>
-      <c r="I7" s="289"/>
-      <c r="J7" s="289"/>
-      <c r="K7" s="289"/>
-      <c r="L7" s="289"/>
-      <c r="M7" s="289"/>
+      <c r="F7" s="214"/>
+      <c r="G7" s="214"/>
+      <c r="H7" s="214"/>
+      <c r="I7" s="214"/>
+      <c r="J7" s="214"/>
+      <c r="K7" s="214"/>
+      <c r="L7" s="214"/>
+      <c r="M7" s="214"/>
       <c r="S7" s="97" t="s">
         <v>6</v>
       </c>
       <c r="T7" s="163" t="s">
         <v>7</v>
       </c>
-      <c r="U7" s="281" t="s">
+      <c r="U7" s="205" t="s">
         <v>8</v>
       </c>
-      <c r="V7" s="281"/>
-      <c r="X7" s="239" t="s">
+      <c r="V7" s="205"/>
+      <c r="X7" s="209" t="s">
         <v>9</v>
       </c>
       <c r="AB7" s="92">
@@ -3160,14 +3160,14 @@
       <c r="C8" s="98"/>
       <c r="D8" s="98"/>
       <c r="E8" s="98"/>
-      <c r="F8" s="289"/>
-      <c r="G8" s="289"/>
-      <c r="H8" s="289"/>
-      <c r="I8" s="289"/>
-      <c r="J8" s="289"/>
-      <c r="K8" s="289"/>
-      <c r="L8" s="289"/>
-      <c r="M8" s="289"/>
+      <c r="F8" s="214"/>
+      <c r="G8" s="214"/>
+      <c r="H8" s="214"/>
+      <c r="I8" s="214"/>
+      <c r="J8" s="214"/>
+      <c r="K8" s="214"/>
+      <c r="L8" s="214"/>
+      <c r="M8" s="214"/>
       <c r="N8" s="99"/>
       <c r="O8" s="99"/>
       <c r="P8" s="99"/>
@@ -3176,9 +3176,9 @@
       <c r="T8" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="U8" s="282"/>
-      <c r="V8" s="283"/>
-      <c r="X8" s="241"/>
+      <c r="U8" s="206"/>
+      <c r="V8" s="207"/>
+      <c r="X8" s="211"/>
       <c r="AB8" s="92">
         <v>5.25</v>
       </c>
@@ -3212,127 +3212,127 @@
       <c r="V9" s="95"/>
     </row>
     <row r="10" spans="2:35" s="100" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="249" t="s">
+      <c r="B10" s="217" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="252" t="s">
+      <c r="C10" s="220" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="252" t="s">
+      <c r="D10" s="220" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="252" t="s">
+      <c r="E10" s="220" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="255" t="s">
+      <c r="F10" s="223" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="256"/>
-      <c r="H10" s="256"/>
-      <c r="I10" s="256"/>
-      <c r="J10" s="256"/>
-      <c r="K10" s="256"/>
-      <c r="L10" s="256"/>
-      <c r="M10" s="256"/>
-      <c r="N10" s="256"/>
-      <c r="O10" s="256"/>
-      <c r="P10" s="256"/>
-      <c r="Q10" s="257"/>
-      <c r="S10" s="290" t="s">
+      <c r="G10" s="224"/>
+      <c r="H10" s="224"/>
+      <c r="I10" s="224"/>
+      <c r="J10" s="224"/>
+      <c r="K10" s="224"/>
+      <c r="L10" s="224"/>
+      <c r="M10" s="224"/>
+      <c r="N10" s="224"/>
+      <c r="O10" s="224"/>
+      <c r="P10" s="224"/>
+      <c r="Q10" s="225"/>
+      <c r="S10" s="216" t="s">
         <v>17</v>
       </c>
-      <c r="T10" s="290"/>
-      <c r="U10" s="290"/>
-      <c r="V10" s="290"/>
-      <c r="Y10" s="268" t="s">
+      <c r="T10" s="216"/>
+      <c r="U10" s="216"/>
+      <c r="V10" s="216"/>
+      <c r="Y10" s="236" t="s">
         <v>18</v>
       </c>
-      <c r="Z10" s="271" t="s">
+      <c r="Z10" s="239" t="s">
         <v>19</v>
       </c>
       <c r="AA10" s="101"/>
-      <c r="AB10" s="258" t="s">
+      <c r="AB10" s="226" t="s">
         <v>20</v>
       </c>
-      <c r="AC10" s="274" t="s">
+      <c r="AC10" s="242" t="s">
         <v>21</v>
       </c>
-      <c r="AD10" s="277" t="s">
+      <c r="AD10" s="245" t="s">
         <v>84</v>
       </c>
-      <c r="AE10" s="258" t="s">
+      <c r="AE10" s="226" t="s">
         <v>22</v>
       </c>
-      <c r="AG10" s="258" t="s">
+      <c r="AG10" s="226" t="s">
         <v>23</v>
       </c>
       <c r="AH10" s="101"/>
-      <c r="AI10" s="258" t="s">
+      <c r="AI10" s="226" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="2:35" s="100" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="250"/>
-      <c r="C11" s="253"/>
-      <c r="D11" s="253"/>
-      <c r="E11" s="253"/>
-      <c r="F11" s="262" t="s">
+      <c r="B11" s="218"/>
+      <c r="C11" s="221"/>
+      <c r="D11" s="221"/>
+      <c r="E11" s="221"/>
+      <c r="F11" s="230" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="262" t="s">
+      <c r="G11" s="230" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="262" t="s">
+      <c r="H11" s="230" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="263" t="s">
+      <c r="I11" s="231" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="263" t="s">
+      <c r="J11" s="231" t="s">
         <v>29</v>
       </c>
-      <c r="K11" s="263" t="s">
+      <c r="K11" s="231" t="s">
         <v>30</v>
       </c>
-      <c r="L11" s="263" t="s">
+      <c r="L11" s="231" t="s">
         <v>31</v>
       </c>
-      <c r="M11" s="265" t="s">
+      <c r="M11" s="233" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="266"/>
-      <c r="O11" s="266"/>
-      <c r="P11" s="266"/>
-      <c r="Q11" s="267"/>
-      <c r="S11" s="290" t="s">
+      <c r="N11" s="234"/>
+      <c r="O11" s="234"/>
+      <c r="P11" s="234"/>
+      <c r="Q11" s="235"/>
+      <c r="S11" s="216" t="s">
         <v>33</v>
       </c>
-      <c r="T11" s="290"/>
-      <c r="U11" s="290"/>
-      <c r="V11" s="290"/>
-      <c r="Y11" s="269"/>
-      <c r="Z11" s="272"/>
+      <c r="T11" s="216"/>
+      <c r="U11" s="216"/>
+      <c r="V11" s="216"/>
+      <c r="Y11" s="237"/>
+      <c r="Z11" s="240"/>
       <c r="AA11" s="101"/>
-      <c r="AB11" s="259"/>
-      <c r="AC11" s="275"/>
-      <c r="AD11" s="278"/>
-      <c r="AE11" s="259"/>
-      <c r="AG11" s="259"/>
+      <c r="AB11" s="227"/>
+      <c r="AC11" s="243"/>
+      <c r="AD11" s="246"/>
+      <c r="AE11" s="227"/>
+      <c r="AG11" s="227"/>
       <c r="AH11" s="101"/>
-      <c r="AI11" s="259"/>
+      <c r="AI11" s="227"/>
     </row>
     <row r="12" spans="2:35" s="102" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="251"/>
-      <c r="C12" s="254"/>
-      <c r="D12" s="254"/>
-      <c r="E12" s="254"/>
-      <c r="F12" s="254"/>
-      <c r="G12" s="254"/>
-      <c r="H12" s="254"/>
-      <c r="I12" s="264"/>
-      <c r="J12" s="264"/>
-      <c r="K12" s="264"/>
-      <c r="L12" s="264"/>
+      <c r="B12" s="219"/>
+      <c r="C12" s="222"/>
+      <c r="D12" s="222"/>
+      <c r="E12" s="222"/>
+      <c r="F12" s="222"/>
+      <c r="G12" s="222"/>
+      <c r="H12" s="222"/>
+      <c r="I12" s="232"/>
+      <c r="J12" s="232"/>
+      <c r="K12" s="232"/>
+      <c r="L12" s="232"/>
       <c r="M12" s="4" t="s">
         <v>34</v>
       </c>
@@ -3354,20 +3354,20 @@
       <c r="T12" s="188" t="s">
         <v>35</v>
       </c>
-      <c r="U12" s="280" t="s">
+      <c r="U12" s="248" t="s">
         <v>36</v>
       </c>
-      <c r="V12" s="280"/>
-      <c r="Y12" s="270"/>
-      <c r="Z12" s="273"/>
+      <c r="V12" s="248"/>
+      <c r="Y12" s="238"/>
+      <c r="Z12" s="241"/>
       <c r="AA12" s="101"/>
-      <c r="AB12" s="261"/>
-      <c r="AC12" s="276"/>
-      <c r="AD12" s="279"/>
-      <c r="AE12" s="261"/>
-      <c r="AG12" s="260"/>
+      <c r="AB12" s="229"/>
+      <c r="AC12" s="244"/>
+      <c r="AD12" s="247"/>
+      <c r="AE12" s="229"/>
+      <c r="AG12" s="228"/>
       <c r="AH12" s="101"/>
-      <c r="AI12" s="261"/>
+      <c r="AI12" s="229"/>
     </row>
     <row r="13" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="103" t="s">
@@ -3397,8 +3397,8 @@
       <c r="Q13" s="13"/>
       <c r="S13" s="14"/>
       <c r="T13" s="189"/>
-      <c r="U13" s="284"/>
-      <c r="V13" s="284"/>
+      <c r="U13" s="202"/>
+      <c r="V13" s="202"/>
       <c r="Y13" s="105">
         <f>F13*C13</f>
         <v>0</v>
@@ -3461,8 +3461,8 @@
       <c r="Q14" s="22"/>
       <c r="S14" s="23"/>
       <c r="T14" s="23"/>
-      <c r="U14" s="285"/>
-      <c r="V14" s="285"/>
+      <c r="U14" s="197"/>
+      <c r="V14" s="197"/>
       <c r="Y14" s="115">
         <f t="shared" ref="Y14:Y71" si="3">F14*C14</f>
         <v>0</v>
@@ -3525,8 +3525,8 @@
       <c r="Q15" s="22"/>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
-      <c r="U15" s="285"/>
-      <c r="V15" s="285"/>
+      <c r="U15" s="197"/>
+      <c r="V15" s="197"/>
       <c r="Y15" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3589,8 +3589,8 @@
       <c r="Q16" s="22"/>
       <c r="S16" s="23"/>
       <c r="T16" s="23"/>
-      <c r="U16" s="291"/>
-      <c r="V16" s="291"/>
+      <c r="U16" s="198"/>
+      <c r="V16" s="198"/>
       <c r="Y16" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3653,8 +3653,8 @@
       <c r="Q17" s="22"/>
       <c r="S17" s="23"/>
       <c r="T17" s="26"/>
-      <c r="U17" s="293"/>
-      <c r="V17" s="293"/>
+      <c r="U17" s="200"/>
+      <c r="V17" s="200"/>
       <c r="Y17" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3717,8 +3717,8 @@
       <c r="Q18" s="22"/>
       <c r="S18" s="23"/>
       <c r="T18" s="26"/>
-      <c r="U18" s="293"/>
-      <c r="V18" s="293"/>
+      <c r="U18" s="200"/>
+      <c r="V18" s="200"/>
       <c r="Y18" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3781,8 +3781,8 @@
       <c r="Q19" s="33"/>
       <c r="S19" s="34"/>
       <c r="T19" s="35"/>
-      <c r="U19" s="292"/>
-      <c r="V19" s="292"/>
+      <c r="U19" s="204"/>
+      <c r="V19" s="204"/>
       <c r="Y19" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3845,8 +3845,8 @@
       <c r="Q20" s="22"/>
       <c r="S20" s="23"/>
       <c r="T20" s="26"/>
-      <c r="U20" s="291"/>
-      <c r="V20" s="291"/>
+      <c r="U20" s="198"/>
+      <c r="V20" s="198"/>
       <c r="Y20" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3909,8 +3909,8 @@
       <c r="Q21" s="33"/>
       <c r="S21" s="34"/>
       <c r="T21" s="35"/>
-      <c r="U21" s="292"/>
-      <c r="V21" s="292"/>
+      <c r="U21" s="204"/>
+      <c r="V21" s="204"/>
       <c r="Y21" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3973,8 +3973,8 @@
       <c r="Q22" s="42"/>
       <c r="S22" s="43"/>
       <c r="T22" s="44"/>
-      <c r="U22" s="291"/>
-      <c r="V22" s="291"/>
+      <c r="U22" s="198"/>
+      <c r="V22" s="198"/>
       <c r="Y22" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4037,8 +4037,8 @@
       <c r="Q23" s="22"/>
       <c r="S23" s="23"/>
       <c r="T23" s="26"/>
-      <c r="U23" s="293"/>
-      <c r="V23" s="293"/>
+      <c r="U23" s="200"/>
+      <c r="V23" s="200"/>
       <c r="Y23" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4101,8 +4101,8 @@
       <c r="Q24" s="22"/>
       <c r="S24" s="23"/>
       <c r="T24" s="26"/>
-      <c r="U24" s="285"/>
-      <c r="V24" s="285"/>
+      <c r="U24" s="197"/>
+      <c r="V24" s="197"/>
       <c r="Y24" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4165,8 +4165,8 @@
       <c r="Q25" s="33"/>
       <c r="S25" s="34"/>
       <c r="T25" s="35"/>
-      <c r="U25" s="293"/>
-      <c r="V25" s="293"/>
+      <c r="U25" s="200"/>
+      <c r="V25" s="200"/>
       <c r="Y25" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4229,8 +4229,8 @@
       <c r="Q26" s="42"/>
       <c r="S26" s="43"/>
       <c r="T26" s="44"/>
-      <c r="U26" s="294"/>
-      <c r="V26" s="294"/>
+      <c r="U26" s="203"/>
+      <c r="V26" s="203"/>
       <c r="Y26" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4293,8 +4293,8 @@
       <c r="Q27" s="33"/>
       <c r="S27" s="34"/>
       <c r="T27" s="35"/>
-      <c r="U27" s="291"/>
-      <c r="V27" s="291"/>
+      <c r="U27" s="198"/>
+      <c r="V27" s="198"/>
       <c r="Y27" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4357,8 +4357,8 @@
       <c r="Q28" s="42"/>
       <c r="S28" s="43"/>
       <c r="T28" s="44"/>
-      <c r="U28" s="294"/>
-      <c r="V28" s="294"/>
+      <c r="U28" s="203"/>
+      <c r="V28" s="203"/>
       <c r="Y28" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4421,8 +4421,8 @@
       <c r="Q29" s="22"/>
       <c r="S29" s="23"/>
       <c r="T29" s="26"/>
-      <c r="U29" s="291"/>
-      <c r="V29" s="291"/>
+      <c r="U29" s="198"/>
+      <c r="V29" s="198"/>
       <c r="Y29" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4483,8 +4483,8 @@
       <c r="Q30" s="22"/>
       <c r="S30" s="23"/>
       <c r="T30" s="26"/>
-      <c r="U30" s="285"/>
-      <c r="V30" s="285"/>
+      <c r="U30" s="197"/>
+      <c r="V30" s="197"/>
       <c r="Y30" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4545,8 +4545,8 @@
       <c r="Q31" s="22"/>
       <c r="S31" s="26"/>
       <c r="T31" s="26"/>
-      <c r="U31" s="293"/>
-      <c r="V31" s="293"/>
+      <c r="U31" s="200"/>
+      <c r="V31" s="200"/>
       <c r="Y31" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4607,8 +4607,8 @@
       <c r="Q32" s="22"/>
       <c r="S32" s="26"/>
       <c r="T32" s="26"/>
-      <c r="U32" s="285"/>
-      <c r="V32" s="285"/>
+      <c r="U32" s="197"/>
+      <c r="V32" s="197"/>
       <c r="Y32" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4664,8 +4664,8 @@
       <c r="Q33" s="22"/>
       <c r="S33" s="26"/>
       <c r="T33" s="26"/>
-      <c r="U33" s="285"/>
-      <c r="V33" s="285"/>
+      <c r="U33" s="197"/>
+      <c r="V33" s="197"/>
       <c r="Y33" s="115"/>
       <c r="Z33" s="116"/>
       <c r="AA33" s="107"/>
@@ -4704,8 +4704,8 @@
       <c r="Q34" s="22"/>
       <c r="S34" s="26"/>
       <c r="T34" s="26"/>
-      <c r="U34" s="285"/>
-      <c r="V34" s="285"/>
+      <c r="U34" s="197"/>
+      <c r="V34" s="197"/>
       <c r="Y34" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4766,8 +4766,8 @@
       <c r="Q35" s="22"/>
       <c r="S35" s="26"/>
       <c r="T35" s="26"/>
-      <c r="U35" s="285"/>
-      <c r="V35" s="285"/>
+      <c r="U35" s="197"/>
+      <c r="V35" s="197"/>
       <c r="Y35" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4828,8 +4828,8 @@
       <c r="Q36" s="33"/>
       <c r="S36" s="35"/>
       <c r="T36" s="35"/>
-      <c r="U36" s="291"/>
-      <c r="V36" s="291"/>
+      <c r="U36" s="198"/>
+      <c r="V36" s="198"/>
       <c r="Y36" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4890,8 +4890,8 @@
       <c r="Q37" s="42"/>
       <c r="S37" s="44"/>
       <c r="T37" s="44"/>
-      <c r="U37" s="294"/>
-      <c r="V37" s="294"/>
+      <c r="U37" s="203"/>
+      <c r="V37" s="203"/>
       <c r="Y37" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4952,8 +4952,8 @@
       <c r="Q38" s="22"/>
       <c r="S38" s="26"/>
       <c r="T38" s="26"/>
-      <c r="U38" s="291"/>
-      <c r="V38" s="291"/>
+      <c r="U38" s="198"/>
+      <c r="V38" s="198"/>
       <c r="Y38" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5014,8 +5014,8 @@
       <c r="Q39" s="33"/>
       <c r="S39" s="35"/>
       <c r="T39" s="35"/>
-      <c r="U39" s="292"/>
-      <c r="V39" s="292"/>
+      <c r="U39" s="204"/>
+      <c r="V39" s="204"/>
       <c r="Y39" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5076,8 +5076,8 @@
       <c r="Q40" s="42"/>
       <c r="S40" s="44"/>
       <c r="T40" s="44"/>
-      <c r="U40" s="291"/>
-      <c r="V40" s="291"/>
+      <c r="U40" s="198"/>
+      <c r="V40" s="198"/>
       <c r="Y40" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5138,8 +5138,8 @@
       <c r="Q41" s="22"/>
       <c r="S41" s="26"/>
       <c r="T41" s="26"/>
-      <c r="U41" s="293"/>
-      <c r="V41" s="293"/>
+      <c r="U41" s="200"/>
+      <c r="V41" s="200"/>
       <c r="Y41" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5200,8 +5200,8 @@
       <c r="Q42" s="22"/>
       <c r="S42" s="26"/>
       <c r="T42" s="26"/>
-      <c r="U42" s="293"/>
-      <c r="V42" s="293"/>
+      <c r="U42" s="200"/>
+      <c r="V42" s="200"/>
       <c r="Y42" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5257,8 +5257,8 @@
       <c r="Q43" s="33"/>
       <c r="S43" s="35"/>
       <c r="T43" s="35"/>
-      <c r="U43" s="292"/>
-      <c r="V43" s="292"/>
+      <c r="U43" s="204"/>
+      <c r="V43" s="204"/>
       <c r="Y43" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5312,8 +5312,8 @@
       <c r="Q44" s="22"/>
       <c r="S44" s="23"/>
       <c r="T44" s="26"/>
-      <c r="U44" s="295"/>
-      <c r="V44" s="295"/>
+      <c r="U44" s="201"/>
+      <c r="V44" s="201"/>
       <c r="Y44" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5364,8 +5364,8 @@
       <c r="Q45" s="22"/>
       <c r="S45" s="23"/>
       <c r="T45" s="26"/>
-      <c r="U45" s="296"/>
-      <c r="V45" s="296"/>
+      <c r="U45" s="195"/>
+      <c r="V45" s="195"/>
       <c r="Y45" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5416,8 +5416,8 @@
       <c r="Q46" s="33"/>
       <c r="S46" s="34"/>
       <c r="T46" s="35"/>
-      <c r="U46" s="284"/>
-      <c r="V46" s="284"/>
+      <c r="U46" s="202"/>
+      <c r="V46" s="202"/>
       <c r="Y46" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5465,8 +5465,8 @@
       <c r="Q47" s="174"/>
       <c r="S47" s="171"/>
       <c r="T47" s="172"/>
-      <c r="U47" s="294"/>
-      <c r="V47" s="294"/>
+      <c r="U47" s="203"/>
+      <c r="V47" s="203"/>
       <c r="Y47" s="115"/>
       <c r="Z47" s="116"/>
       <c r="AA47" s="107"/>
@@ -5507,8 +5507,8 @@
       <c r="Q48" s="22"/>
       <c r="S48" s="23"/>
       <c r="T48" s="26"/>
-      <c r="U48" s="285"/>
-      <c r="V48" s="285"/>
+      <c r="U48" s="197"/>
+      <c r="V48" s="197"/>
       <c r="Y48" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5569,8 +5569,8 @@
       <c r="Q49" s="22"/>
       <c r="S49" s="26"/>
       <c r="T49" s="26"/>
-      <c r="U49" s="285"/>
-      <c r="V49" s="285"/>
+      <c r="U49" s="197"/>
+      <c r="V49" s="197"/>
       <c r="Y49" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5633,8 +5633,8 @@
       <c r="Q50" s="22"/>
       <c r="S50" s="23"/>
       <c r="T50" s="26"/>
-      <c r="U50" s="285"/>
-      <c r="V50" s="285"/>
+      <c r="U50" s="197"/>
+      <c r="V50" s="197"/>
       <c r="Y50" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5697,8 +5697,8 @@
       <c r="Q51" s="57"/>
       <c r="S51" s="58"/>
       <c r="T51" s="58"/>
-      <c r="U51" s="295"/>
-      <c r="V51" s="295"/>
+      <c r="U51" s="201"/>
+      <c r="V51" s="201"/>
       <c r="Y51" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5757,8 +5757,8 @@
       <c r="Q52" s="42"/>
       <c r="S52" s="44"/>
       <c r="T52" s="44"/>
-      <c r="U52" s="296"/>
-      <c r="V52" s="296"/>
+      <c r="U52" s="195"/>
+      <c r="V52" s="195"/>
       <c r="Y52" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5817,8 +5817,8 @@
       <c r="Q53" s="22"/>
       <c r="S53" s="23"/>
       <c r="T53" s="23"/>
-      <c r="U53" s="284"/>
-      <c r="V53" s="284"/>
+      <c r="U53" s="202"/>
+      <c r="V53" s="202"/>
       <c r="Y53" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5871,8 +5871,8 @@
       <c r="Q54" s="22"/>
       <c r="S54" s="23"/>
       <c r="T54" s="23"/>
-      <c r="U54" s="293"/>
-      <c r="V54" s="293"/>
+      <c r="U54" s="200"/>
+      <c r="V54" s="200"/>
       <c r="Y54" s="115"/>
       <c r="Z54" s="116"/>
       <c r="AA54" s="107"/>
@@ -5906,8 +5906,8 @@
       <c r="Q55" s="22"/>
       <c r="S55" s="23"/>
       <c r="T55" s="23"/>
-      <c r="U55" s="293"/>
-      <c r="V55" s="293"/>
+      <c r="U55" s="200"/>
+      <c r="V55" s="200"/>
       <c r="Y55" s="115"/>
       <c r="Z55" s="116"/>
       <c r="AA55" s="107"/>
@@ -5941,8 +5941,8 @@
       <c r="Q56" s="22"/>
       <c r="S56" s="23"/>
       <c r="T56" s="23"/>
-      <c r="U56" s="285"/>
-      <c r="V56" s="285"/>
+      <c r="U56" s="197"/>
+      <c r="V56" s="197"/>
       <c r="Y56" s="115"/>
       <c r="Z56" s="116"/>
       <c r="AA56" s="107"/>
@@ -5983,8 +5983,8 @@
       <c r="Q57" s="22"/>
       <c r="S57" s="23"/>
       <c r="T57" s="26"/>
-      <c r="U57" s="291"/>
-      <c r="V57" s="291"/>
+      <c r="U57" s="198"/>
+      <c r="V57" s="198"/>
       <c r="Y57" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6037,8 +6037,8 @@
       <c r="Q58" s="22"/>
       <c r="S58" s="23"/>
       <c r="T58" s="26"/>
-      <c r="U58" s="293"/>
-      <c r="V58" s="293"/>
+      <c r="U58" s="200"/>
+      <c r="V58" s="200"/>
       <c r="Y58" s="115"/>
       <c r="Z58" s="116"/>
       <c r="AA58" s="107"/>
@@ -6072,8 +6072,8 @@
       <c r="Q59" s="22"/>
       <c r="S59" s="23"/>
       <c r="T59" s="26"/>
-      <c r="U59" s="293"/>
-      <c r="V59" s="293"/>
+      <c r="U59" s="200"/>
+      <c r="V59" s="200"/>
       <c r="Y59" s="115"/>
       <c r="Z59" s="116"/>
       <c r="AA59" s="107"/>
@@ -6107,8 +6107,8 @@
       <c r="Q60" s="22"/>
       <c r="S60" s="23"/>
       <c r="T60" s="26"/>
-      <c r="U60" s="285"/>
-      <c r="V60" s="285"/>
+      <c r="U60" s="197"/>
+      <c r="V60" s="197"/>
       <c r="Y60" s="115"/>
       <c r="Z60" s="116"/>
       <c r="AA60" s="107"/>
@@ -6140,8 +6140,8 @@
       <c r="Q61" s="22"/>
       <c r="S61" s="23"/>
       <c r="T61" s="26"/>
-      <c r="U61" s="291"/>
-      <c r="V61" s="291"/>
+      <c r="U61" s="198"/>
+      <c r="V61" s="198"/>
       <c r="Y61" s="115"/>
       <c r="Z61" s="116"/>
       <c r="AA61" s="107"/>
@@ -6180,8 +6180,8 @@
       <c r="Q62" s="22"/>
       <c r="S62" s="180"/>
       <c r="T62" s="59"/>
-      <c r="U62" s="297"/>
-      <c r="V62" s="297"/>
+      <c r="U62" s="199"/>
+      <c r="V62" s="199"/>
       <c r="Y62" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6241,8 +6241,8 @@
       <c r="Q63" s="22"/>
       <c r="S63" s="43"/>
       <c r="T63" s="44"/>
-      <c r="U63" s="296"/>
-      <c r="V63" s="296"/>
+      <c r="U63" s="195"/>
+      <c r="V63" s="195"/>
       <c r="Y63" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6301,8 +6301,8 @@
       <c r="Q64" s="33"/>
       <c r="S64" s="34"/>
       <c r="T64" s="35"/>
-      <c r="U64" s="296"/>
-      <c r="V64" s="296"/>
+      <c r="U64" s="195"/>
+      <c r="V64" s="195"/>
       <c r="Y64" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6360,8 +6360,8 @@
       <c r="Q65" s="42"/>
       <c r="S65" s="44"/>
       <c r="T65" s="44"/>
-      <c r="U65" s="296"/>
-      <c r="V65" s="296"/>
+      <c r="U65" s="195"/>
+      <c r="V65" s="195"/>
       <c r="Y65" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6422,8 +6422,8 @@
       <c r="Q66" s="22"/>
       <c r="S66" s="26"/>
       <c r="T66" s="26"/>
-      <c r="U66" s="296"/>
-      <c r="V66" s="296"/>
+      <c r="U66" s="195"/>
+      <c r="V66" s="195"/>
       <c r="Y66" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6484,8 +6484,8 @@
       <c r="Q67" s="22"/>
       <c r="S67" s="26"/>
       <c r="T67" s="26"/>
-      <c r="U67" s="296"/>
-      <c r="V67" s="296"/>
+      <c r="U67" s="195"/>
+      <c r="V67" s="195"/>
       <c r="Y67" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6546,8 +6546,8 @@
       <c r="Q68" s="22"/>
       <c r="S68" s="26"/>
       <c r="T68" s="26"/>
-      <c r="U68" s="296"/>
-      <c r="V68" s="296"/>
+      <c r="U68" s="195"/>
+      <c r="V68" s="195"/>
       <c r="Y68" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6608,8 +6608,8 @@
       <c r="Q69" s="22"/>
       <c r="S69" s="26"/>
       <c r="T69" s="26"/>
-      <c r="U69" s="296"/>
-      <c r="V69" s="296"/>
+      <c r="U69" s="195"/>
+      <c r="V69" s="195"/>
       <c r="Y69" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6670,8 +6670,8 @@
       <c r="Q70" s="22"/>
       <c r="S70" s="26"/>
       <c r="T70" s="26"/>
-      <c r="U70" s="296"/>
-      <c r="V70" s="296"/>
+      <c r="U70" s="195"/>
+      <c r="V70" s="195"/>
       <c r="Y70" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6732,8 +6732,8 @@
       <c r="Q71" s="57"/>
       <c r="S71" s="58"/>
       <c r="T71" s="58"/>
-      <c r="U71" s="296"/>
-      <c r="V71" s="296"/>
+      <c r="U71" s="195"/>
+      <c r="V71" s="195"/>
       <c r="Y71" s="131">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6810,8 +6810,8 @@
       </c>
       <c r="S72" s="64"/>
       <c r="T72" s="64"/>
-      <c r="U72" s="296"/>
-      <c r="V72" s="296"/>
+      <c r="U72" s="195"/>
+      <c r="V72" s="195"/>
       <c r="AB72" s="102">
         <v>0.61</v>
       </c>
@@ -6858,21 +6858,21 @@
       </c>
       <c r="S73" s="70"/>
       <c r="T73" s="70"/>
-      <c r="U73" s="296"/>
-      <c r="V73" s="296"/>
+      <c r="U73" s="195"/>
+      <c r="V73" s="195"/>
       <c r="AB73" s="102">
         <v>0.61</v>
       </c>
     </row>
     <row r="74" spans="2:35" s="102" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B74" s="234" t="s">
+      <c r="B74" s="249" t="s">
         <v>55</v>
       </c>
-      <c r="C74" s="234"/>
-      <c r="D74" s="234"/>
-      <c r="E74" s="234"/>
-      <c r="F74" s="234"/>
-      <c r="G74" s="234"/>
+      <c r="C74" s="249"/>
+      <c r="D74" s="249"/>
+      <c r="E74" s="249"/>
+      <c r="F74" s="249"/>
+      <c r="G74" s="249"/>
       <c r="H74" s="72" t="str">
         <f>ROUND(((F13+F28+F52+F53+F57+F62+F63+F64)/72+(F14+F17+F18)/108+(F15+SUM(F19:F27)+F29+F30+F48+F50+F42)/63+F16/96+SUM(F31:F41)/100+SUM(F44:F46)/24+SUM(F65:F71)/100+(F51+F43+F49)/100),1)&amp;" pallets"</f>
         <v>0 pallets</v>
@@ -6948,27 +6948,27 @@
       <c r="C76" s="142"/>
       <c r="D76" s="142"/>
       <c r="E76" s="142"/>
-      <c r="F76" s="235"/>
-      <c r="G76" s="235"/>
-      <c r="H76" s="235"/>
-      <c r="I76" s="236"/>
+      <c r="F76" s="250"/>
+      <c r="G76" s="250"/>
+      <c r="H76" s="250"/>
+      <c r="I76" s="251"/>
       <c r="J76" s="77"/>
       <c r="K76" s="77"/>
       <c r="L76" s="77"/>
-      <c r="M76" s="237" t="s">
+      <c r="M76" s="252" t="s">
         <v>57</v>
       </c>
-      <c r="N76" s="238"/>
-      <c r="O76" s="235"/>
-      <c r="P76" s="235"/>
-      <c r="Q76" s="236"/>
+      <c r="N76" s="253"/>
+      <c r="O76" s="250"/>
+      <c r="P76" s="250"/>
+      <c r="Q76" s="251"/>
       <c r="R76" s="139"/>
-      <c r="S76" s="246" t="s">
+      <c r="S76" s="196" t="s">
         <v>58</v>
       </c>
-      <c r="T76" s="246"/>
-      <c r="U76" s="246"/>
-      <c r="V76" s="246"/>
+      <c r="T76" s="196"/>
+      <c r="U76" s="196"/>
+      <c r="V76" s="196"/>
       <c r="W76" s="78"/>
       <c r="X76" s="78"/>
       <c r="Y76" s="78"/>
@@ -7023,31 +7023,31 @@
       <c r="C78" s="142"/>
       <c r="D78" s="142"/>
       <c r="E78" s="142"/>
-      <c r="F78" s="235"/>
-      <c r="G78" s="235"/>
-      <c r="H78" s="235"/>
-      <c r="I78" s="236"/>
+      <c r="F78" s="250"/>
+      <c r="G78" s="250"/>
+      <c r="H78" s="250"/>
+      <c r="I78" s="251"/>
       <c r="J78" s="80"/>
       <c r="K78" s="80"/>
       <c r="L78" s="80"/>
-      <c r="M78" s="245" t="s">
+      <c r="M78" s="257" t="s">
         <v>60</v>
       </c>
-      <c r="N78" s="245"/>
+      <c r="N78" s="257"/>
       <c r="O78" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="P78" s="244"/>
-      <c r="Q78" s="236"/>
+      <c r="P78" s="256"/>
+      <c r="Q78" s="251"/>
       <c r="R78" s="139"/>
-      <c r="S78" s="246" t="s">
+      <c r="S78" s="196" t="s">
         <v>62</v>
       </c>
-      <c r="T78" s="246"/>
-      <c r="U78" s="246"/>
-      <c r="V78" s="246"/>
+      <c r="T78" s="196"/>
+      <c r="U78" s="196"/>
+      <c r="V78" s="196"/>
       <c r="W78" s="78"/>
-      <c r="X78" s="239" t="s">
+      <c r="X78" s="209" t="s">
         <v>63</v>
       </c>
       <c r="Y78" s="78"/>
@@ -7082,7 +7082,7 @@
       <c r="U79" s="81"/>
       <c r="V79" s="81"/>
       <c r="W79" s="78"/>
-      <c r="X79" s="240"/>
+      <c r="X79" s="210"/>
       <c r="Y79" s="78"/>
       <c r="Z79" s="78"/>
       <c r="AA79" s="78"/>
@@ -7102,35 +7102,35 @@
       <c r="C80" s="142"/>
       <c r="D80" s="142"/>
       <c r="E80" s="142"/>
-      <c r="F80" s="235" t="str">
+      <c r="F80" s="250" t="str">
         <f>IF(U7&gt;0,"",F76-T80)</f>
         <v/>
       </c>
-      <c r="G80" s="235"/>
-      <c r="H80" s="235"/>
-      <c r="I80" s="236"/>
+      <c r="G80" s="250"/>
+      <c r="H80" s="250"/>
+      <c r="I80" s="251"/>
       <c r="J80" s="80"/>
       <c r="K80" s="80"/>
       <c r="L80" s="80"/>
-      <c r="M80" s="242" t="str">
+      <c r="M80" s="254" t="str">
         <f>IF(U7&gt;0,"",T5+30)</f>
         <v/>
       </c>
-      <c r="N80" s="243"/>
+      <c r="N80" s="255"/>
       <c r="O80" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="P80" s="244"/>
-      <c r="Q80" s="236"/>
+      <c r="P80" s="256"/>
+      <c r="Q80" s="251"/>
       <c r="R80" s="139"/>
-      <c r="S80" s="247" t="s">
+      <c r="S80" s="258" t="s">
         <v>66</v>
       </c>
-      <c r="T80" s="248"/>
-      <c r="U80" s="248"/>
-      <c r="V80" s="248"/>
+      <c r="T80" s="259"/>
+      <c r="U80" s="259"/>
+      <c r="V80" s="259"/>
       <c r="W80" s="78"/>
-      <c r="X80" s="241"/>
+      <c r="X80" s="211"/>
       <c r="Y80" s="78"/>
       <c r="Z80" s="78"/>
       <c r="AA80" s="78"/>
@@ -7180,83 +7180,83 @@
       <c r="AI81" s="78"/>
     </row>
     <row r="82" spans="2:35" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="214" t="s">
+      <c r="B82" s="278" t="s">
         <v>67</v>
       </c>
-      <c r="C82" s="215"/>
-      <c r="D82" s="215"/>
-      <c r="E82" s="215"/>
-      <c r="F82" s="215"/>
-      <c r="G82" s="215"/>
-      <c r="H82" s="216"/>
-      <c r="I82" s="223" t="s">
+      <c r="C82" s="279"/>
+      <c r="D82" s="279"/>
+      <c r="E82" s="279"/>
+      <c r="F82" s="279"/>
+      <c r="G82" s="279"/>
+      <c r="H82" s="280"/>
+      <c r="I82" s="287" t="s">
         <v>68</v>
       </c>
       <c r="J82" s="148"/>
       <c r="K82" s="148"/>
       <c r="L82" s="148"/>
-      <c r="M82" s="225"/>
-      <c r="N82" s="228" t="s">
+      <c r="M82" s="289"/>
+      <c r="N82" s="292" t="s">
         <v>69</v>
       </c>
-      <c r="O82" s="231"/>
-      <c r="P82" s="225"/>
-      <c r="Q82" s="205" t="s">
+      <c r="O82" s="295"/>
+      <c r="P82" s="289"/>
+      <c r="Q82" s="269" t="s">
         <v>70</v>
       </c>
-      <c r="R82" s="206"/>
-      <c r="S82" s="211"/>
-      <c r="T82" s="205" t="s">
+      <c r="R82" s="270"/>
+      <c r="S82" s="275"/>
+      <c r="T82" s="269" t="s">
         <v>71</v>
       </c>
-      <c r="U82" s="195"/>
-      <c r="V82" s="195"/>
+      <c r="U82" s="215"/>
+      <c r="V82" s="215"/>
     </row>
     <row r="83" spans="2:35" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="217"/>
-      <c r="C83" s="218"/>
-      <c r="D83" s="218"/>
-      <c r="E83" s="218"/>
-      <c r="F83" s="218"/>
-      <c r="G83" s="218"/>
-      <c r="H83" s="219"/>
-      <c r="I83" s="199"/>
+      <c r="B83" s="281"/>
+      <c r="C83" s="282"/>
+      <c r="D83" s="282"/>
+      <c r="E83" s="282"/>
+      <c r="F83" s="282"/>
+      <c r="G83" s="282"/>
+      <c r="H83" s="283"/>
+      <c r="I83" s="263"/>
       <c r="J83" s="91"/>
       <c r="K83" s="91"/>
       <c r="L83" s="91"/>
-      <c r="M83" s="226"/>
-      <c r="N83" s="229"/>
-      <c r="O83" s="232"/>
-      <c r="P83" s="226"/>
-      <c r="Q83" s="207"/>
-      <c r="R83" s="208"/>
-      <c r="S83" s="212"/>
-      <c r="T83" s="207"/>
-      <c r="U83" s="195"/>
-      <c r="V83" s="195"/>
+      <c r="M83" s="290"/>
+      <c r="N83" s="293"/>
+      <c r="O83" s="296"/>
+      <c r="P83" s="290"/>
+      <c r="Q83" s="271"/>
+      <c r="R83" s="272"/>
+      <c r="S83" s="276"/>
+      <c r="T83" s="271"/>
+      <c r="U83" s="215"/>
+      <c r="V83" s="215"/>
     </row>
     <row r="84" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="220"/>
-      <c r="C84" s="221"/>
-      <c r="D84" s="221"/>
-      <c r="E84" s="221"/>
-      <c r="F84" s="221"/>
-      <c r="G84" s="221"/>
-      <c r="H84" s="222"/>
-      <c r="I84" s="224"/>
+      <c r="B84" s="284"/>
+      <c r="C84" s="285"/>
+      <c r="D84" s="285"/>
+      <c r="E84" s="285"/>
+      <c r="F84" s="285"/>
+      <c r="G84" s="285"/>
+      <c r="H84" s="286"/>
+      <c r="I84" s="288"/>
       <c r="J84" s="149"/>
       <c r="K84" s="149"/>
       <c r="L84" s="149"/>
-      <c r="M84" s="227"/>
-      <c r="N84" s="230"/>
-      <c r="O84" s="233"/>
-      <c r="P84" s="227"/>
-      <c r="Q84" s="209"/>
-      <c r="R84" s="210"/>
-      <c r="S84" s="213"/>
-      <c r="T84" s="209"/>
-      <c r="U84" s="195"/>
-      <c r="V84" s="195"/>
+      <c r="M84" s="291"/>
+      <c r="N84" s="294"/>
+      <c r="O84" s="297"/>
+      <c r="P84" s="291"/>
+      <c r="Q84" s="273"/>
+      <c r="R84" s="274"/>
+      <c r="S84" s="277"/>
+      <c r="T84" s="273"/>
+      <c r="U84" s="215"/>
+      <c r="V84" s="215"/>
     </row>
     <row r="85" spans="2:35" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="V85" s="190"/>
@@ -7318,22 +7318,22 @@
       <c r="V88" s="157"/>
     </row>
     <row r="89" spans="2:35" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B89" s="202"/>
-      <c r="C89" s="203"/>
-      <c r="D89" s="203"/>
-      <c r="E89" s="203"/>
-      <c r="F89" s="203"/>
-      <c r="G89" s="203"/>
-      <c r="H89" s="203"/>
-      <c r="I89" s="204"/>
+      <c r="B89" s="266"/>
+      <c r="C89" s="267"/>
+      <c r="D89" s="267"/>
+      <c r="E89" s="267"/>
+      <c r="F89" s="267"/>
+      <c r="G89" s="267"/>
+      <c r="H89" s="267"/>
+      <c r="I89" s="268"/>
       <c r="J89" s="88"/>
       <c r="K89" s="88"/>
       <c r="L89" s="88"/>
-      <c r="M89" s="202"/>
-      <c r="N89" s="203"/>
-      <c r="O89" s="203"/>
-      <c r="P89" s="203"/>
-      <c r="Q89" s="204"/>
+      <c r="M89" s="266"/>
+      <c r="N89" s="267"/>
+      <c r="O89" s="267"/>
+      <c r="P89" s="267"/>
+      <c r="Q89" s="268"/>
       <c r="R89" s="158"/>
       <c r="S89" s="159"/>
       <c r="T89" s="159"/>
@@ -7342,29 +7342,29 @@
       <c r="W89" s="155"/>
     </row>
     <row r="90" spans="2:35" ht="18" x14ac:dyDescent="0.25">
-      <c r="B90" s="196" t="s">
+      <c r="B90" s="260" t="s">
         <v>76</v>
       </c>
-      <c r="C90" s="197"/>
-      <c r="D90" s="197"/>
-      <c r="E90" s="197"/>
-      <c r="F90" s="197"/>
-      <c r="G90" s="197"/>
-      <c r="H90" s="197"/>
-      <c r="I90" s="198"/>
-      <c r="M90" s="196" t="s">
+      <c r="C90" s="261"/>
+      <c r="D90" s="261"/>
+      <c r="E90" s="261"/>
+      <c r="F90" s="261"/>
+      <c r="G90" s="261"/>
+      <c r="H90" s="261"/>
+      <c r="I90" s="262"/>
+      <c r="M90" s="260" t="s">
         <v>76</v>
       </c>
-      <c r="N90" s="197"/>
-      <c r="O90" s="197"/>
-      <c r="P90" s="197"/>
-      <c r="Q90" s="198"/>
-      <c r="R90" s="199" t="s">
+      <c r="N90" s="261"/>
+      <c r="O90" s="261"/>
+      <c r="P90" s="261"/>
+      <c r="Q90" s="262"/>
+      <c r="R90" s="263" t="s">
         <v>77</v>
       </c>
-      <c r="S90" s="200"/>
-      <c r="T90" s="200"/>
-      <c r="U90" s="201"/>
+      <c r="S90" s="264"/>
+      <c r="T90" s="264"/>
+      <c r="U90" s="265"/>
       <c r="V90" s="192"/>
       <c r="W90" s="153"/>
     </row>
@@ -7405,16 +7405,16 @@
       <c r="V93" s="154"/>
     </row>
     <row r="94" spans="2:35" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B94" s="202" t="s">
+      <c r="B94" s="266" t="s">
         <v>87</v>
       </c>
-      <c r="C94" s="203"/>
-      <c r="D94" s="203"/>
-      <c r="E94" s="203"/>
-      <c r="F94" s="203"/>
-      <c r="G94" s="203"/>
-      <c r="H94" s="203"/>
-      <c r="I94" s="204"/>
+      <c r="C94" s="267"/>
+      <c r="D94" s="267"/>
+      <c r="E94" s="267"/>
+      <c r="F94" s="267"/>
+      <c r="G94" s="267"/>
+      <c r="H94" s="267"/>
+      <c r="I94" s="268"/>
       <c r="J94" s="88"/>
       <c r="K94" s="88"/>
       <c r="L94" s="88"/>
@@ -7433,24 +7433,24 @@
       <c r="W94" s="155"/>
     </row>
     <row r="95" spans="2:35" ht="18" x14ac:dyDescent="0.25">
-      <c r="B95" s="196" t="s">
+      <c r="B95" s="260" t="s">
         <v>80</v>
       </c>
-      <c r="C95" s="197"/>
-      <c r="D95" s="197"/>
-      <c r="E95" s="197"/>
-      <c r="F95" s="197"/>
-      <c r="G95" s="197"/>
-      <c r="H95" s="197"/>
-      <c r="I95" s="198"/>
+      <c r="C95" s="261"/>
+      <c r="D95" s="261"/>
+      <c r="E95" s="261"/>
+      <c r="F95" s="261"/>
+      <c r="G95" s="261"/>
+      <c r="H95" s="261"/>
+      <c r="I95" s="262"/>
       <c r="M95" s="153"/>
       <c r="Q95" s="86"/>
-      <c r="R95" s="199" t="s">
+      <c r="R95" s="263" t="s">
         <v>81</v>
       </c>
-      <c r="S95" s="200"/>
-      <c r="T95" s="200"/>
-      <c r="U95" s="201"/>
+      <c r="S95" s="264"/>
+      <c r="T95" s="264"/>
+      <c r="U95" s="265"/>
       <c r="V95" s="164"/>
     </row>
     <row r="96" spans="2:35" ht="12.75" x14ac:dyDescent="0.25">
@@ -7492,80 +7492,36 @@
     <row r="103" spans="2:23" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="126">
-    <mergeCell ref="U70:V70"/>
-    <mergeCell ref="U71:V71"/>
-    <mergeCell ref="U72:V72"/>
-    <mergeCell ref="U73:V73"/>
-    <mergeCell ref="S76:V76"/>
-    <mergeCell ref="U65:V65"/>
-    <mergeCell ref="U66:V66"/>
-    <mergeCell ref="U67:V67"/>
-    <mergeCell ref="U68:V68"/>
-    <mergeCell ref="U69:V69"/>
-    <mergeCell ref="U60:V60"/>
-    <mergeCell ref="U61:V61"/>
-    <mergeCell ref="U62:V62"/>
-    <mergeCell ref="U63:V63"/>
-    <mergeCell ref="U64:V64"/>
-    <mergeCell ref="U55:V55"/>
-    <mergeCell ref="U56:V56"/>
-    <mergeCell ref="U57:V57"/>
-    <mergeCell ref="U58:V58"/>
-    <mergeCell ref="U59:V59"/>
-    <mergeCell ref="U50:V50"/>
-    <mergeCell ref="U51:V51"/>
-    <mergeCell ref="U52:V52"/>
-    <mergeCell ref="U53:V53"/>
-    <mergeCell ref="U54:V54"/>
-    <mergeCell ref="U45:V45"/>
-    <mergeCell ref="U46:V46"/>
-    <mergeCell ref="U47:V47"/>
-    <mergeCell ref="U48:V48"/>
-    <mergeCell ref="U49:V49"/>
-    <mergeCell ref="U40:V40"/>
-    <mergeCell ref="U41:V41"/>
-    <mergeCell ref="U42:V42"/>
-    <mergeCell ref="U43:V43"/>
-    <mergeCell ref="U44:V44"/>
-    <mergeCell ref="U35:V35"/>
-    <mergeCell ref="U36:V36"/>
-    <mergeCell ref="U37:V37"/>
-    <mergeCell ref="U38:V38"/>
-    <mergeCell ref="U39:V39"/>
-    <mergeCell ref="U30:V30"/>
-    <mergeCell ref="U31:V31"/>
-    <mergeCell ref="U32:V32"/>
-    <mergeCell ref="U33:V33"/>
-    <mergeCell ref="U34:V34"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="U29:V29"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="U21:V21"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="F2:S2"/>
-    <mergeCell ref="X2:X5"/>
-    <mergeCell ref="F5:M5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="X7:X8"/>
-    <mergeCell ref="F8:M8"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="S10:V10"/>
-    <mergeCell ref="S11:V11"/>
+    <mergeCell ref="U82:V84"/>
+    <mergeCell ref="B90:I90"/>
+    <mergeCell ref="M90:Q90"/>
+    <mergeCell ref="R90:U90"/>
+    <mergeCell ref="B94:I94"/>
+    <mergeCell ref="B95:I95"/>
+    <mergeCell ref="R95:U95"/>
+    <mergeCell ref="Q82:R84"/>
+    <mergeCell ref="S82:S84"/>
+    <mergeCell ref="T82:T84"/>
+    <mergeCell ref="B89:I89"/>
+    <mergeCell ref="M89:Q89"/>
+    <mergeCell ref="B82:H84"/>
+    <mergeCell ref="I82:I84"/>
+    <mergeCell ref="M82:M84"/>
+    <mergeCell ref="N82:N84"/>
+    <mergeCell ref="O82:P84"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="F76:I76"/>
+    <mergeCell ref="M76:N76"/>
+    <mergeCell ref="O76:Q76"/>
+    <mergeCell ref="X78:X80"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="S78:V78"/>
+    <mergeCell ref="S80:V80"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="D10:D12"/>
@@ -7588,36 +7544,80 @@
     <mergeCell ref="AD10:AD12"/>
     <mergeCell ref="AE10:AE12"/>
     <mergeCell ref="U12:V12"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="F76:I76"/>
-    <mergeCell ref="M76:N76"/>
-    <mergeCell ref="O76:Q76"/>
-    <mergeCell ref="X78:X80"/>
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="M80:N80"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="M78:N78"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="S78:V78"/>
-    <mergeCell ref="S80:V80"/>
-    <mergeCell ref="U82:V84"/>
-    <mergeCell ref="B90:I90"/>
-    <mergeCell ref="M90:Q90"/>
-    <mergeCell ref="R90:U90"/>
-    <mergeCell ref="B94:I94"/>
-    <mergeCell ref="B95:I95"/>
-    <mergeCell ref="R95:U95"/>
-    <mergeCell ref="Q82:R84"/>
-    <mergeCell ref="S82:S84"/>
-    <mergeCell ref="T82:T84"/>
-    <mergeCell ref="B89:I89"/>
-    <mergeCell ref="M89:Q89"/>
-    <mergeCell ref="B82:H84"/>
-    <mergeCell ref="I82:I84"/>
-    <mergeCell ref="M82:M84"/>
-    <mergeCell ref="N82:N84"/>
-    <mergeCell ref="O82:P84"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="F2:S2"/>
+    <mergeCell ref="X2:X5"/>
+    <mergeCell ref="F5:M5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="F8:M8"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="S10:V10"/>
+    <mergeCell ref="S11:V11"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="U21:V21"/>
+    <mergeCell ref="U22:V22"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="U30:V30"/>
+    <mergeCell ref="U31:V31"/>
+    <mergeCell ref="U32:V32"/>
+    <mergeCell ref="U33:V33"/>
+    <mergeCell ref="U34:V34"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="U29:V29"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="U41:V41"/>
+    <mergeCell ref="U42:V42"/>
+    <mergeCell ref="U43:V43"/>
+    <mergeCell ref="U44:V44"/>
+    <mergeCell ref="U35:V35"/>
+    <mergeCell ref="U36:V36"/>
+    <mergeCell ref="U37:V37"/>
+    <mergeCell ref="U38:V38"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="U50:V50"/>
+    <mergeCell ref="U51:V51"/>
+    <mergeCell ref="U52:V52"/>
+    <mergeCell ref="U53:V53"/>
+    <mergeCell ref="U54:V54"/>
+    <mergeCell ref="U45:V45"/>
+    <mergeCell ref="U46:V46"/>
+    <mergeCell ref="U47:V47"/>
+    <mergeCell ref="U48:V48"/>
+    <mergeCell ref="U49:V49"/>
+    <mergeCell ref="U60:V60"/>
+    <mergeCell ref="U61:V61"/>
+    <mergeCell ref="U62:V62"/>
+    <mergeCell ref="U63:V63"/>
+    <mergeCell ref="U64:V64"/>
+    <mergeCell ref="U55:V55"/>
+    <mergeCell ref="U56:V56"/>
+    <mergeCell ref="U57:V57"/>
+    <mergeCell ref="U58:V58"/>
+    <mergeCell ref="U59:V59"/>
+    <mergeCell ref="U70:V70"/>
+    <mergeCell ref="U71:V71"/>
+    <mergeCell ref="U72:V72"/>
+    <mergeCell ref="U73:V73"/>
+    <mergeCell ref="S76:V76"/>
+    <mergeCell ref="U65:V65"/>
+    <mergeCell ref="U66:V66"/>
+    <mergeCell ref="U67:V67"/>
+    <mergeCell ref="U68:V68"/>
+    <mergeCell ref="U69:V69"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0" top="0" bottom="0" header="0" footer="0.19685039370078741"/>
